--- a/Methanol/Methanol_Bio_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_Brownfield_Leuna/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="27928"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Brownfield_Memmingen_Bio\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{BB321755-11A9-4296-B9D2-67D4CB6B7F97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E70D58-6F3B-4347-868A-8396D0AAD775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1348,7 +1348,7 @@
     <numFmt numFmtId="165" formatCode="0.000"/>
     <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
-  <fonts count="9" x14ac:knownFonts="1">
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -1389,41 +1389,13 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
-    <font>
-      <b/>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FF00B050"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="11"/>
-      <color rgb="FFFF0000"/>
-      <name val="Calibri"/>
-      <family val="2"/>
-      <scheme val="minor"/>
-    </font>
   </fonts>
-  <fills count="3">
+  <fills count="2">
     <fill>
       <patternFill patternType="none"/>
     </fill>
     <fill>
       <patternFill patternType="gray125"/>
-    </fill>
-    <fill>
-      <patternFill patternType="solid">
-        <fgColor rgb="FF00B050"/>
-        <bgColor indexed="64"/>
-      </patternFill>
     </fill>
   </fills>
   <borders count="8">
@@ -1508,106 +1480,94 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="61">
+  <cellXfs count="51">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="6" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="7" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="1" fontId="7" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1933,18 +1893,18 @@
   <dimension ref="A1:G76"/>
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="10.88671875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="22" customWidth="1"/>
-    <col min="3" max="3" width="36.21875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="21" style="1" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="9" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="40.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="20.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="20.77734375" style="1" customWidth="1"/>
-    <col min="9" max="9" width="13.88671875" style="1" bestFit="1" customWidth="1"/>
-    <col min="10" max="10" width="14" style="1" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="10.77734375" style="1" bestFit="1" customWidth="1"/>
-    <col min="12" max="16384" width="8.88671875" style="1"/>
+    <col min="1" max="1" width="10.88671875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="40" customWidth="1"/>
+    <col min="3" max="3" width="36.21875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21" style="6" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="15" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="40.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="20.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="20.77734375" style="6" customWidth="1"/>
+    <col min="9" max="9" width="13.88671875" style="6" bestFit="1" customWidth="1"/>
+    <col min="10" max="10" width="14" style="6" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="10.77734375" style="6" bestFit="1" customWidth="1"/>
+    <col min="12" max="16384" width="8.88671875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:7" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -1966,1244 +1926,1244 @@
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="22"/>
+      <c r="G1" s="40"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="9" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="9" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="6">
+      <c r="E2" s="10">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="2" t="s">
+      <c r="F2" s="9" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="7">
+      <c r="E3" s="13">
         <v>50</v>
       </c>
-      <c r="F3" s="1" t="s">
+      <c r="F3" s="6" t="s">
         <v>185</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="46"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="8">
+      <c r="E4" s="14">
         <v>1000</v>
       </c>
-      <c r="F4" s="1" t="s">
+      <c r="F4" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="9">
+      <c r="E5" s="15">
         <v>0.03</v>
       </c>
-      <c r="F5" s="1" t="s">
+      <c r="F5" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="46"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="1" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="10">
+      <c r="E6" s="16">
         <v>20</v>
       </c>
-      <c r="F6" s="1" t="s">
+      <c r="F6" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="46"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="9">
+      <c r="E7" s="15">
         <v>0.08</v>
       </c>
-      <c r="F7" s="1" t="s">
+      <c r="F7" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="46"/>
-      <c r="B8" s="57" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="C8" s="11" t="s">
+      <c r="C8" s="18" t="s">
         <v>84</v>
       </c>
-      <c r="D8" s="11" t="s">
+      <c r="D8" s="18" t="s">
         <v>233</v>
       </c>
-      <c r="E8" s="12">
+      <c r="E8" s="19">
         <v>1.5</v>
       </c>
-      <c r="F8" s="11" t="s">
+      <c r="F8" s="18" t="s">
         <v>232</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="46"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="1" t="s">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>234</v>
       </c>
-      <c r="E9" s="7">
+      <c r="E9" s="13">
         <v>285.39999999999998</v>
       </c>
-      <c r="F9" s="1" t="s">
+      <c r="F9" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="1" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>235</v>
       </c>
-      <c r="E10" s="7">
-        <v>5000</v>
-      </c>
-      <c r="F10" s="7" t="s">
+      <c r="E10" s="13">
+        <v>5110</v>
+      </c>
+      <c r="F10" s="13" t="s">
         <v>240</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
-      <c r="B11" s="54"/>
-      <c r="C11" s="1" t="s">
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D11" s="1" t="s">
+      <c r="D11" s="6" t="s">
         <v>236</v>
       </c>
-      <c r="E11" s="9">
+      <c r="E11" s="15">
         <v>0.05</v>
       </c>
-      <c r="F11" s="1" t="s">
+      <c r="F11" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="46"/>
-      <c r="B12" s="54"/>
-      <c r="C12" s="1" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="12"/>
+      <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
-      <c r="D12" s="1" t="s">
+      <c r="D12" s="6" t="s">
         <v>237</v>
       </c>
-      <c r="E12" s="7">
+      <c r="E12" s="13">
         <v>0.189</v>
       </c>
-      <c r="F12" s="1" t="s">
+      <c r="F12" s="6" t="s">
         <v>241</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="1" t="s">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="6" t="s">
         <v>246</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>242</v>
       </c>
-      <c r="E13" s="7">
+      <c r="E13" s="13">
         <v>1.375</v>
       </c>
-      <c r="F13" s="1" t="s">
+      <c r="F13" s="6" t="s">
         <v>243</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="1" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>238</v>
       </c>
-      <c r="E14" s="10">
+      <c r="E14" s="16">
         <v>25</v>
       </c>
-      <c r="F14" s="1" t="s">
+      <c r="F14" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
-      <c r="B15" s="58"/>
-      <c r="C15" s="13" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="20"/>
+      <c r="C15" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="13" t="s">
+      <c r="D15" s="21" t="s">
         <v>239</v>
       </c>
-      <c r="E15" s="14">
+      <c r="E15" s="22">
         <v>0.08</v>
       </c>
-      <c r="F15" s="13" t="s">
+      <c r="F15" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
-      <c r="B16" s="57" t="s">
+      <c r="A16" s="11"/>
+      <c r="B16" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="C16" s="11" t="s">
+      <c r="C16" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="11" t="s">
+      <c r="D16" s="18" t="s">
         <v>276</v>
       </c>
-      <c r="E16" s="16">
+      <c r="E16" s="28">
         <v>3.7</v>
       </c>
-      <c r="F16" s="11" t="s">
+      <c r="F16" s="18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="46"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="1" t="s">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="6" t="s">
         <v>277</v>
       </c>
-      <c r="E17" s="9">
+      <c r="E17" s="15">
         <v>0.27</v>
       </c>
-      <c r="F17" s="1" t="s">
+      <c r="F17" s="6" t="s">
         <v>302</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="1" t="s">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="6" t="s">
         <v>278</v>
       </c>
-      <c r="E18" s="9">
+      <c r="E18" s="15">
         <v>700</v>
       </c>
-      <c r="F18" s="1" t="s">
+      <c r="F18" s="6" t="s">
         <v>282</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="1" t="s">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="6" t="s">
         <v>279</v>
       </c>
-      <c r="E19" s="9">
+      <c r="E19" s="15">
         <v>0.02</v>
       </c>
-      <c r="F19" s="1" t="s">
+      <c r="F19" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="46"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="1" t="s">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="6" t="s">
         <v>280</v>
       </c>
-      <c r="E20" s="9">
+      <c r="E20" s="15">
         <v>20</v>
       </c>
-      <c r="F20" s="1" t="s">
+      <c r="F20" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="46"/>
-      <c r="B21" s="58"/>
-      <c r="C21" s="13" t="s">
+      <c r="A21" s="11"/>
+      <c r="B21" s="20"/>
+      <c r="C21" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="13" t="s">
+      <c r="D21" s="21" t="s">
         <v>281</v>
       </c>
-      <c r="E21" s="14">
+      <c r="E21" s="22">
         <v>0.05</v>
       </c>
-      <c r="F21" s="13" t="s">
+      <c r="F21" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="46"/>
-      <c r="B22" s="59" t="s">
+      <c r="A22" s="11"/>
+      <c r="B22" s="23" t="s">
         <v>342</v>
       </c>
-      <c r="C22" s="1" t="s">
+      <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D22" s="40" t="s">
+      <c r="D22" s="6" t="s">
         <v>351</v>
       </c>
-      <c r="E22" s="39">
+      <c r="E22" s="13">
         <v>0.2</v>
       </c>
-      <c r="F22" s="1" t="s">
+      <c r="F22" s="6" t="s">
         <v>244</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="46"/>
-      <c r="B23" s="59"/>
-      <c r="C23" s="1" t="s">
+      <c r="A23" s="11"/>
+      <c r="B23" s="23"/>
+      <c r="C23" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="D23" s="40" t="s">
+      <c r="D23" s="6" t="s">
         <v>352</v>
       </c>
-      <c r="E23" s="39">
+      <c r="E23" s="13">
         <v>0.92800000000000005</v>
       </c>
-      <c r="F23" s="1" t="s">
+      <c r="F23" s="6" t="s">
         <v>284</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="46"/>
-      <c r="B24" s="59"/>
-      <c r="C24" s="1" t="s">
+      <c r="A24" s="11"/>
+      <c r="B24" s="23"/>
+      <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D24" s="40" t="s">
+      <c r="D24" s="6" t="s">
         <v>353</v>
       </c>
-      <c r="E24" s="39">
+      <c r="E24" s="13">
         <v>1640</v>
       </c>
-      <c r="F24" s="1" t="s">
+      <c r="F24" s="6" t="s">
         <v>245</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="46"/>
-      <c r="B25" s="59"/>
-      <c r="C25" s="1" t="s">
+      <c r="A25" s="11"/>
+      <c r="B25" s="23"/>
+      <c r="C25" s="6" t="s">
         <v>379</v>
       </c>
-      <c r="D25" s="40" t="s">
+      <c r="D25" s="6" t="s">
         <v>354</v>
       </c>
-      <c r="E25" s="41">
+      <c r="E25" s="15">
         <v>0.04</v>
       </c>
-      <c r="F25" s="1" t="s">
+      <c r="F25" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="46"/>
-      <c r="B26" s="59"/>
-      <c r="C26" s="1" t="s">
+      <c r="A26" s="11"/>
+      <c r="B26" s="23"/>
+      <c r="C26" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D26" s="40" t="s">
+      <c r="D26" s="6" t="s">
         <v>373</v>
       </c>
-      <c r="E26" s="41">
+      <c r="E26" s="15">
         <v>2.5</v>
       </c>
-      <c r="F26" s="40" t="s">
+      <c r="F26" s="6" t="s">
         <v>374</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="46"/>
-      <c r="B27" s="59"/>
-      <c r="C27" s="1" t="s">
+      <c r="A27" s="11"/>
+      <c r="B27" s="23"/>
+      <c r="C27" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="D27" s="42" t="s">
+      <c r="D27" s="6" t="s">
         <v>356</v>
       </c>
-      <c r="E27" s="43">
+      <c r="E27" s="15">
         <v>1.5</v>
       </c>
-      <c r="F27" s="42" t="s">
+      <c r="F27" s="6" t="s">
         <v>357</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="46"/>
-      <c r="B28" s="59"/>
-      <c r="C28" s="1" t="s">
+      <c r="A28" s="11"/>
+      <c r="B28" s="23"/>
+      <c r="C28" s="6" t="s">
         <v>380</v>
       </c>
-      <c r="D28" s="42" t="s">
+      <c r="D28" s="6" t="s">
         <v>377</v>
       </c>
-      <c r="E28" s="43">
+      <c r="E28" s="15">
         <v>1.5E-3</v>
       </c>
-      <c r="F28" s="42" t="s">
+      <c r="F28" s="6" t="s">
         <v>378</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="46"/>
-      <c r="B29" s="59"/>
-      <c r="C29" s="1" t="s">
+      <c r="A29" s="11"/>
+      <c r="B29" s="23"/>
+      <c r="C29" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D29" s="40" t="s">
+      <c r="D29" s="6" t="s">
         <v>358</v>
       </c>
-      <c r="E29" s="44">
+      <c r="E29" s="16">
         <v>25</v>
       </c>
-      <c r="F29" s="1" t="s">
+      <c r="F29" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="46"/>
-      <c r="B30" s="59"/>
-      <c r="C30" s="1" t="s">
+      <c r="A30" s="11"/>
+      <c r="B30" s="23"/>
+      <c r="C30" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D30" s="40" t="s">
+      <c r="D30" s="6" t="s">
         <v>359</v>
       </c>
-      <c r="E30" s="41">
+      <c r="E30" s="15">
         <v>0.08</v>
       </c>
-      <c r="F30" s="1" t="s">
+      <c r="F30" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="45" t="s">
+      <c r="A31" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="49" t="s">
+      <c r="B31" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="2" t="s">
+      <c r="C31" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="2" t="s">
+      <c r="D31" s="9" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="15">
+      <c r="E31" s="25">
         <v>490</v>
       </c>
-      <c r="F31" s="2" t="s">
+      <c r="F31" s="9" t="s">
         <v>93</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="46"/>
-      <c r="B32" s="50"/>
-      <c r="C32" s="1" t="s">
+      <c r="A32" s="11"/>
+      <c r="B32" s="23"/>
+      <c r="C32" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D32" s="1" t="s">
+      <c r="D32" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="9">
+      <c r="E32" s="15">
         <v>0.01</v>
       </c>
-      <c r="F32" s="1" t="s">
+      <c r="F32" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="46"/>
-      <c r="B33" s="50"/>
-      <c r="C33" s="1" t="s">
+      <c r="A33" s="11"/>
+      <c r="B33" s="23"/>
+      <c r="C33" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="10">
+      <c r="E33" s="16">
         <v>20</v>
       </c>
-      <c r="F33" s="1" t="s">
+      <c r="F33" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="46"/>
-      <c r="B34" s="50"/>
-      <c r="C34" s="1" t="s">
+      <c r="A34" s="11"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="23">
+      <c r="E34" s="41">
         <v>1.0000000000000001E-5</v>
       </c>
-      <c r="F34" s="1" t="s">
+      <c r="F34" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="46"/>
-      <c r="B35" s="50"/>
-      <c r="C35" s="1" t="s">
+      <c r="A35" s="11"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="9">
+      <c r="E35" s="15">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F35" s="1" t="s">
+      <c r="F35" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="46"/>
-      <c r="B36" s="50"/>
-      <c r="C36" s="1" t="s">
+      <c r="A36" s="11"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="9">
+      <c r="E36" s="15">
         <v>0.83299999999999996</v>
       </c>
-      <c r="F36" s="1" t="s">
+      <c r="F36" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="50"/>
-      <c r="C37" s="1" t="s">
+      <c r="A37" s="11"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="9">
+      <c r="E37" s="15">
         <v>0.05</v>
       </c>
-      <c r="F37" s="1" t="s">
+      <c r="F37" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="46"/>
-      <c r="B38" s="51"/>
-      <c r="C38" s="13" t="s">
+      <c r="A38" s="11"/>
+      <c r="B38" s="26"/>
+      <c r="C38" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="13" t="s">
+      <c r="D38" s="21" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="14">
+      <c r="E38" s="22">
         <v>0</v>
       </c>
-      <c r="F38" s="13" t="s">
+      <c r="F38" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
-      <c r="B39" s="52" t="s">
+      <c r="A39" s="11"/>
+      <c r="B39" s="27" t="s">
         <v>317</v>
       </c>
-      <c r="C39" s="2" t="s">
+      <c r="C39" s="9" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="2" t="s">
+      <c r="D39" s="9" t="s">
         <v>318</v>
       </c>
-      <c r="E39" s="15">
+      <c r="E39" s="25">
         <v>2.83</v>
       </c>
-      <c r="F39" s="2" t="s">
+      <c r="F39" s="9" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
-      <c r="B40" s="50"/>
-      <c r="C40" s="1" t="s">
+      <c r="A40" s="11"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="6" t="s">
         <v>319</v>
       </c>
-      <c r="E40" s="9">
+      <c r="E40" s="15">
         <v>0.03</v>
       </c>
-      <c r="F40" s="1" t="s">
+      <c r="F40" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
-      <c r="B41" s="50"/>
-      <c r="C41" s="1" t="s">
+      <c r="A41" s="11"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="6" t="s">
         <v>320</v>
       </c>
-      <c r="E41" s="10">
+      <c r="E41" s="16">
         <v>30</v>
       </c>
-      <c r="F41" s="1" t="s">
+      <c r="F41" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
-      <c r="B42" s="50"/>
-      <c r="C42" s="1" t="s">
+      <c r="A42" s="11"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="6" t="s">
         <v>20</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="6" t="s">
         <v>321</v>
       </c>
-      <c r="E42" s="9">
+      <c r="E42" s="15">
         <v>7.3999999999999999E-4</v>
       </c>
-      <c r="F42" s="1" t="s">
+      <c r="F42" s="6" t="s">
         <v>94</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="50"/>
-      <c r="C43" s="1" t="s">
+      <c r="A43" s="11"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="6" t="s">
         <v>322</v>
       </c>
-      <c r="E43" s="9">
+      <c r="E43" s="15">
         <v>0.98</v>
       </c>
-      <c r="F43" s="1" t="s">
+      <c r="F43" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
-      <c r="B44" s="50"/>
-      <c r="C44" s="1" t="s">
+      <c r="A44" s="11"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="6" t="s">
         <v>323</v>
       </c>
-      <c r="E44" s="9">
+      <c r="E44" s="15">
         <v>0.98</v>
       </c>
-      <c r="F44" s="1" t="s">
+      <c r="F44" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="46"/>
-      <c r="B45" s="50"/>
-      <c r="C45" s="1" t="s">
+      <c r="A45" s="11"/>
+      <c r="B45" s="23"/>
+      <c r="C45" s="6" t="s">
         <v>15</v>
       </c>
-      <c r="D45" s="1" t="s">
+      <c r="D45" s="6" t="s">
         <v>324</v>
       </c>
-      <c r="E45" s="9">
+      <c r="E45" s="15">
         <v>0.05</v>
       </c>
-      <c r="F45" s="1" t="s">
+      <c r="F45" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="46"/>
-      <c r="B46" s="50"/>
-      <c r="C46" s="13" t="s">
+      <c r="A46" s="11"/>
+      <c r="B46" s="23"/>
+      <c r="C46" s="21" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="13" t="s">
+      <c r="D46" s="21" t="s">
         <v>325</v>
       </c>
-      <c r="E46" s="14">
+      <c r="E46" s="22">
         <v>0</v>
       </c>
-      <c r="F46" s="13" t="s">
+      <c r="F46" s="21" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="46"/>
-      <c r="B47" s="52" t="s">
+      <c r="A47" s="11"/>
+      <c r="B47" s="27" t="s">
         <v>203</v>
       </c>
-      <c r="C47" s="11" t="s">
+      <c r="C47" s="18" t="s">
         <v>91</v>
       </c>
-      <c r="D47" s="11" t="s">
+      <c r="D47" s="18" t="s">
         <v>62</v>
       </c>
-      <c r="E47" s="16">
+      <c r="E47" s="28">
         <v>1.6999999999999999E-3</v>
       </c>
-      <c r="F47" s="11" t="s">
+      <c r="F47" s="18" t="s">
         <v>96</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="46"/>
-      <c r="B48" s="54"/>
-      <c r="C48" s="1" t="s">
+      <c r="A48" s="11"/>
+      <c r="B48" s="12"/>
+      <c r="C48" s="6" t="s">
         <v>21</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="7">
+      <c r="E48" s="13">
         <f>E49*4</f>
         <v>424</v>
       </c>
-      <c r="F48" s="1" t="s">
+      <c r="F48" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="54"/>
-      <c r="C49" s="1" t="s">
+      <c r="A49" s="11"/>
+      <c r="B49" s="12"/>
+      <c r="C49" s="6" t="s">
         <v>16</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="7">
+      <c r="E49" s="13">
         <v>106</v>
       </c>
-      <c r="F49" s="1" t="s">
+      <c r="F49" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="46"/>
-      <c r="B50" s="54"/>
-      <c r="C50" s="1" t="s">
+      <c r="A50" s="11"/>
+      <c r="B50" s="12"/>
+      <c r="C50" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="9">
+      <c r="E50" s="15">
         <v>2.5000000000000001E-2</v>
       </c>
-      <c r="F50" s="1" t="s">
+      <c r="F50" s="6" t="s">
         <v>64</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="46"/>
-      <c r="B51" s="54"/>
-      <c r="C51" s="1" t="s">
+      <c r="A51" s="11"/>
+      <c r="B51" s="12"/>
+      <c r="C51" s="6" t="s">
         <v>35</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="9">
+      <c r="E51" s="15">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F51" s="1" t="s">
+      <c r="F51" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="46"/>
-      <c r="B52" s="54"/>
-      <c r="C52" s="1" t="s">
+      <c r="A52" s="11"/>
+      <c r="B52" s="12"/>
+      <c r="C52" s="6" t="s">
         <v>36</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="9">
+      <c r="E52" s="15">
         <v>0.93500000000000005</v>
       </c>
-      <c r="F52" s="1" t="s">
+      <c r="F52" s="6" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
-      <c r="B53" s="54"/>
-      <c r="C53" s="1" t="s">
+      <c r="A53" s="11"/>
+      <c r="B53" s="12"/>
+      <c r="C53" s="6" t="s">
         <v>89</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="7">
+      <c r="E53" s="13">
         <v>0.25</v>
       </c>
-      <c r="F53" s="1" t="s">
+      <c r="F53" s="6" t="s">
         <v>90</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
-      <c r="B54" s="54"/>
-      <c r="C54" s="1" t="s">
+      <c r="A54" s="11"/>
+      <c r="B54" s="12"/>
+      <c r="C54" s="6" t="s">
         <v>88</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="9">
+      <c r="E54" s="15">
         <v>0</v>
       </c>
-      <c r="F54" s="1" t="s">
+      <c r="F54" s="6" t="s">
         <v>95</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
-      <c r="B55" s="54"/>
-      <c r="C55" s="1" t="s">
+      <c r="A55" s="11"/>
+      <c r="B55" s="12"/>
+      <c r="C55" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D55" s="1" t="s">
+      <c r="D55" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="10">
+      <c r="E55" s="16">
         <v>15</v>
       </c>
-      <c r="F55" s="1" t="s">
+      <c r="F55" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="47"/>
-      <c r="B56" s="55"/>
-      <c r="C56" s="17" t="s">
+      <c r="A56" s="29"/>
+      <c r="B56" s="30"/>
+      <c r="C56" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="17" t="s">
+      <c r="D56" s="31" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="18">
+      <c r="E56" s="32">
         <v>0.1</v>
       </c>
-      <c r="F56" s="17" t="s">
+      <c r="F56" s="31" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="45" t="s">
+      <c r="A57" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="30" t="s">
+      <c r="B57" s="48" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="31" t="s">
+      <c r="C57" s="43" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="31" t="s">
+      <c r="D57" s="43" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="32">
+      <c r="E57" s="44">
         <v>0.1699</v>
       </c>
-      <c r="F57" s="31" t="s">
+      <c r="F57" s="43" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="48"/>
-      <c r="B58" s="27" t="s">
+      <c r="A58" s="39"/>
+      <c r="B58" s="49" t="s">
         <v>343</v>
       </c>
-      <c r="C58" s="28" t="s">
+      <c r="C58" s="34" t="s">
         <v>344</v>
       </c>
-      <c r="D58" s="28" t="s">
+      <c r="D58" s="34" t="s">
         <v>345</v>
       </c>
-      <c r="E58" s="29">
+      <c r="E58" s="50">
         <v>0</v>
       </c>
-      <c r="F58" s="28" t="s">
+      <c r="F58" s="34" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="46"/>
-      <c r="B59" s="52" t="s">
+      <c r="A59" s="11"/>
+      <c r="B59" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C59" s="11" t="s">
+      <c r="C59" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="11" t="s">
+      <c r="D59" s="18" t="s">
         <v>46</v>
       </c>
-      <c r="E59" s="16">
+      <c r="E59" s="28">
         <v>0.99</v>
       </c>
-      <c r="F59" s="11" t="s">
+      <c r="F59" s="18" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="46"/>
-      <c r="B60" s="50"/>
-      <c r="C60" s="1" t="s">
+      <c r="A60" s="11"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="6" t="s">
         <v>43</v>
       </c>
-      <c r="E60" s="19">
+      <c r="E60" s="1">
         <v>1100</v>
       </c>
-      <c r="F60" s="1" t="s">
+      <c r="F60" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="46"/>
-      <c r="B61" s="50"/>
-      <c r="C61" s="1" t="s">
+      <c r="A61" s="11"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="6" t="s">
         <v>44</v>
       </c>
-      <c r="E61" s="19">
+      <c r="E61" s="1">
         <v>17.84</v>
       </c>
-      <c r="F61" s="1" t="s">
+      <c r="F61" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="46"/>
-      <c r="B62" s="50"/>
-      <c r="C62" s="1" t="s">
+      <c r="A62" s="11"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E62" s="7">
+      <c r="E62" s="13">
         <v>0</v>
       </c>
-      <c r="F62" s="1" t="s">
+      <c r="F62" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="46"/>
-      <c r="B63" s="50"/>
-      <c r="C63" s="1" t="s">
+      <c r="A63" s="11"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E63" s="10">
+      <c r="E63" s="16">
         <v>25</v>
       </c>
-      <c r="F63" s="1" t="s">
+      <c r="F63" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="46"/>
-      <c r="B64" s="50"/>
-      <c r="C64" s="1" t="s">
+      <c r="A64" s="11"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E64" s="7">
+      <c r="E64" s="13">
         <v>1000000</v>
       </c>
-      <c r="F64" s="1" t="s">
+      <c r="F64" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="46"/>
-      <c r="B65" s="51"/>
-      <c r="C65" s="13" t="s">
+      <c r="A65" s="11"/>
+      <c r="B65" s="26"/>
+      <c r="C65" s="21" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="13" t="s">
+      <c r="D65" s="21" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="14">
+      <c r="E65" s="22">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F65" s="13" t="s">
+      <c r="F65" s="21" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="46"/>
-      <c r="B66" s="52" t="s">
+      <c r="A66" s="11"/>
+      <c r="B66" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="18" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="18" t="s">
         <v>47</v>
       </c>
-      <c r="E66" s="16">
+      <c r="E66" s="28">
         <v>0.997</v>
       </c>
-      <c r="F66" s="11" t="s">
+      <c r="F66" s="18" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="46"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="1" t="s">
+      <c r="A67" s="11"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="6" t="s">
         <v>10</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="6" t="s">
         <v>48</v>
       </c>
-      <c r="E67" s="19">
+      <c r="E67" s="1">
         <v>1080</v>
       </c>
-      <c r="F67" s="1" t="s">
+      <c r="F67" s="6" t="s">
         <v>12</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
-      <c r="B68" s="50"/>
-      <c r="C68" s="1" t="s">
+      <c r="A68" s="11"/>
+      <c r="B68" s="23"/>
+      <c r="C68" s="6" t="s">
         <v>17</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="6" t="s">
         <v>52</v>
       </c>
-      <c r="E68" s="19">
+      <c r="E68" s="1">
         <v>12.68</v>
       </c>
-      <c r="F68" s="1" t="s">
+      <c r="F68" s="6" t="s">
         <v>92</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="46"/>
-      <c r="B69" s="50"/>
-      <c r="C69" s="1" t="s">
+      <c r="A69" s="11"/>
+      <c r="B69" s="23"/>
+      <c r="C69" s="6" t="s">
         <v>18</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="6" t="s">
         <v>49</v>
       </c>
-      <c r="E69" s="21">
+      <c r="E69" s="2">
         <v>5.0000000000000001E-3</v>
       </c>
-      <c r="F69" s="1" t="s">
+      <c r="F69" s="6" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="46"/>
-      <c r="B70" s="50"/>
-      <c r="C70" s="1" t="s">
+      <c r="A70" s="11"/>
+      <c r="B70" s="23"/>
+      <c r="C70" s="6" t="s">
         <v>13</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E70" s="10">
+      <c r="E70" s="16">
         <v>25</v>
       </c>
-      <c r="F70" s="1" t="s">
+      <c r="F70" s="6" t="s">
         <v>14</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="46"/>
-      <c r="B71" s="50"/>
-      <c r="C71" s="1" t="s">
+      <c r="A71" s="11"/>
+      <c r="B71" s="23"/>
+      <c r="C71" s="6" t="s">
         <v>68</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E71" s="20">
+      <c r="E71" s="37">
         <v>1000000</v>
       </c>
-      <c r="F71" s="1" t="s">
+      <c r="F71" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="47"/>
-      <c r="B72" s="53"/>
-      <c r="C72" s="17" t="s">
+      <c r="A72" s="29"/>
+      <c r="B72" s="38"/>
+      <c r="C72" s="31" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="17" t="s">
+      <c r="D72" s="31" t="s">
         <v>51</v>
       </c>
-      <c r="E72" s="18">
+      <c r="E72" s="32">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F72" s="17" t="s">
+      <c r="F72" s="31" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="45" t="s">
+      <c r="A73" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="33" t="s">
+      <c r="B73" s="42" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="34" t="s">
+      <c r="C73" s="43" t="s">
         <v>77</v>
       </c>
-      <c r="D73" s="34" t="s">
+      <c r="D73" s="43" t="s">
         <v>78</v>
       </c>
-      <c r="E73" s="35">
+      <c r="E73" s="44">
         <v>-1E-4</v>
       </c>
-      <c r="F73" s="34" t="s">
+      <c r="F73" s="43" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="46"/>
-      <c r="B74" s="22" t="s">
+      <c r="A74" s="11"/>
+      <c r="B74" s="40" t="s">
         <v>299</v>
       </c>
-      <c r="C74" s="1" t="s">
+      <c r="C74" s="6" t="s">
         <v>300</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="6" t="s">
         <v>301</v>
       </c>
-      <c r="E74" s="9">
+      <c r="E74" s="15">
         <v>-1E-4</v>
       </c>
-      <c r="F74" s="1" t="s">
+      <c r="F74" s="6" t="s">
         <v>326</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="46"/>
-      <c r="B75" s="24" t="s">
+      <c r="A75" s="11"/>
+      <c r="B75" s="45" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="25" t="s">
+      <c r="C75" s="46" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="25" t="s">
+      <c r="D75" s="46" t="s">
         <v>81</v>
       </c>
-      <c r="E75" s="26">
+      <c r="E75" s="47">
         <v>-1.5</v>
       </c>
-      <c r="F75" s="25" t="s">
+      <c r="F75" s="46" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="47"/>
+      <c r="A76" s="29"/>
       <c r="B76" s="4" t="s">
         <v>262</v>
       </c>
-      <c r="C76" s="17" t="s">
+      <c r="C76" s="31" t="s">
         <v>274</v>
       </c>
-      <c r="D76" s="17" t="s">
+      <c r="D76" s="31" t="s">
         <v>272</v>
       </c>
-      <c r="E76" s="18">
+      <c r="E76" s="32">
         <v>-0.6</v>
       </c>
-      <c r="F76" s="17" t="s">
+      <c r="F76" s="31" t="s">
         <v>275</v>
       </c>
     </row>
@@ -3234,13 +3194,13 @@
   <dimension ref="A1:F149"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.5546875" style="1" customWidth="1"/>
-    <col min="2" max="2" width="30.33203125" style="1" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="38.5546875" style="1" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="50.77734375" style="1" customWidth="1"/>
-    <col min="5" max="5" width="46.109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="37.5546875" style="1" customWidth="1"/>
-    <col min="7" max="16384" width="11.5546875" style="1"/>
+    <col min="1" max="1" width="14.5546875" style="6" customWidth="1"/>
+    <col min="2" max="2" width="30.33203125" style="6" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="38.5546875" style="6" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="50.77734375" style="6" customWidth="1"/>
+    <col min="5" max="5" width="46.109375" style="6" customWidth="1"/>
+    <col min="6" max="6" width="37.5546875" style="6" customWidth="1"/>
+    <col min="7" max="16384" width="11.5546875" style="6"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
@@ -3264,1955 +3224,1946 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="45" t="s">
+      <c r="A2" s="7" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="56" t="s">
+      <c r="B2" s="8" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="2" t="s">
+      <c r="C2" s="9" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="2" t="s">
+      <c r="D2" s="9" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="6"/>
-      <c r="F2" s="2" t="s">
+      <c r="E2" s="10"/>
+      <c r="F2" s="9" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="46"/>
-      <c r="B3" s="54"/>
-      <c r="C3" s="1" t="s">
+      <c r="A3" s="11"/>
+      <c r="B3" s="12"/>
+      <c r="C3" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D3" s="1" t="s">
+      <c r="D3" s="6" t="s">
         <v>116</v>
       </c>
-      <c r="E3" s="7"/>
-      <c r="F3" s="1" t="s">
+      <c r="E3" s="13"/>
+      <c r="F3" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="46"/>
-      <c r="B4" s="54"/>
-      <c r="C4" s="1" t="s">
+      <c r="A4" s="11"/>
+      <c r="B4" s="12"/>
+      <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D4" s="1" t="s">
+      <c r="D4" s="6" t="s">
         <v>124</v>
       </c>
-      <c r="E4" s="8"/>
-      <c r="F4" s="1" t="s">
+      <c r="E4" s="14"/>
+      <c r="F4" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="46"/>
-      <c r="B5" s="54"/>
-      <c r="C5" s="1" t="s">
+      <c r="A5" s="11"/>
+      <c r="B5" s="12"/>
+      <c r="C5" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="1" t="s">
+      <c r="D5" s="6" t="s">
         <v>138</v>
       </c>
-      <c r="E5" s="9"/>
-      <c r="F5" s="1" t="s">
+      <c r="E5" s="15"/>
+      <c r="F5" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="46"/>
-      <c r="B6" s="54"/>
-      <c r="C6" s="1" t="s">
+      <c r="A6" s="11"/>
+      <c r="B6" s="12"/>
+      <c r="C6" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D6" s="1" t="s">
+      <c r="D6" s="6" t="s">
         <v>144</v>
       </c>
-      <c r="E6" s="10"/>
-      <c r="F6" s="1" t="s">
+      <c r="E6" s="16"/>
+      <c r="F6" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="46"/>
-      <c r="B7" s="54"/>
-      <c r="C7" s="1" t="s">
+      <c r="A7" s="11"/>
+      <c r="B7" s="12"/>
+      <c r="C7" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D7" s="1" t="s">
+      <c r="D7" s="6" t="s">
         <v>159</v>
       </c>
-      <c r="E7" s="10"/>
-      <c r="F7" s="1" t="s">
+      <c r="E7" s="16"/>
+      <c r="F7" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="46"/>
-      <c r="B8" s="54"/>
-      <c r="C8" s="1" t="s">
+      <c r="A8" s="11"/>
+      <c r="B8" s="12"/>
+      <c r="C8" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D8" s="1" t="s">
+      <c r="D8" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E8" s="10"/>
-      <c r="F8" s="1" t="s">
+      <c r="E8" s="16"/>
+      <c r="F8" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="46"/>
-      <c r="B9" s="54"/>
-      <c r="C9" s="1" t="s">
+      <c r="A9" s="11"/>
+      <c r="B9" s="12"/>
+      <c r="C9" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D9" s="1" t="s">
+      <c r="D9" s="6" t="s">
         <v>167</v>
       </c>
-      <c r="E9" s="10"/>
-      <c r="F9" s="1" t="s">
+      <c r="E9" s="16"/>
+      <c r="F9" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="46"/>
-      <c r="B10" s="54"/>
-      <c r="C10" s="1" t="s">
+      <c r="A10" s="11"/>
+      <c r="B10" s="12"/>
+      <c r="C10" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D10" s="1" t="s">
+      <c r="D10" s="6" t="s">
         <v>196</v>
       </c>
-      <c r="E10" s="10"/>
-      <c r="F10" s="1" t="s">
+      <c r="E10" s="16"/>
+      <c r="F10" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="46"/>
-      <c r="B11" s="54"/>
-      <c r="E11" s="9"/>
+      <c r="A11" s="11"/>
+      <c r="B11" s="12"/>
+      <c r="E11" s="15"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="46"/>
-      <c r="B12" s="57" t="s">
+      <c r="A12" s="11"/>
+      <c r="B12" s="17" t="s">
         <v>231</v>
       </c>
-      <c r="C12" s="11" t="s">
+      <c r="C12" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D12" s="18" t="s">
         <v>247</v>
       </c>
-      <c r="E12" s="12"/>
-      <c r="F12" s="11" t="s">
+      <c r="E12" s="19"/>
+      <c r="F12" s="18" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="46"/>
-      <c r="B13" s="54"/>
-      <c r="C13" s="1" t="s">
+      <c r="A13" s="11"/>
+      <c r="B13" s="12"/>
+      <c r="C13" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D13" s="1" t="s">
+      <c r="D13" s="6" t="s">
         <v>298</v>
       </c>
-      <c r="E13" s="7"/>
-      <c r="F13" s="1" t="s">
+      <c r="E13" s="13"/>
+      <c r="F13" s="6" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="46"/>
-      <c r="B14" s="54"/>
-      <c r="C14" s="1" t="s">
+      <c r="A14" s="11"/>
+      <c r="B14" s="12"/>
+      <c r="C14" s="6" t="s">
         <v>140</v>
       </c>
-      <c r="D14" s="1" t="s">
+      <c r="D14" s="6" t="s">
         <v>248</v>
       </c>
-      <c r="E14" s="7"/>
-      <c r="F14" s="7" t="s">
+      <c r="E14" s="13"/>
+      <c r="F14" s="13" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="46"/>
-      <c r="B15" s="54"/>
-      <c r="C15" s="1" t="s">
+      <c r="A15" s="11"/>
+      <c r="B15" s="12"/>
+      <c r="C15" s="6" t="s">
         <v>256</v>
       </c>
-      <c r="D15" s="1" t="s">
+      <c r="D15" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E15" s="9"/>
-      <c r="F15" s="1" t="s">
+      <c r="E15" s="15"/>
+      <c r="F15" s="6" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="46"/>
-      <c r="B16" s="54"/>
-      <c r="C16" s="1" t="s">
+      <c r="A16" s="11"/>
+      <c r="B16" s="12"/>
+      <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D16" s="1" t="s">
+      <c r="D16" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E16" s="7"/>
-      <c r="F16" s="1" t="s">
+      <c r="E16" s="13"/>
+      <c r="F16" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="46"/>
-      <c r="B17" s="54"/>
-      <c r="C17" s="1" t="s">
+      <c r="A17" s="11"/>
+      <c r="B17" s="12"/>
+      <c r="C17" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D17" s="1" t="s">
+      <c r="D17" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E17" s="7"/>
-      <c r="F17" s="1" t="s">
+      <c r="E17" s="13"/>
+      <c r="F17" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="46"/>
-      <c r="B18" s="54"/>
-      <c r="C18" s="1" t="s">
+      <c r="A18" s="11"/>
+      <c r="B18" s="12"/>
+      <c r="C18" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D18" s="1" t="s">
+      <c r="D18" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E18" s="10"/>
-      <c r="F18" s="1" t="s">
+      <c r="E18" s="16"/>
+      <c r="F18" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="46"/>
-      <c r="B19" s="54"/>
-      <c r="C19" s="1" t="s">
+      <c r="A19" s="11"/>
+      <c r="B19" s="12"/>
+      <c r="C19" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D19" s="1" t="s">
+      <c r="D19" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E19" s="10"/>
-      <c r="F19" s="1" t="s">
+      <c r="E19" s="16"/>
+      <c r="F19" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="46"/>
-      <c r="B20" s="54"/>
-      <c r="C20" s="1" t="s">
+      <c r="A20" s="11"/>
+      <c r="B20" s="12"/>
+      <c r="C20" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D20" s="1" t="s">
+      <c r="D20" s="6" t="s">
         <v>253</v>
       </c>
-      <c r="E20" s="10"/>
-      <c r="F20" s="1" t="s">
+      <c r="E20" s="16"/>
+      <c r="F20" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="46"/>
-      <c r="B21" s="54"/>
-      <c r="C21" s="1" t="s">
+      <c r="A21" s="11"/>
+      <c r="B21" s="12"/>
+      <c r="C21" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D21" s="1" t="s">
+      <c r="D21" s="6" t="s">
         <v>254</v>
       </c>
-      <c r="E21" s="10"/>
-      <c r="F21" s="1" t="s">
+      <c r="E21" s="16"/>
+      <c r="F21" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="46"/>
-      <c r="B22" s="58"/>
-      <c r="C22" s="13"/>
-      <c r="D22" s="13"/>
-      <c r="E22" s="14"/>
-      <c r="F22" s="13"/>
+      <c r="A22" s="11"/>
+      <c r="B22" s="20"/>
+      <c r="C22" s="21"/>
+      <c r="D22" s="21"/>
+      <c r="E22" s="22"/>
+      <c r="F22" s="21"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="46"/>
-      <c r="B23" s="57" t="s">
+      <c r="A23" s="11"/>
+      <c r="B23" s="17" t="s">
         <v>273</v>
       </c>
-      <c r="C23" s="1" t="s">
+      <c r="C23" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D23" s="1" t="s">
+      <c r="D23" s="6" t="s">
         <v>285</v>
       </c>
-      <c r="E23" s="7"/>
-      <c r="F23" s="1" t="s">
+      <c r="E23" s="13"/>
+      <c r="F23" s="6" t="s">
         <v>293</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="46"/>
-      <c r="B24" s="54"/>
-      <c r="C24" s="1" t="s">
+      <c r="A24" s="11"/>
+      <c r="B24" s="12"/>
+      <c r="C24" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D24" s="1" t="s">
+      <c r="D24" s="6" t="s">
         <v>286</v>
       </c>
-      <c r="E24" s="7"/>
-      <c r="F24" s="1" t="s">
+      <c r="E24" s="13"/>
+      <c r="F24" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="46"/>
-      <c r="B25" s="54"/>
-      <c r="C25" s="1" t="s">
+      <c r="A25" s="11"/>
+      <c r="B25" s="12"/>
+      <c r="C25" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D25" s="1" t="s">
+      <c r="D25" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="E25" s="9"/>
-      <c r="F25" s="1" t="s">
+      <c r="E25" s="15"/>
+      <c r="F25" s="6" t="s">
         <v>297</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="46"/>
-      <c r="B26" s="54"/>
-      <c r="C26" s="1" t="s">
+      <c r="A26" s="11"/>
+      <c r="B26" s="12"/>
+      <c r="C26" s="6" t="s">
         <v>295</v>
       </c>
-      <c r="D26" s="1" t="s">
+      <c r="D26" s="6" t="s">
         <v>296</v>
       </c>
-      <c r="E26" s="10"/>
-      <c r="F26" s="1" t="s">
+      <c r="E26" s="16"/>
+      <c r="F26" s="6" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="46"/>
-      <c r="B27" s="54"/>
-      <c r="C27" s="1" t="s">
+      <c r="A27" s="11"/>
+      <c r="B27" s="12"/>
+      <c r="C27" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D27" s="1" t="s">
+      <c r="D27" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E27" s="10"/>
-      <c r="F27" s="1" t="s">
+      <c r="E27" s="16"/>
+      <c r="F27" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="46"/>
-      <c r="B28" s="54"/>
-      <c r="C28" s="1" t="s">
+      <c r="A28" s="11"/>
+      <c r="B28" s="12"/>
+      <c r="C28" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D28" s="1" t="s">
+      <c r="D28" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E28" s="10"/>
-      <c r="F28" s="1" t="s">
+      <c r="E28" s="16"/>
+      <c r="F28" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="46"/>
-      <c r="B29" s="54"/>
-      <c r="C29" s="1" t="s">
+      <c r="A29" s="11"/>
+      <c r="B29" s="12"/>
+      <c r="C29" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D29" s="1" t="s">
+      <c r="D29" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="E29" s="10"/>
-      <c r="F29" s="1" t="s">
+      <c r="E29" s="16"/>
+      <c r="F29" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="46"/>
-      <c r="B30" s="54"/>
-      <c r="C30" s="1" t="s">
+      <c r="A30" s="11"/>
+      <c r="B30" s="12"/>
+      <c r="C30" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D30" s="1" t="s">
+      <c r="D30" s="6" t="s">
         <v>291</v>
       </c>
-      <c r="E30" s="9"/>
-      <c r="F30" s="1" t="s">
+      <c r="E30" s="15"/>
+      <c r="F30" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="46"/>
-      <c r="B31" s="54"/>
-      <c r="C31" s="1" t="s">
+      <c r="A31" s="11"/>
+      <c r="B31" s="12"/>
+      <c r="C31" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D31" s="1" t="s">
+      <c r="D31" s="6" t="s">
         <v>292</v>
       </c>
-      <c r="E31" s="9"/>
-      <c r="F31" s="1" t="s">
+      <c r="E31" s="15"/>
+      <c r="F31" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="46"/>
-      <c r="B32" s="58"/>
-      <c r="C32" s="13"/>
-      <c r="D32" s="13"/>
-      <c r="E32" s="14"/>
-      <c r="F32" s="13"/>
+      <c r="A32" s="11"/>
+      <c r="B32" s="20"/>
+      <c r="C32" s="21"/>
+      <c r="D32" s="21"/>
+      <c r="E32" s="22"/>
+      <c r="F32" s="21"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="46"/>
-      <c r="B33" s="59" t="s">
+      <c r="A33" s="11"/>
+      <c r="B33" s="23" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="1" t="s">
+      <c r="C33" s="6" t="s">
         <v>97</v>
       </c>
-      <c r="D33" s="1" t="s">
+      <c r="D33" s="6" t="s">
         <v>361</v>
       </c>
-      <c r="E33" s="7"/>
-      <c r="F33" s="1" t="s">
+      <c r="E33" s="13"/>
+      <c r="F33" s="6" t="s">
         <v>105</v>
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="46"/>
-      <c r="B34" s="59"/>
-      <c r="C34" s="1" t="s">
+      <c r="A34" s="11"/>
+      <c r="B34" s="23"/>
+      <c r="C34" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D34" s="1" t="s">
+      <c r="D34" s="6" t="s">
         <v>362</v>
       </c>
-      <c r="E34" s="7"/>
-      <c r="F34" s="1" t="s">
+      <c r="E34" s="13"/>
+      <c r="F34" s="6" t="s">
         <v>187</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="46"/>
-      <c r="B35" s="59"/>
-      <c r="C35" s="1" t="s">
+      <c r="A35" s="11"/>
+      <c r="B35" s="23"/>
+      <c r="C35" s="6" t="s">
         <v>84</v>
       </c>
-      <c r="D35" s="1" t="s">
+      <c r="D35" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="E35" s="9"/>
-      <c r="F35" s="1" t="s">
+      <c r="E35" s="15"/>
+      <c r="F35" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="46"/>
-      <c r="B36" s="59"/>
-      <c r="C36" s="1" t="s">
+      <c r="A36" s="11"/>
+      <c r="B36" s="23"/>
+      <c r="C36" s="6" t="s">
         <v>283</v>
       </c>
-      <c r="D36" s="1" t="s">
+      <c r="D36" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E36" s="9"/>
-      <c r="F36" s="1" t="s">
+      <c r="E36" s="15"/>
+      <c r="F36" s="6" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="46"/>
-      <c r="B37" s="59"/>
-      <c r="C37" s="1" t="s">
+      <c r="A37" s="11"/>
+      <c r="B37" s="23"/>
+      <c r="C37" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D37" s="1" t="s">
+      <c r="D37" s="6" t="s">
         <v>375</v>
       </c>
-      <c r="E37" s="9"/>
-      <c r="F37" s="1" t="s">
+      <c r="E37" s="15"/>
+      <c r="F37" s="6" t="s">
         <v>376</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="46"/>
-      <c r="B38" s="59"/>
-      <c r="C38" s="1" t="s">
+      <c r="A38" s="11"/>
+      <c r="B38" s="23"/>
+      <c r="C38" s="6" t="s">
         <v>260</v>
       </c>
-      <c r="D38" s="1" t="s">
+      <c r="D38" s="6" t="s">
         <v>364</v>
       </c>
-      <c r="E38" s="10"/>
-      <c r="F38" s="1" t="s">
+      <c r="E38" s="16"/>
+      <c r="F38" s="6" t="s">
         <v>259</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="46"/>
-      <c r="B39" s="59"/>
-      <c r="C39" s="1" t="s">
+      <c r="A39" s="11"/>
+      <c r="B39" s="23"/>
+      <c r="C39" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D39" s="1" t="s">
+      <c r="D39" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E39" s="10"/>
-      <c r="F39" s="1" t="s">
+      <c r="E39" s="16"/>
+      <c r="F39" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="46"/>
-      <c r="B40" s="59"/>
-      <c r="C40" s="1" t="s">
+      <c r="A40" s="11"/>
+      <c r="B40" s="23"/>
+      <c r="C40" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D40" s="1" t="s">
+      <c r="D40" s="6" t="s">
         <v>369</v>
       </c>
-      <c r="E40" s="10"/>
-      <c r="F40" s="1" t="s">
+      <c r="E40" s="16"/>
+      <c r="F40" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="46"/>
-      <c r="B41" s="59"/>
-      <c r="C41" s="1" t="s">
+      <c r="A41" s="11"/>
+      <c r="B41" s="23"/>
+      <c r="C41" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D41" s="1" t="s">
+      <c r="D41" s="6" t="s">
         <v>381</v>
       </c>
-      <c r="E41" s="10"/>
-      <c r="F41" s="1" t="s">
+      <c r="E41" s="16"/>
+      <c r="F41" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="46"/>
-      <c r="B42" s="59"/>
-      <c r="C42" s="1" t="s">
+      <c r="A42" s="11"/>
+      <c r="B42" s="23"/>
+      <c r="C42" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D42" s="1" t="s">
+      <c r="D42" s="6" t="s">
         <v>367</v>
       </c>
-      <c r="E42" s="10"/>
-      <c r="F42" s="1" t="s">
+      <c r="E42" s="16"/>
+      <c r="F42" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="46"/>
-      <c r="B43" s="59"/>
-      <c r="C43" s="1" t="s">
+      <c r="A43" s="11"/>
+      <c r="B43" s="23"/>
+      <c r="C43" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D43" s="1" t="s">
+      <c r="D43" s="6" t="s">
         <v>368</v>
       </c>
-      <c r="E43" s="9"/>
-      <c r="F43" s="1" t="s">
+      <c r="E43" s="15"/>
+      <c r="F43" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="46"/>
-      <c r="B44" s="59"/>
-      <c r="C44" s="1" t="s">
+      <c r="A44" s="11"/>
+      <c r="B44" s="23"/>
+      <c r="C44" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D44" s="1" t="s">
+      <c r="D44" s="6" t="s">
         <v>370</v>
       </c>
-      <c r="E44" s="9"/>
-      <c r="F44" s="1" t="s">
+      <c r="E44" s="15"/>
+      <c r="F44" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="46"/>
-      <c r="B45" s="59"/>
-      <c r="E45" s="9"/>
+      <c r="A45" s="11"/>
+      <c r="B45" s="23"/>
+      <c r="E45" s="15"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="45" t="s">
+      <c r="A46" s="7" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="49" t="s">
+      <c r="B46" s="24" t="s">
         <v>3</v>
       </c>
-      <c r="C46" s="2" t="s">
+      <c r="C46" s="9" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="2" t="s">
+      <c r="D46" s="9" t="s">
         <v>104</v>
       </c>
-      <c r="E46" s="15"/>
-      <c r="F46" s="2" t="s">
+      <c r="E46" s="25"/>
+      <c r="F46" s="9" t="s">
         <v>188</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="46"/>
-      <c r="B47" s="50"/>
-      <c r="C47" s="1" t="s">
+      <c r="A47" s="11"/>
+      <c r="B47" s="23"/>
+      <c r="C47" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D47" s="1" t="s">
+      <c r="D47" s="6" t="s">
         <v>111</v>
       </c>
-      <c r="E47" s="9"/>
-      <c r="F47" s="1" t="s">
+      <c r="E47" s="15"/>
+      <c r="F47" s="6" t="s">
         <v>30</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="46"/>
-      <c r="B48" s="50"/>
-      <c r="C48" s="1" t="s">
+      <c r="A48" s="11"/>
+      <c r="B48" s="23"/>
+      <c r="C48" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D48" s="1" t="s">
+      <c r="D48" s="6" t="s">
         <v>134</v>
       </c>
-      <c r="E48" s="10"/>
-      <c r="F48" s="1" t="s">
+      <c r="E48" s="16"/>
+      <c r="F48" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="46"/>
-      <c r="B49" s="50"/>
-      <c r="C49" s="1" t="s">
+      <c r="A49" s="11"/>
+      <c r="B49" s="23"/>
+      <c r="C49" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D49" s="1" t="s">
+      <c r="D49" s="6" t="s">
         <v>135</v>
       </c>
-      <c r="E49" s="9"/>
-      <c r="F49" s="1" t="s">
+      <c r="E49" s="15"/>
+      <c r="F49" s="6" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="46"/>
-      <c r="B50" s="50"/>
-      <c r="C50" s="1" t="s">
+      <c r="A50" s="11"/>
+      <c r="B50" s="23"/>
+      <c r="C50" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D50" s="1" t="s">
+      <c r="D50" s="6" t="s">
         <v>147</v>
       </c>
-      <c r="E50" s="9"/>
-      <c r="F50" s="1" t="s">
+      <c r="E50" s="15"/>
+      <c r="F50" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="46"/>
-      <c r="B51" s="50"/>
-      <c r="C51" s="1" t="s">
+      <c r="A51" s="11"/>
+      <c r="B51" s="23"/>
+      <c r="C51" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D51" s="1" t="s">
+      <c r="D51" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E51" s="9"/>
-      <c r="F51" s="1" t="s">
+      <c r="E51" s="15"/>
+      <c r="F51" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="46"/>
-      <c r="B52" s="50"/>
-      <c r="C52" s="1" t="s">
+      <c r="A52" s="11"/>
+      <c r="B52" s="23"/>
+      <c r="C52" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D52" s="1" t="s">
+      <c r="D52" s="6" t="s">
         <v>201</v>
       </c>
-      <c r="E52" s="9"/>
-      <c r="F52" s="1" t="s">
+      <c r="E52" s="15"/>
+      <c r="F52" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="46"/>
-      <c r="B53" s="50"/>
-      <c r="C53" s="1" t="s">
+      <c r="A53" s="11"/>
+      <c r="B53" s="23"/>
+      <c r="C53" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D53" s="1" t="s">
+      <c r="D53" s="6" t="s">
         <v>172</v>
       </c>
-      <c r="E53" s="9"/>
-      <c r="F53" s="1" t="s">
+      <c r="E53" s="15"/>
+      <c r="F53" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="46"/>
-      <c r="B54" s="50"/>
-      <c r="C54" s="1" t="s">
+      <c r="A54" s="11"/>
+      <c r="B54" s="23"/>
+      <c r="C54" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D54" s="1" t="s">
+      <c r="D54" s="6" t="s">
         <v>195</v>
       </c>
-      <c r="E54" s="9"/>
-      <c r="F54" s="1" t="s">
+      <c r="E54" s="15"/>
+      <c r="F54" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="46"/>
-      <c r="B55" s="51"/>
-      <c r="C55" s="13"/>
-      <c r="D55" s="13"/>
-      <c r="E55" s="14"/>
-      <c r="F55" s="13"/>
+      <c r="A55" s="11"/>
+      <c r="B55" s="26"/>
+      <c r="C55" s="21"/>
+      <c r="D55" s="21"/>
+      <c r="E55" s="22"/>
+      <c r="F55" s="21"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="46"/>
-      <c r="B56" s="50" t="s">
+      <c r="A56" s="11"/>
+      <c r="B56" s="23" t="s">
         <v>317</v>
       </c>
-      <c r="C56" s="1" t="s">
+      <c r="C56" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D56" s="1" t="s">
+      <c r="D56" s="6" t="s">
         <v>327</v>
       </c>
-      <c r="E56" s="7"/>
-      <c r="F56" s="1" t="s">
+      <c r="E56" s="13"/>
+      <c r="F56" s="6" t="s">
         <v>340</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="46"/>
-      <c r="B57" s="50"/>
-      <c r="C57" s="1" t="s">
+      <c r="A57" s="11"/>
+      <c r="B57" s="23"/>
+      <c r="C57" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D57" s="1" t="s">
+      <c r="D57" s="6" t="s">
         <v>328</v>
       </c>
-      <c r="E57" s="9"/>
-      <c r="F57" s="1" t="s">
+      <c r="E57" s="15"/>
+      <c r="F57" s="6" t="s">
         <v>341</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="46"/>
-      <c r="B58" s="50"/>
-      <c r="C58" s="1" t="s">
+      <c r="A58" s="11"/>
+      <c r="B58" s="23"/>
+      <c r="C58" s="6" t="s">
         <v>136</v>
       </c>
-      <c r="D58" s="1" t="s">
+      <c r="D58" s="6" t="s">
         <v>329</v>
       </c>
-      <c r="E58" s="10"/>
-      <c r="F58" s="1" t="s">
+      <c r="E58" s="16"/>
+      <c r="F58" s="6" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="46"/>
-      <c r="B59" s="50"/>
-      <c r="C59" s="1" t="s">
+      <c r="A59" s="11"/>
+      <c r="B59" s="23"/>
+      <c r="C59" s="6" t="s">
         <v>137</v>
       </c>
-      <c r="D59" s="1" t="s">
+      <c r="D59" s="6" t="s">
         <v>330</v>
       </c>
-      <c r="E59" s="9"/>
-      <c r="F59" s="1" t="s">
+      <c r="E59" s="15"/>
+      <c r="F59" s="6" t="s">
         <v>387</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="46"/>
-      <c r="B60" s="50"/>
-      <c r="C60" s="1" t="s">
+      <c r="A60" s="11"/>
+      <c r="B60" s="23"/>
+      <c r="C60" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D60" s="1" t="s">
+      <c r="D60" s="6" t="s">
         <v>331</v>
       </c>
-      <c r="E60" s="9"/>
-      <c r="F60" s="1" t="s">
+      <c r="E60" s="15"/>
+      <c r="F60" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="46"/>
-      <c r="B61" s="50"/>
-      <c r="C61" s="1" t="s">
+      <c r="A61" s="11"/>
+      <c r="B61" s="23"/>
+      <c r="C61" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D61" s="1" t="s">
+      <c r="D61" s="6" t="s">
         <v>332</v>
       </c>
-      <c r="E61" s="9"/>
-      <c r="F61" s="1" t="s">
+      <c r="E61" s="15"/>
+      <c r="F61" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="46"/>
-      <c r="B62" s="50"/>
-      <c r="C62" s="1" t="s">
+      <c r="A62" s="11"/>
+      <c r="B62" s="23"/>
+      <c r="C62" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D62" s="1" t="s">
+      <c r="D62" s="6" t="s">
         <v>333</v>
       </c>
-      <c r="E62" s="9"/>
-      <c r="F62" s="1" t="s">
+      <c r="E62" s="15"/>
+      <c r="F62" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="46"/>
-      <c r="B63" s="50"/>
-      <c r="C63" s="1" t="s">
+      <c r="A63" s="11"/>
+      <c r="B63" s="23"/>
+      <c r="C63" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D63" s="1" t="s">
+      <c r="D63" s="6" t="s">
         <v>334</v>
       </c>
-      <c r="E63" s="9"/>
-      <c r="F63" s="1" t="s">
+      <c r="E63" s="15"/>
+      <c r="F63" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="46"/>
-      <c r="B64" s="50"/>
-      <c r="C64" s="1" t="s">
+      <c r="A64" s="11"/>
+      <c r="B64" s="23"/>
+      <c r="C64" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D64" s="1" t="s">
+      <c r="D64" s="6" t="s">
         <v>335</v>
       </c>
-      <c r="E64" s="9"/>
-      <c r="F64" s="1" t="s">
+      <c r="E64" s="15"/>
+      <c r="F64" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="46"/>
-      <c r="B65" s="51"/>
-      <c r="E65" s="9"/>
+      <c r="A65" s="11"/>
+      <c r="B65" s="26"/>
+      <c r="E65" s="15"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="46"/>
-      <c r="B66" s="52" t="s">
+      <c r="A66" s="11"/>
+      <c r="B66" s="27" t="s">
         <v>6</v>
       </c>
-      <c r="C66" s="11" t="s">
+      <c r="C66" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D66" s="11" t="s">
+      <c r="D66" s="18" t="s">
         <v>101</v>
       </c>
-      <c r="E66" s="16"/>
-      <c r="F66" s="11" t="s">
+      <c r="E66" s="28"/>
+      <c r="F66" s="18" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="46"/>
-      <c r="B67" s="50"/>
-      <c r="C67" s="1" t="s">
+      <c r="A67" s="11"/>
+      <c r="B67" s="23"/>
+      <c r="C67" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D67" s="1" t="s">
+      <c r="D67" s="6" t="s">
         <v>103</v>
       </c>
-      <c r="E67" s="9"/>
-      <c r="F67" s="1" t="s">
+      <c r="E67" s="15"/>
+      <c r="F67" s="6" t="s">
         <v>106</v>
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="46"/>
-      <c r="B68" s="54"/>
-      <c r="C68" s="1" t="s">
+      <c r="A68" s="11"/>
+      <c r="B68" s="12"/>
+      <c r="C68" s="6" t="s">
         <v>112</v>
       </c>
-      <c r="D68" s="1" t="s">
+      <c r="D68" s="6" t="s">
         <v>113</v>
       </c>
-      <c r="E68" s="7"/>
-      <c r="F68" s="1" t="s">
+      <c r="E68" s="13"/>
+      <c r="F68" s="6" t="s">
         <v>115</v>
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="46"/>
-      <c r="B69" s="54"/>
-      <c r="C69" s="1" t="s">
+      <c r="A69" s="11"/>
+      <c r="B69" s="12"/>
+      <c r="C69" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D69" s="1" t="s">
+      <c r="D69" s="6" t="s">
         <v>186</v>
       </c>
-      <c r="E69" s="7"/>
-      <c r="F69" s="1" t="s">
+      <c r="E69" s="13"/>
+      <c r="F69" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="46"/>
-      <c r="B70" s="54"/>
-      <c r="C70" s="1" t="s">
+      <c r="A70" s="11"/>
+      <c r="B70" s="12"/>
+      <c r="C70" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D70" s="1" t="s">
+      <c r="D70" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E70" s="7"/>
-      <c r="F70" s="1" t="s">
+      <c r="E70" s="13"/>
+      <c r="F70" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="46"/>
-      <c r="B71" s="54"/>
-      <c r="C71" s="1" t="s">
+      <c r="A71" s="11"/>
+      <c r="B71" s="12"/>
+      <c r="C71" s="6" t="s">
         <v>128</v>
       </c>
-      <c r="D71" s="1" t="s">
+      <c r="D71" s="6" t="s">
         <v>126</v>
       </c>
-      <c r="E71" s="9"/>
-      <c r="F71" s="1" t="s">
+      <c r="E71" s="15"/>
+      <c r="F71" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="46"/>
-      <c r="B72" s="54"/>
-      <c r="C72" s="1" t="s">
+      <c r="A72" s="11"/>
+      <c r="B72" s="12"/>
+      <c r="C72" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D72" s="1" t="s">
+      <c r="D72" s="6" t="s">
         <v>146</v>
       </c>
-      <c r="E72" s="7"/>
-      <c r="F72" s="1" t="s">
+      <c r="E72" s="13"/>
+      <c r="F72" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="46"/>
-      <c r="B73" s="54"/>
-      <c r="C73" s="1" t="s">
+      <c r="A73" s="11"/>
+      <c r="B73" s="12"/>
+      <c r="C73" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D73" s="1" t="s">
+      <c r="D73" s="6" t="s">
         <v>158</v>
       </c>
-      <c r="E73" s="9"/>
-      <c r="F73" s="1" t="s">
+      <c r="E73" s="15"/>
+      <c r="F73" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="46"/>
-      <c r="B74" s="54"/>
-      <c r="C74" s="1" t="s">
+      <c r="A74" s="11"/>
+      <c r="B74" s="12"/>
+      <c r="C74" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D74" s="1" t="s">
+      <c r="D74" s="6" t="s">
         <v>202</v>
       </c>
-      <c r="E74" s="9"/>
-      <c r="F74" s="1" t="s">
+      <c r="E74" s="15"/>
+      <c r="F74" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="46"/>
-      <c r="B75" s="54"/>
-      <c r="C75" s="1" t="s">
+      <c r="A75" s="11"/>
+      <c r="B75" s="12"/>
+      <c r="C75" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D75" s="1" t="s">
+      <c r="D75" s="6" t="s">
         <v>171</v>
       </c>
-      <c r="E75" s="9"/>
-      <c r="F75" s="1" t="s">
+      <c r="E75" s="15"/>
+      <c r="F75" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="46"/>
-      <c r="B76" s="54"/>
-      <c r="C76" s="1" t="s">
+      <c r="A76" s="11"/>
+      <c r="B76" s="12"/>
+      <c r="C76" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D76" s="1" t="s">
+      <c r="D76" s="6" t="s">
         <v>194</v>
       </c>
-      <c r="E76" s="9"/>
-      <c r="F76" s="1" t="s">
+      <c r="E76" s="15"/>
+      <c r="F76" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="47"/>
-      <c r="B77" s="55"/>
-      <c r="C77" s="17"/>
-      <c r="D77" s="17"/>
-      <c r="E77" s="18"/>
-      <c r="F77" s="17"/>
+      <c r="A77" s="29"/>
+      <c r="B77" s="30"/>
+      <c r="C77" s="31"/>
+      <c r="D77" s="31"/>
+      <c r="E77" s="32"/>
+      <c r="F77" s="31"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="45" t="s">
+      <c r="A78" s="7" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="56" t="s">
+      <c r="B78" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="2" t="s">
+      <c r="C78" s="9" t="s">
         <v>118</v>
       </c>
-      <c r="D78" s="2" t="s">
+      <c r="D78" s="9" t="s">
         <v>117</v>
       </c>
-      <c r="E78" s="15"/>
-      <c r="F78" s="2" t="s">
+      <c r="E78" s="25"/>
+      <c r="F78" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="46"/>
-      <c r="B79" s="60"/>
-      <c r="C79" s="36" t="s">
+      <c r="A79" s="11"/>
+      <c r="B79" s="33"/>
+      <c r="C79" s="34" t="s">
         <v>154</v>
       </c>
-      <c r="D79" s="36" t="s">
+      <c r="D79" s="34" t="s">
         <v>153</v>
       </c>
-      <c r="E79" s="37"/>
-      <c r="F79" s="36" t="s">
+      <c r="E79" s="35"/>
+      <c r="F79" s="34" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="46"/>
-      <c r="B80" s="58"/>
-      <c r="C80" s="13"/>
-      <c r="D80" s="13"/>
-      <c r="E80" s="38"/>
-      <c r="F80" s="13"/>
+      <c r="A80" s="11"/>
+      <c r="B80" s="20"/>
+      <c r="C80" s="21"/>
+      <c r="D80" s="21"/>
+      <c r="E80" s="36"/>
+      <c r="F80" s="21"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="46"/>
-      <c r="B81" s="60" t="s">
+      <c r="A81" s="11"/>
+      <c r="B81" s="33" t="s">
         <v>343</v>
       </c>
-      <c r="C81" s="36" t="s">
+      <c r="C81" s="34" t="s">
         <v>346</v>
       </c>
-      <c r="D81" s="36" t="s">
+      <c r="D81" s="34" t="s">
         <v>349</v>
       </c>
-      <c r="E81" s="37"/>
-      <c r="F81" s="36" t="s">
+      <c r="E81" s="35"/>
+      <c r="F81" s="34" t="s">
         <v>348</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="46"/>
-      <c r="B82" s="60"/>
-      <c r="C82" s="1" t="s">
+      <c r="A82" s="11"/>
+      <c r="B82" s="33"/>
+      <c r="C82" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="D82" s="1" t="s">
+      <c r="D82" s="6" t="s">
         <v>350</v>
       </c>
-      <c r="E82" s="7"/>
-      <c r="F82" s="1" t="s">
+      <c r="E82" s="13"/>
+      <c r="F82" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="46"/>
-      <c r="B83" s="60"/>
-      <c r="E83" s="7"/>
+      <c r="A83" s="11"/>
+      <c r="B83" s="33"/>
+      <c r="E83" s="13"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="46"/>
-      <c r="B84" s="52" t="s">
+      <c r="A84" s="11"/>
+      <c r="B84" s="27" t="s">
         <v>4</v>
       </c>
-      <c r="C84" s="11" t="s">
+      <c r="C84" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D84" s="11" t="s">
+      <c r="D84" s="18" t="s">
         <v>100</v>
       </c>
-      <c r="E84" s="16"/>
-      <c r="F84" s="11" t="s">
+      <c r="E84" s="28"/>
+      <c r="F84" s="18" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="46"/>
-      <c r="B85" s="50"/>
-      <c r="C85" s="1" t="s">
+      <c r="A85" s="11"/>
+      <c r="B85" s="23"/>
+      <c r="C85" s="6" t="s">
         <v>108</v>
       </c>
-      <c r="D85" s="1" t="s">
+      <c r="D85" s="6" t="s">
         <v>110</v>
       </c>
-      <c r="E85" s="19"/>
-      <c r="F85" s="1" t="s">
+      <c r="E85" s="1"/>
+      <c r="F85" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="46"/>
-      <c r="B86" s="50"/>
-      <c r="C86" s="1" t="s">
+      <c r="A86" s="11"/>
+      <c r="B86" s="23"/>
+      <c r="C86" s="6" t="s">
         <v>123</v>
       </c>
-      <c r="D86" s="1" t="s">
+      <c r="D86" s="6" t="s">
         <v>122</v>
       </c>
-      <c r="E86" s="19"/>
-      <c r="F86" s="1" t="s">
+      <c r="E86" s="1"/>
+      <c r="F86" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="46"/>
-      <c r="B87" s="50"/>
-      <c r="C87" s="1" t="s">
+      <c r="A87" s="11"/>
+      <c r="B87" s="23"/>
+      <c r="C87" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D87" s="1" t="s">
+      <c r="D87" s="6" t="s">
         <v>145</v>
       </c>
-      <c r="E87" s="7"/>
-      <c r="F87" s="1" t="s">
+      <c r="E87" s="13"/>
+      <c r="F87" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="46"/>
-      <c r="B88" s="50"/>
-      <c r="C88" s="1" t="s">
+      <c r="A88" s="11"/>
+      <c r="B88" s="23"/>
+      <c r="C88" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D88" s="1" t="s">
+      <c r="D88" s="6" t="s">
         <v>157</v>
       </c>
-      <c r="E88" s="10"/>
-      <c r="F88" s="1" t="s">
+      <c r="E88" s="16"/>
+      <c r="F88" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="46"/>
-      <c r="B89" s="50"/>
-      <c r="C89" s="1" t="s">
+      <c r="A89" s="11"/>
+      <c r="B89" s="23"/>
+      <c r="C89" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D89" s="1" t="s">
+      <c r="D89" s="6" t="s">
         <v>163</v>
       </c>
-      <c r="E89" s="7"/>
-      <c r="F89" s="1" t="s">
+      <c r="E89" s="13"/>
+      <c r="F89" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="46"/>
-      <c r="B90" s="50"/>
-      <c r="C90" s="1" t="s">
+      <c r="A90" s="11"/>
+      <c r="B90" s="23"/>
+      <c r="C90" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D90" s="1" t="s">
+      <c r="D90" s="6" t="s">
         <v>200</v>
       </c>
-      <c r="E90" s="7"/>
-      <c r="F90" s="1" t="s">
+      <c r="E90" s="13"/>
+      <c r="F90" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="46"/>
-      <c r="B91" s="50"/>
-      <c r="C91" s="1" t="s">
+      <c r="A91" s="11"/>
+      <c r="B91" s="23"/>
+      <c r="C91" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D91" s="1" t="s">
+      <c r="D91" s="6" t="s">
         <v>170</v>
       </c>
-      <c r="E91" s="9"/>
-      <c r="F91" s="1" t="s">
+      <c r="E91" s="15"/>
+      <c r="F91" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="46"/>
-      <c r="B92" s="50"/>
-      <c r="C92" s="1" t="s">
+      <c r="A92" s="11"/>
+      <c r="B92" s="23"/>
+      <c r="C92" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D92" s="1" t="s">
+      <c r="D92" s="6" t="s">
         <v>192</v>
       </c>
-      <c r="E92" s="9"/>
-      <c r="F92" s="1" t="s">
+      <c r="E92" s="15"/>
+      <c r="F92" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="46"/>
-      <c r="B93" s="51"/>
+      <c r="A93" s="11"/>
+      <c r="B93" s="26"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="46"/>
-      <c r="B94" s="52" t="s">
+      <c r="A94" s="11"/>
+      <c r="B94" s="27" t="s">
         <v>5</v>
       </c>
-      <c r="C94" s="11" t="s">
+      <c r="C94" s="18" t="s">
         <v>97</v>
       </c>
-      <c r="D94" s="11" t="s">
+      <c r="D94" s="18" t="s">
         <v>102</v>
       </c>
-      <c r="E94" s="16"/>
-      <c r="F94" s="11" t="s">
+      <c r="E94" s="28"/>
+      <c r="F94" s="18" t="s">
         <v>99</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="46"/>
-      <c r="B95" s="50"/>
-      <c r="C95" s="1" t="s">
+      <c r="A95" s="11"/>
+      <c r="B95" s="23"/>
+      <c r="C95" s="6" t="s">
         <v>109</v>
       </c>
-      <c r="D95" s="1" t="s">
+      <c r="D95" s="6" t="s">
         <v>107</v>
       </c>
-      <c r="E95" s="19"/>
-      <c r="F95" s="1" t="s">
+      <c r="E95" s="1"/>
+      <c r="F95" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="46"/>
-      <c r="B96" s="50"/>
-      <c r="C96" s="1" t="s">
+      <c r="A96" s="11"/>
+      <c r="B96" s="23"/>
+      <c r="C96" s="6" t="s">
         <v>121</v>
       </c>
-      <c r="D96" s="1" t="s">
+      <c r="D96" s="6" t="s">
         <v>120</v>
       </c>
-      <c r="E96" s="19"/>
-      <c r="F96" s="1" t="s">
+      <c r="E96" s="1"/>
+      <c r="F96" s="6" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="46"/>
-      <c r="B97" s="50"/>
-      <c r="C97" s="1" t="s">
+      <c r="A97" s="11"/>
+      <c r="B97" s="23"/>
+      <c r="C97" s="6" t="s">
         <v>142</v>
       </c>
-      <c r="D97" s="1" t="s">
+      <c r="D97" s="6" t="s">
         <v>143</v>
       </c>
-      <c r="E97" s="19"/>
-      <c r="F97" s="1" t="s">
+      <c r="E97" s="1"/>
+      <c r="F97" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="46"/>
-      <c r="B98" s="50"/>
-      <c r="C98" s="1" t="s">
+      <c r="A98" s="11"/>
+      <c r="B98" s="23"/>
+      <c r="C98" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D98" s="1" t="s">
+      <c r="D98" s="6" t="s">
         <v>155</v>
       </c>
-      <c r="E98" s="10"/>
-      <c r="F98" s="1" t="s">
+      <c r="E98" s="16"/>
+      <c r="F98" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="46"/>
-      <c r="B99" s="50"/>
-      <c r="C99" s="1" t="s">
+      <c r="A99" s="11"/>
+      <c r="B99" s="23"/>
+      <c r="C99" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D99" s="1" t="s">
+      <c r="D99" s="6" t="s">
         <v>161</v>
       </c>
-      <c r="E99" s="20"/>
-      <c r="F99" s="1" t="s">
+      <c r="E99" s="37"/>
+      <c r="F99" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="46"/>
-      <c r="B100" s="50"/>
-      <c r="C100" s="1" t="s">
+      <c r="A100" s="11"/>
+      <c r="B100" s="23"/>
+      <c r="C100" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D100" s="1" t="s">
+      <c r="D100" s="6" t="s">
         <v>199</v>
       </c>
-      <c r="E100" s="20"/>
-      <c r="F100" s="1" t="s">
+      <c r="E100" s="37"/>
+      <c r="F100" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="46"/>
-      <c r="B101" s="50"/>
-      <c r="C101" s="1" t="s">
+      <c r="A101" s="11"/>
+      <c r="B101" s="23"/>
+      <c r="C101" s="6" t="s">
         <v>168</v>
       </c>
-      <c r="D101" s="1" t="s">
+      <c r="D101" s="6" t="s">
         <v>169</v>
       </c>
-      <c r="E101" s="9"/>
-      <c r="F101" s="1" t="s">
+      <c r="E101" s="15"/>
+      <c r="F101" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="46"/>
-      <c r="B102" s="50"/>
-      <c r="C102" s="1" t="s">
+      <c r="A102" s="11"/>
+      <c r="B102" s="23"/>
+      <c r="C102" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D102" s="1" t="s">
+      <c r="D102" s="6" t="s">
         <v>191</v>
       </c>
-      <c r="E102" s="9"/>
-      <c r="F102" s="1" t="s">
+      <c r="E102" s="15"/>
+      <c r="F102" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="47"/>
-      <c r="B103" s="53"/>
+      <c r="A103" s="29"/>
+      <c r="B103" s="38"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="45" t="s">
+      <c r="A104" s="7" t="s">
         <v>76</v>
       </c>
-      <c r="B104" s="56" t="s">
+      <c r="B104" s="8" t="s">
         <v>73</v>
       </c>
-      <c r="C104" s="2" t="s">
+      <c r="C104" s="9" t="s">
         <v>130</v>
       </c>
-      <c r="D104" s="2" t="s">
+      <c r="D104" s="9" t="s">
         <v>129</v>
       </c>
-      <c r="E104" s="6"/>
-      <c r="F104" s="2" t="s">
+      <c r="E104" s="10"/>
+      <c r="F104" s="9" t="s">
         <v>119</v>
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="46"/>
-      <c r="B105" s="54"/>
-      <c r="C105" s="1" t="s">
+      <c r="A105" s="11"/>
+      <c r="B105" s="12"/>
+      <c r="C105" s="6" t="s">
         <v>230</v>
       </c>
-      <c r="D105" s="1" t="s">
+      <c r="D105" s="6" t="s">
         <v>229</v>
       </c>
-      <c r="E105" s="9"/>
-      <c r="F105" s="1" t="s">
+      <c r="E105" s="15"/>
+      <c r="F105" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="46"/>
-      <c r="B106" s="54"/>
-      <c r="C106" s="1" t="s">
+      <c r="A106" s="11"/>
+      <c r="B106" s="12"/>
+      <c r="C106" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D106" s="1" t="s">
+      <c r="D106" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E106" s="9"/>
-      <c r="F106" s="1" t="s">
+      <c r="E106" s="15"/>
+      <c r="F106" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="46"/>
-      <c r="B107" s="58"/>
-      <c r="C107" s="13"/>
-      <c r="D107" s="13"/>
-      <c r="E107" s="14"/>
-      <c r="F107" s="13"/>
+      <c r="A107" s="11"/>
+      <c r="B107" s="20"/>
+      <c r="C107" s="21"/>
+      <c r="D107" s="21"/>
+      <c r="E107" s="22"/>
+      <c r="F107" s="21"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="46"/>
-      <c r="B108" s="57" t="s">
+      <c r="A108" s="11"/>
+      <c r="B108" s="17" t="s">
         <v>303</v>
       </c>
-      <c r="C108" s="1" t="s">
+      <c r="C108" s="6" t="s">
         <v>304</v>
       </c>
-      <c r="D108" s="1" t="s">
+      <c r="D108" s="6" t="s">
         <v>305</v>
       </c>
-      <c r="E108" s="9"/>
-      <c r="F108" s="1" t="s">
+      <c r="E108" s="15"/>
+      <c r="F108" s="6" t="s">
         <v>294</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="46"/>
-      <c r="B109" s="54"/>
-      <c r="C109" s="1" t="s">
+      <c r="A109" s="11"/>
+      <c r="B109" s="12"/>
+      <c r="C109" s="6" t="s">
         <v>308</v>
       </c>
-      <c r="D109" s="1" t="s">
+      <c r="D109" s="6" t="s">
         <v>306</v>
       </c>
-      <c r="E109" s="9"/>
-      <c r="F109" s="1" t="s">
+      <c r="E109" s="15"/>
+      <c r="F109" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="46"/>
-      <c r="B110" s="54"/>
-      <c r="C110" s="1" t="s">
+      <c r="A110" s="11"/>
+      <c r="B110" s="12"/>
+      <c r="C110" s="6" t="s">
         <v>309</v>
       </c>
-      <c r="D110" s="1" t="s">
+      <c r="D110" s="6" t="s">
         <v>307</v>
       </c>
-      <c r="E110" s="9"/>
-      <c r="F110" s="1" t="s">
+      <c r="E110" s="15"/>
+      <c r="F110" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="46"/>
-      <c r="B111" s="58"/>
-      <c r="E111" s="9"/>
+      <c r="A111" s="11"/>
+      <c r="B111" s="20"/>
+      <c r="E111" s="15"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="46"/>
-      <c r="B112" s="57" t="s">
+      <c r="A112" s="11"/>
+      <c r="B112" s="17" t="s">
         <v>79</v>
       </c>
-      <c r="C112" s="11" t="s">
+      <c r="C112" s="18" t="s">
         <v>132</v>
       </c>
-      <c r="D112" s="11" t="s">
+      <c r="D112" s="18" t="s">
         <v>131</v>
       </c>
-      <c r="E112" s="16"/>
-      <c r="F112" s="11" t="s">
+      <c r="E112" s="28"/>
+      <c r="F112" s="18" t="s">
         <v>133</v>
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="46"/>
-      <c r="B113" s="54"/>
-      <c r="C113" s="1" t="s">
+      <c r="A113" s="11"/>
+      <c r="B113" s="12"/>
+      <c r="C113" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="D113" s="1" t="s">
+      <c r="D113" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E113" s="9"/>
-      <c r="F113" s="1" t="s">
+      <c r="E113" s="15"/>
+      <c r="F113" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="46"/>
-      <c r="B114" s="58"/>
-      <c r="C114" s="13"/>
-      <c r="D114" s="13"/>
-      <c r="E114" s="14"/>
-      <c r="F114" s="13"/>
+      <c r="A114" s="11"/>
+      <c r="B114" s="20"/>
+      <c r="C114" s="21"/>
+      <c r="D114" s="21"/>
+      <c r="E114" s="22"/>
+      <c r="F114" s="21"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="46"/>
-      <c r="B115" s="57" t="s">
+      <c r="A115" s="11"/>
+      <c r="B115" s="17" t="s">
         <v>262</v>
       </c>
-      <c r="C115" s="1" t="s">
+      <c r="C115" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D115" s="1" t="s">
+      <c r="D115" s="6" t="s">
         <v>264</v>
       </c>
-      <c r="E115" s="9"/>
-      <c r="F115" s="1" t="s">
+      <c r="E115" s="15"/>
+      <c r="F115" s="6" t="s">
         <v>258</v>
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="46"/>
-      <c r="B116" s="54"/>
-      <c r="C116" s="1" t="s">
+      <c r="A116" s="11"/>
+      <c r="B116" s="12"/>
+      <c r="C116" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D116" s="1" t="s">
+      <c r="D116" s="6" t="s">
         <v>265</v>
       </c>
-      <c r="E116" s="9"/>
-      <c r="F116" s="1" t="s">
+      <c r="E116" s="15"/>
+      <c r="F116" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="47"/>
-      <c r="B117" s="55"/>
-      <c r="C117" s="17"/>
-      <c r="D117" s="17"/>
-      <c r="E117" s="18"/>
-      <c r="F117" s="17"/>
+      <c r="A117" s="29"/>
+      <c r="B117" s="30"/>
+      <c r="C117" s="31"/>
+      <c r="D117" s="31"/>
+      <c r="E117" s="32"/>
+      <c r="F117" s="31"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="45" t="s">
+      <c r="A118" s="7" t="s">
         <v>164</v>
       </c>
-      <c r="B118" s="56" t="s">
+      <c r="B118" s="8" t="s">
         <v>13</v>
       </c>
-      <c r="C118" s="2" t="s">
+      <c r="C118" s="9" t="s">
         <v>174</v>
       </c>
-      <c r="D118" s="2" t="s">
+      <c r="D118" s="9" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="2"/>
-      <c r="F118" s="2" t="s">
+      <c r="E118" s="9"/>
+      <c r="F118" s="9" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="48"/>
-      <c r="B119" s="54"/>
-      <c r="C119" s="1" t="s">
+      <c r="A119" s="39"/>
+      <c r="B119" s="12"/>
+      <c r="C119" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D119" s="1" t="s">
+      <c r="D119" s="6" t="s">
         <v>176</v>
       </c>
-      <c r="F119" s="1" t="s">
+      <c r="F119" s="6" t="s">
         <v>141</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="48"/>
-      <c r="B120" s="58"/>
-      <c r="C120" s="13"/>
-      <c r="D120" s="13"/>
-      <c r="E120" s="13"/>
-      <c r="F120" s="13"/>
+      <c r="A120" s="39"/>
+      <c r="B120" s="20"/>
+      <c r="C120" s="21"/>
+      <c r="D120" s="21"/>
+      <c r="E120" s="21"/>
+      <c r="F120" s="21"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="48"/>
-      <c r="B121" s="57" t="s">
+      <c r="A121" s="39"/>
+      <c r="B121" s="17" t="s">
         <v>184</v>
       </c>
-      <c r="C121" s="1" t="s">
+      <c r="C121" s="6" t="s">
         <v>166</v>
       </c>
-      <c r="D121" s="1" t="s">
+      <c r="D121" s="6" t="s">
         <v>165</v>
       </c>
-      <c r="F121" s="1" t="s">
+      <c r="F121" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="48"/>
-      <c r="B122" s="54"/>
-      <c r="C122" s="1" t="s">
+      <c r="A122" s="39"/>
+      <c r="B122" s="12"/>
+      <c r="C122" s="6" t="s">
         <v>182</v>
       </c>
-      <c r="D122" s="1" t="s">
+      <c r="D122" s="6" t="s">
         <v>311</v>
       </c>
-      <c r="F122" s="1" t="s">
+      <c r="F122" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="48"/>
-      <c r="B123" s="54"/>
-      <c r="C123" s="1" t="s">
+      <c r="A123" s="39"/>
+      <c r="B123" s="12"/>
+      <c r="C123" s="6" t="s">
         <v>178</v>
       </c>
-      <c r="D123" s="1" t="s">
+      <c r="D123" s="6" t="s">
         <v>177</v>
       </c>
-      <c r="F123" s="1" t="s">
+      <c r="F123" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="48"/>
-      <c r="B124" s="54"/>
-      <c r="C124" s="1" t="s">
+      <c r="A124" s="39"/>
+      <c r="B124" s="12"/>
+      <c r="C124" s="6" t="s">
         <v>180</v>
       </c>
-      <c r="D124" s="1" t="s">
+      <c r="D124" s="6" t="s">
         <v>179</v>
       </c>
-      <c r="F124" s="1" t="s">
+      <c r="F124" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="48"/>
-      <c r="B125" s="54"/>
-      <c r="C125" s="1" t="s">
+      <c r="A125" s="39"/>
+      <c r="B125" s="12"/>
+      <c r="C125" s="6" t="s">
         <v>183</v>
       </c>
-      <c r="D125" s="1" t="s">
+      <c r="D125" s="6" t="s">
         <v>181</v>
       </c>
-      <c r="F125" s="1" t="s">
+      <c r="F125" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="48"/>
-      <c r="B126" s="54"/>
-      <c r="C126" s="1" t="s">
+      <c r="A126" s="39"/>
+      <c r="B126" s="12"/>
+      <c r="C126" s="6" t="s">
         <v>193</v>
       </c>
-      <c r="D126" s="1" t="s">
+      <c r="D126" s="6" t="s">
         <v>189</v>
       </c>
-      <c r="F126" s="1" t="s">
+      <c r="F126" s="6" t="s">
         <v>150</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="48"/>
-      <c r="B127" s="54"/>
+      <c r="A127" s="39"/>
+      <c r="B127" s="12"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="48"/>
-      <c r="B128" s="57" t="s">
+      <c r="A128" s="39"/>
+      <c r="B128" s="17" t="s">
         <v>208</v>
       </c>
-      <c r="C128" s="11" t="s">
+      <c r="C128" s="18" t="s">
         <v>205</v>
       </c>
-      <c r="D128" s="11" t="s">
+      <c r="D128" s="18" t="s">
         <v>209</v>
       </c>
-      <c r="E128" s="11"/>
-      <c r="F128" s="11" t="s">
+      <c r="E128" s="18"/>
+      <c r="F128" s="18" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="48"/>
-      <c r="B129" s="54"/>
-      <c r="C129" s="1" t="s">
+      <c r="A129" s="39"/>
+      <c r="B129" s="12"/>
+      <c r="C129" s="6" t="s">
         <v>206</v>
       </c>
-      <c r="D129" s="1" t="s">
+      <c r="D129" s="6" t="s">
         <v>212</v>
       </c>
-      <c r="F129" s="1" t="s">
+      <c r="F129" s="6" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="48"/>
-      <c r="B130" s="54"/>
-      <c r="C130" s="1" t="s">
+      <c r="A130" s="39"/>
+      <c r="B130" s="12"/>
+      <c r="C130" s="6" t="s">
         <v>217</v>
       </c>
-      <c r="D130" s="1" t="s">
+      <c r="D130" s="6" t="s">
         <v>216</v>
       </c>
-      <c r="F130" s="1" t="s">
+      <c r="F130" s="6" t="s">
         <v>221</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="48"/>
-      <c r="B131" s="54"/>
-      <c r="C131" s="1" t="s">
+      <c r="A131" s="39"/>
+      <c r="B131" s="12"/>
+      <c r="C131" s="6" t="s">
         <v>207</v>
       </c>
-      <c r="D131" s="1" t="s">
+      <c r="D131" s="6" t="s">
         <v>211</v>
       </c>
-      <c r="F131" s="1" t="s">
+      <c r="F131" s="6" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="48"/>
-      <c r="B132" s="54"/>
-      <c r="C132" s="1" t="s">
+      <c r="A132" s="39"/>
+      <c r="B132" s="12"/>
+      <c r="C132" s="6" t="s">
         <v>312</v>
       </c>
-      <c r="D132" s="1" t="s">
+      <c r="D132" s="6" t="s">
         <v>313</v>
       </c>
-      <c r="F132" s="1" t="s">
+      <c r="F132" s="6" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="48"/>
-      <c r="B133" s="54"/>
-      <c r="C133" s="1" t="s">
+      <c r="A133" s="39"/>
+      <c r="B133" s="12"/>
+      <c r="C133" s="6" t="s">
         <v>336</v>
       </c>
-      <c r="D133" s="1" t="s">
+      <c r="D133" s="6" t="s">
         <v>337</v>
       </c>
-      <c r="F133" s="1" t="s">
+      <c r="F133" s="6" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="48"/>
-      <c r="B134" s="54"/>
-      <c r="C134" s="1" t="s">
+      <c r="A134" s="39"/>
+      <c r="B134" s="12"/>
+      <c r="C134" s="6" t="s">
         <v>338</v>
       </c>
-      <c r="D134" s="1" t="s">
+      <c r="D134" s="6" t="s">
         <v>339</v>
       </c>
-      <c r="F134" s="1" t="s">
+      <c r="F134" s="6" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="48"/>
-      <c r="B135" s="54"/>
-      <c r="C135" s="1" t="s">
+      <c r="A135" s="39"/>
+      <c r="B135" s="12"/>
+      <c r="C135" s="6" t="s">
         <v>219</v>
       </c>
-      <c r="D135" s="1" t="s">
+      <c r="D135" s="6" t="s">
         <v>218</v>
       </c>
-      <c r="F135" s="1" t="s">
+      <c r="F135" s="6" t="s">
         <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="48"/>
-      <c r="B136" s="54"/>
-      <c r="C136" s="1" t="s">
+      <c r="A136" s="39"/>
+      <c r="B136" s="12"/>
+      <c r="C136" s="6" t="s">
         <v>223</v>
       </c>
-      <c r="D136" s="1" t="s">
+      <c r="D136" s="6" t="s">
         <v>213</v>
       </c>
-      <c r="F136" s="1" t="s">
+      <c r="F136" s="6" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="48"/>
-      <c r="B137" s="54"/>
-      <c r="C137" s="1" t="s">
+      <c r="A137" s="39"/>
+      <c r="B137" s="12"/>
+      <c r="C137" s="6" t="s">
         <v>204</v>
       </c>
-      <c r="D137" s="1" t="s">
+      <c r="D137" s="6" t="s">
         <v>222</v>
       </c>
-      <c r="F137" s="1" t="s">
+      <c r="F137" s="6" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="48"/>
-      <c r="B138" s="54"/>
-      <c r="C138" s="1" t="s">
+      <c r="A138" s="39"/>
+      <c r="B138" s="12"/>
+      <c r="C138" s="6" t="s">
         <v>266</v>
       </c>
-      <c r="D138" s="1" t="s">
+      <c r="D138" s="6" t="s">
         <v>371</v>
       </c>
-      <c r="F138" s="1" t="s">
+      <c r="F138" s="6" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="48"/>
-      <c r="B139" s="54"/>
-      <c r="C139" s="1" t="s">
+      <c r="A139" s="39"/>
+      <c r="B139" s="12"/>
+      <c r="C139" s="6" t="s">
         <v>268</v>
       </c>
-      <c r="D139" s="1" t="s">
+      <c r="D139" s="6" t="s">
         <v>267</v>
       </c>
-      <c r="F139" s="1" t="s">
+      <c r="F139" s="6" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="48"/>
-      <c r="B140" s="54"/>
+      <c r="A140" s="39"/>
+      <c r="B140" s="12"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="48"/>
-      <c r="B141" s="57" t="s">
+      <c r="A141" s="39"/>
+      <c r="B141" s="17" t="s">
         <v>224</v>
       </c>
-      <c r="C141" s="11" t="s">
+      <c r="C141" s="18" t="s">
         <v>226</v>
       </c>
-      <c r="D141" s="11" t="s">
+      <c r="D141" s="18" t="s">
         <v>225</v>
       </c>
-      <c r="E141" s="11"/>
-      <c r="F141" s="11" t="s">
+      <c r="E141" s="18"/>
+      <c r="F141" s="18" t="s">
         <v>210</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="48"/>
-      <c r="B142" s="60"/>
-      <c r="C142" s="1" t="s">
+      <c r="A142" s="39"/>
+      <c r="B142" s="33"/>
+      <c r="C142" s="6" t="s">
         <v>314</v>
       </c>
-      <c r="D142" s="1" t="s">
+      <c r="D142" s="6" t="s">
         <v>315</v>
       </c>
-      <c r="F142" s="1" t="s">
+      <c r="F142" s="6" t="s">
         <v>316</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="48"/>
-      <c r="B143" s="60"/>
-      <c r="C143" s="1" t="s">
+      <c r="A143" s="39"/>
+      <c r="B143" s="33"/>
+      <c r="C143" s="6" t="s">
         <v>227</v>
       </c>
-      <c r="D143" s="1" t="s">
+      <c r="D143" s="6" t="s">
         <v>228</v>
       </c>
-      <c r="F143" s="1" t="s">
+      <c r="F143" s="6" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="48"/>
-      <c r="B144" s="60"/>
-      <c r="C144" s="1" t="s">
+      <c r="A144" s="39"/>
+      <c r="B144" s="33"/>
+      <c r="C144" s="6" t="s">
         <v>269</v>
       </c>
-      <c r="D144" s="1" t="s">
+      <c r="D144" s="6" t="s">
         <v>270</v>
       </c>
-      <c r="F144" s="1" t="s">
+      <c r="F144" s="6" t="s">
         <v>214</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="48"/>
-      <c r="B145" s="60"/>
-      <c r="C145" s="1" t="s">
+      <c r="A145" s="39"/>
+      <c r="B145" s="33"/>
+      <c r="C145" s="6" t="s">
         <v>271</v>
       </c>
-      <c r="D145" s="1" t="s">
+      <c r="D145" s="6" t="s">
         <v>310</v>
       </c>
-      <c r="F145" s="1" t="s">
+      <c r="F145" s="6" t="s">
         <v>215</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="48"/>
-      <c r="B146" s="58"/>
+      <c r="A146" s="39"/>
+      <c r="B146" s="20"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="48"/>
-      <c r="B147" s="57" t="s">
+      <c r="A147" s="39"/>
+      <c r="B147" s="17" t="s">
         <v>382</v>
       </c>
-      <c r="C147" s="11" t="s">
+      <c r="C147" s="18" t="s">
         <v>383</v>
       </c>
-      <c r="D147" s="11" t="s">
+      <c r="D147" s="18" t="s">
         <v>384</v>
       </c>
-      <c r="E147" s="11"/>
-      <c r="F147" s="11" t="s">
+      <c r="E147" s="18"/>
+      <c r="F147" s="18" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="48"/>
-      <c r="B148" s="54"/>
-      <c r="C148" s="1" t="s">
+      <c r="A148" s="39"/>
+      <c r="B148" s="12"/>
+      <c r="C148" s="6" t="s">
         <v>385</v>
       </c>
-      <c r="D148" s="1" t="s">
+      <c r="D148" s="6" t="s">
         <v>386</v>
       </c>
-      <c r="F148" s="1" t="s">
+      <c r="F148" s="6" t="s">
         <v>275</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="48"/>
+      <c r="A149" s="39"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A117"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B78:B80"/>
     <mergeCell ref="B147:B148"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="A118:A149"/>
@@ -5229,6 +5180,15 @@
     <mergeCell ref="B115:B117"/>
     <mergeCell ref="B121:B127"/>
     <mergeCell ref="B128:B140"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A117"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="B78:B80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Bio_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_Brownfield_Leuna/Datenbank.xlsx
@@ -8,9 +8,9 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{F6E70D58-6F3B-4347-868A-8396D0AAD775}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523E8C33-20C8-41EC-A865-1569DF69AC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="13896" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -453,9 +453,6 @@
     <t>€/kWa</t>
   </si>
   <si>
-    <t>€/kg_H2 * h</t>
-  </si>
-  <si>
     <t>(%_Kapa)/h</t>
   </si>
   <si>
@@ -738,9 +735,6 @@
     <t>kW_el</t>
   </si>
   <si>
-    <t>€ h / kg a</t>
-  </si>
-  <si>
     <t>calc_cost_gesamt</t>
   </si>
   <si>
@@ -1336,6 +1330,12 @@
   </si>
   <si>
     <t>kWh_th/a</t>
+  </si>
+  <si>
+    <t>€ / kg a</t>
+  </si>
+  <si>
+    <t>kg</t>
   </si>
 </sst>
 </file>
@@ -1488,71 +1488,26 @@
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
@@ -1568,6 +1523,51 @@
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="Standard" xfId="0" builtinId="0"/>
@@ -1894,10 +1894,10 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="40" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="25" customWidth="1"/>
     <col min="3" max="3" width="36.21875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="19" style="15" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="19" style="11" bestFit="1" customWidth="1"/>
     <col min="6" max="6" width="40.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="20.77734375" style="6" bestFit="1" customWidth="1"/>
     <col min="8" max="8" width="20.77734375" style="6" customWidth="1"/>
@@ -1926,54 +1926,54 @@
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="40"/>
+      <c r="G1" s="25"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="D2" s="7" t="s">
         <v>25</v>
       </c>
-      <c r="E2" s="10">
+      <c r="E2" s="8">
         <v>0.66600000000000004</v>
       </c>
-      <c r="F2" s="9" t="s">
+      <c r="F2" s="7" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D3" s="6" t="s">
         <v>63</v>
       </c>
-      <c r="E3" s="13">
+      <c r="E3" s="9">
         <v>50</v>
       </c>
       <c r="F3" s="6" t="s">
-        <v>185</v>
+        <v>184</v>
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D4" s="6" t="s">
         <v>26</v>
       </c>
-      <c r="E4" s="14">
+      <c r="E4" s="10">
         <v>1000</v>
       </c>
       <c r="F4" s="6" t="s">
@@ -1981,15 +1981,15 @@
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="45"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D5" s="6" t="s">
         <v>27</v>
       </c>
-      <c r="E5" s="15">
+      <c r="E5" s="11">
         <v>0.03</v>
       </c>
       <c r="F5" s="6" t="s">
@@ -1997,15 +1997,15 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
+      <c r="A6" s="37"/>
+      <c r="B6" s="45"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D6" s="6" t="s">
         <v>28</v>
       </c>
-      <c r="E6" s="16">
+      <c r="E6" s="12">
         <v>20</v>
       </c>
       <c r="F6" s="6" t="s">
@@ -2013,15 +2013,15 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
+      <c r="A7" s="37"/>
+      <c r="B7" s="45"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D7" s="6" t="s">
         <v>29</v>
       </c>
-      <c r="E7" s="15">
+      <c r="E7" s="11">
         <v>0.08</v>
       </c>
       <c r="F7" s="6" t="s">
@@ -2029,33 +2029,33 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="17" t="s">
+      <c r="A8" s="37"/>
+      <c r="B8" s="48" t="s">
+        <v>229</v>
+      </c>
+      <c r="C8" s="13" t="s">
+        <v>84</v>
+      </c>
+      <c r="D8" s="13" t="s">
         <v>231</v>
       </c>
-      <c r="C8" s="18" t="s">
-        <v>84</v>
-      </c>
-      <c r="D8" s="18" t="s">
-        <v>233</v>
-      </c>
-      <c r="E8" s="19">
+      <c r="E8" s="14">
         <v>1.5</v>
       </c>
-      <c r="F8" s="18" t="s">
-        <v>232</v>
+      <c r="F8" s="13" t="s">
+        <v>230</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
+      <c r="A9" s="37"/>
+      <c r="B9" s="45"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>234</v>
-      </c>
-      <c r="E9" s="13">
+        <v>232</v>
+      </c>
+      <c r="E9" s="9">
         <v>285.39999999999998</v>
       </c>
       <c r="F9" s="6" t="s">
@@ -2063,31 +2063,31 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
+      <c r="A10" s="37"/>
+      <c r="B10" s="45"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>235</v>
-      </c>
-      <c r="E10" s="13">
+        <v>233</v>
+      </c>
+      <c r="E10" s="9">
         <v>5110</v>
       </c>
-      <c r="F10" s="13" t="s">
-        <v>240</v>
+      <c r="F10" s="9" t="s">
+        <v>238</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
+      <c r="A11" s="37"/>
+      <c r="B11" s="45"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>236</v>
-      </c>
-      <c r="E11" s="15">
+        <v>234</v>
+      </c>
+      <c r="E11" s="11">
         <v>0.05</v>
       </c>
       <c r="F11" s="6" t="s">
@@ -2095,47 +2095,47 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="12"/>
+      <c r="A12" s="37"/>
+      <c r="B12" s="45"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>237</v>
-      </c>
-      <c r="E12" s="13">
+        <v>235</v>
+      </c>
+      <c r="E12" s="9">
         <v>0.189</v>
       </c>
       <c r="F12" s="6" t="s">
+        <v>239</v>
+      </c>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="37"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="6" t="s">
+        <v>244</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>240</v>
+      </c>
+      <c r="E13" s="9">
+        <v>1.375</v>
+      </c>
+      <c r="F13" s="6" t="s">
         <v>241</v>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="6" t="s">
-        <v>246</v>
-      </c>
-      <c r="D13" s="6" t="s">
-        <v>242</v>
-      </c>
-      <c r="E13" s="13">
-        <v>1.375</v>
-      </c>
-      <c r="F13" s="6" t="s">
-        <v>243</v>
-      </c>
-    </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
+      <c r="A14" s="37"/>
+      <c r="B14" s="45"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>238</v>
-      </c>
-      <c r="E14" s="16">
+        <v>236</v>
+      </c>
+      <c r="E14" s="12">
         <v>25</v>
       </c>
       <c r="F14" s="6" t="s">
@@ -2143,81 +2143,81 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="20"/>
-      <c r="C15" s="21" t="s">
+      <c r="A15" s="37"/>
+      <c r="B15" s="49"/>
+      <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D15" s="21" t="s">
-        <v>239</v>
-      </c>
-      <c r="E15" s="22">
+      <c r="D15" s="15" t="s">
+        <v>237</v>
+      </c>
+      <c r="E15" s="16">
         <v>0.08</v>
       </c>
-      <c r="F15" s="21" t="s">
+      <c r="F15" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="17" t="s">
-        <v>273</v>
-      </c>
-      <c r="C16" s="18" t="s">
+      <c r="A16" s="37"/>
+      <c r="B16" s="48" t="s">
+        <v>271</v>
+      </c>
+      <c r="C16" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D16" s="18" t="s">
-        <v>276</v>
-      </c>
-      <c r="E16" s="28">
+      <c r="D16" s="13" t="s">
+        <v>274</v>
+      </c>
+      <c r="E16" s="18">
         <v>3.7</v>
       </c>
-      <c r="F16" s="18" t="s">
+      <c r="F16" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
+      <c r="A17" s="37"/>
+      <c r="B17" s="45"/>
       <c r="C17" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>277</v>
-      </c>
-      <c r="E17" s="15">
+        <v>275</v>
+      </c>
+      <c r="E17" s="11">
         <v>0.27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>302</v>
+        <v>300</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
+      <c r="A18" s="37"/>
+      <c r="B18" s="45"/>
       <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>278</v>
-      </c>
-      <c r="E18" s="15">
+        <v>276</v>
+      </c>
+      <c r="E18" s="11">
         <v>700</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
+      <c r="A19" s="37"/>
+      <c r="B19" s="45"/>
       <c r="C19" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>279</v>
-      </c>
-      <c r="E19" s="15">
+        <v>277</v>
+      </c>
+      <c r="E19" s="11">
         <v>0.02</v>
       </c>
       <c r="F19" s="6" t="s">
@@ -2225,15 +2225,15 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
+      <c r="A20" s="37"/>
+      <c r="B20" s="45"/>
       <c r="C20" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>280</v>
-      </c>
-      <c r="E20" s="15">
+        <v>278</v>
+      </c>
+      <c r="E20" s="11">
         <v>20</v>
       </c>
       <c r="F20" s="6" t="s">
@@ -2241,81 +2241,81 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="20"/>
-      <c r="C21" s="21" t="s">
+      <c r="A21" s="37"/>
+      <c r="B21" s="49"/>
+      <c r="C21" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D21" s="21" t="s">
-        <v>281</v>
-      </c>
-      <c r="E21" s="22">
+      <c r="D21" s="15" t="s">
+        <v>279</v>
+      </c>
+      <c r="E21" s="16">
         <v>0.05</v>
       </c>
-      <c r="F21" s="21" t="s">
+      <c r="F21" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="23" t="s">
-        <v>342</v>
+      <c r="A22" s="37"/>
+      <c r="B22" s="41" t="s">
+        <v>340</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>351</v>
-      </c>
-      <c r="E22" s="13">
+        <v>349</v>
+      </c>
+      <c r="E22" s="9">
         <v>0.2</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="23"/>
+      <c r="A23" s="37"/>
+      <c r="B23" s="41"/>
       <c r="C23" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>352</v>
-      </c>
-      <c r="E23" s="13">
+        <v>350</v>
+      </c>
+      <c r="E23" s="9">
         <v>0.92800000000000005</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="23"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="41"/>
       <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>353</v>
-      </c>
-      <c r="E24" s="13">
+        <v>351</v>
+      </c>
+      <c r="E24" s="9">
         <v>1640</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="23"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="6" t="s">
-        <v>379</v>
+        <v>377</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>354</v>
-      </c>
-      <c r="E25" s="15">
+        <v>352</v>
+      </c>
+      <c r="E25" s="11">
         <v>0.04</v>
       </c>
       <c r="F25" s="6" t="s">
@@ -2323,63 +2323,63 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="23"/>
+      <c r="A26" s="37"/>
+      <c r="B26" s="41"/>
       <c r="C26" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>371</v>
+      </c>
+      <c r="E26" s="11">
+        <v>2.5</v>
+      </c>
+      <c r="F26" s="6" t="s">
         <v>372</v>
       </c>
-      <c r="D26" s="6" t="s">
-        <v>373</v>
-      </c>
-      <c r="E26" s="15">
-        <v>2.5</v>
-      </c>
-      <c r="F26" s="6" t="s">
-        <v>374</v>
-      </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="23"/>
+      <c r="A27" s="37"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="6" t="s">
+        <v>353</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>354</v>
+      </c>
+      <c r="E27" s="11">
+        <v>1.5</v>
+      </c>
+      <c r="F27" s="6" t="s">
         <v>355</v>
       </c>
-      <c r="D27" s="6" t="s">
-        <v>356</v>
-      </c>
-      <c r="E27" s="15">
-        <v>1.5</v>
-      </c>
-      <c r="F27" s="6" t="s">
-        <v>357</v>
-      </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="23"/>
+      <c r="A28" s="37"/>
+      <c r="B28" s="41"/>
       <c r="C28" s="6" t="s">
-        <v>380</v>
+        <v>378</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>377</v>
-      </c>
-      <c r="E28" s="15">
+        <v>375</v>
+      </c>
+      <c r="E28" s="11">
         <v>1.5E-3</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>378</v>
+        <v>376</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="23"/>
+      <c r="A29" s="37"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>358</v>
-      </c>
-      <c r="E29" s="16">
+        <v>356</v>
+      </c>
+      <c r="E29" s="12">
         <v>25</v>
       </c>
       <c r="F29" s="6" t="s">
@@ -2387,15 +2387,15 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="11"/>
-      <c r="B30" s="23"/>
+      <c r="A30" s="37"/>
+      <c r="B30" s="41"/>
       <c r="C30" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>359</v>
-      </c>
-      <c r="E30" s="15">
+        <v>357</v>
+      </c>
+      <c r="E30" s="11">
         <v>0.08</v>
       </c>
       <c r="F30" s="6" t="s">
@@ -2403,35 +2403,35 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="7" t="s">
+      <c r="A31" s="36" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="24" t="s">
+      <c r="B31" s="40" t="s">
         <v>3</v>
       </c>
-      <c r="C31" s="9" t="s">
+      <c r="C31" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D31" s="9" t="s">
+      <c r="D31" s="7" t="s">
         <v>33</v>
       </c>
-      <c r="E31" s="25">
+      <c r="E31" s="17">
         <v>490</v>
       </c>
-      <c r="F31" s="9" t="s">
-        <v>93</v>
+      <c r="F31" s="7" t="s">
+        <v>82</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="23"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="41"/>
       <c r="C32" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D32" s="6" t="s">
         <v>40</v>
       </c>
-      <c r="E32" s="15">
+      <c r="E32" s="11">
         <v>0.01</v>
       </c>
       <c r="F32" s="6" t="s">
@@ -2439,15 +2439,15 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="23"/>
+      <c r="A33" s="37"/>
+      <c r="B33" s="41"/>
       <c r="C33" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D33" s="6" t="s">
         <v>32</v>
       </c>
-      <c r="E33" s="16">
+      <c r="E33" s="12">
         <v>20</v>
       </c>
       <c r="F33" s="6" t="s">
@@ -2455,31 +2455,31 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="23"/>
+      <c r="A34" s="37"/>
+      <c r="B34" s="41"/>
       <c r="C34" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="41">
+      <c r="E34" s="26">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F34" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="23"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="41"/>
       <c r="C35" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D35" s="6" t="s">
         <v>37</v>
       </c>
-      <c r="E35" s="15">
+      <c r="E35" s="11">
         <v>0.83299999999999996</v>
       </c>
       <c r="F35" s="6" t="s">
@@ -2487,15 +2487,15 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="23"/>
+      <c r="A36" s="37"/>
+      <c r="B36" s="41"/>
       <c r="C36" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D36" s="6" t="s">
         <v>38</v>
       </c>
-      <c r="E36" s="15">
+      <c r="E36" s="11">
         <v>0.83299999999999996</v>
       </c>
       <c r="F36" s="6" t="s">
@@ -2503,15 +2503,15 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="23"/>
+      <c r="A37" s="37"/>
+      <c r="B37" s="41"/>
       <c r="C37" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D37" s="6" t="s">
         <v>31</v>
       </c>
-      <c r="E37" s="15">
+      <c r="E37" s="11">
         <v>0.05</v>
       </c>
       <c r="F37" s="6" t="s">
@@ -2519,49 +2519,49 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="11"/>
-      <c r="B38" s="26"/>
-      <c r="C38" s="21" t="s">
+      <c r="A38" s="37"/>
+      <c r="B38" s="42"/>
+      <c r="C38" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D38" s="21" t="s">
+      <c r="D38" s="15" t="s">
         <v>39</v>
       </c>
-      <c r="E38" s="22">
+      <c r="E38" s="16">
         <v>0</v>
       </c>
-      <c r="F38" s="21" t="s">
-        <v>95</v>
+      <c r="F38" s="15" t="s">
+        <v>94</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="27" t="s">
-        <v>317</v>
-      </c>
-      <c r="C39" s="9" t="s">
+      <c r="A39" s="37"/>
+      <c r="B39" s="43" t="s">
+        <v>315</v>
+      </c>
+      <c r="C39" s="7" t="s">
         <v>87</v>
       </c>
-      <c r="D39" s="9" t="s">
-        <v>318</v>
-      </c>
-      <c r="E39" s="25">
+      <c r="D39" s="7" t="s">
+        <v>316</v>
+      </c>
+      <c r="E39" s="17">
         <v>2.83</v>
       </c>
-      <c r="F39" s="9" t="s">
-        <v>326</v>
+      <c r="F39" s="7" t="s">
+        <v>324</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="23"/>
+      <c r="A40" s="37"/>
+      <c r="B40" s="41"/>
       <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>319</v>
-      </c>
-      <c r="E40" s="15">
+        <v>317</v>
+      </c>
+      <c r="E40" s="11">
         <v>0.03</v>
       </c>
       <c r="F40" s="6" t="s">
@@ -2569,15 +2569,15 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="23"/>
+      <c r="A41" s="37"/>
+      <c r="B41" s="41"/>
       <c r="C41" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>320</v>
-      </c>
-      <c r="E41" s="16">
+        <v>318</v>
+      </c>
+      <c r="E41" s="12">
         <v>30</v>
       </c>
       <c r="F41" s="6" t="s">
@@ -2585,31 +2585,31 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="23"/>
+      <c r="A42" s="37"/>
+      <c r="B42" s="41"/>
       <c r="C42" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>321</v>
-      </c>
-      <c r="E42" s="15">
+        <v>319</v>
+      </c>
+      <c r="E42" s="11">
         <v>7.3999999999999999E-4</v>
       </c>
       <c r="F42" s="6" t="s">
-        <v>94</v>
+        <v>93</v>
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="23"/>
+      <c r="A43" s="37"/>
+      <c r="B43" s="41"/>
       <c r="C43" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>322</v>
-      </c>
-      <c r="E43" s="15">
+        <v>320</v>
+      </c>
+      <c r="E43" s="11">
         <v>0.98</v>
       </c>
       <c r="F43" s="6" t="s">
@@ -2617,15 +2617,15 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="23"/>
+      <c r="A44" s="37"/>
+      <c r="B44" s="41"/>
       <c r="C44" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>323</v>
-      </c>
-      <c r="E44" s="15">
+        <v>321</v>
+      </c>
+      <c r="E44" s="11">
         <v>0.98</v>
       </c>
       <c r="F44" s="6" t="s">
@@ -2633,15 +2633,15 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="11"/>
-      <c r="B45" s="23"/>
+      <c r="A45" s="37"/>
+      <c r="B45" s="41"/>
       <c r="C45" s="6" t="s">
         <v>15</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>324</v>
-      </c>
-      <c r="E45" s="15">
+        <v>322</v>
+      </c>
+      <c r="E45" s="11">
         <v>0.05</v>
       </c>
       <c r="F45" s="6" t="s">
@@ -2649,49 +2649,49 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="11"/>
-      <c r="B46" s="23"/>
-      <c r="C46" s="21" t="s">
+      <c r="A46" s="37"/>
+      <c r="B46" s="41"/>
+      <c r="C46" s="15" t="s">
         <v>88</v>
       </c>
-      <c r="D46" s="21" t="s">
-        <v>325</v>
-      </c>
-      <c r="E46" s="22">
+      <c r="D46" s="15" t="s">
+        <v>323</v>
+      </c>
+      <c r="E46" s="16">
         <v>0</v>
       </c>
-      <c r="F46" s="21" t="s">
+      <c r="F46" s="15" t="s">
+        <v>94</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="37"/>
+      <c r="B47" s="43" t="s">
+        <v>201</v>
+      </c>
+      <c r="C47" s="13" t="s">
+        <v>91</v>
+      </c>
+      <c r="D47" s="13" t="s">
+        <v>62</v>
+      </c>
+      <c r="E47" s="18">
+        <v>1.6999999999999999E-3</v>
+      </c>
+      <c r="F47" s="13" t="s">
         <v>95</v>
       </c>
     </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="27" t="s">
-        <v>203</v>
-      </c>
-      <c r="C47" s="18" t="s">
-        <v>91</v>
-      </c>
-      <c r="D47" s="18" t="s">
-        <v>62</v>
-      </c>
-      <c r="E47" s="28">
-        <v>1.6999999999999999E-3</v>
-      </c>
-      <c r="F47" s="18" t="s">
-        <v>96</v>
-      </c>
-    </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="12"/>
+      <c r="A48" s="37"/>
+      <c r="B48" s="45"/>
       <c r="C48" s="6" t="s">
         <v>21</v>
       </c>
       <c r="D48" s="6" t="s">
         <v>55</v>
       </c>
-      <c r="E48" s="13">
+      <c r="E48" s="9">
         <f>E49*4</f>
         <v>424</v>
       </c>
@@ -2700,15 +2700,15 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="12"/>
+      <c r="A49" s="37"/>
+      <c r="B49" s="45"/>
       <c r="C49" s="6" t="s">
         <v>16</v>
       </c>
       <c r="D49" s="6" t="s">
         <v>56</v>
       </c>
-      <c r="E49" s="13">
+      <c r="E49" s="9">
         <v>106</v>
       </c>
       <c r="F49" s="6" t="s">
@@ -2716,15 +2716,15 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="12"/>
+      <c r="A50" s="37"/>
+      <c r="B50" s="45"/>
       <c r="C50" s="6" t="s">
         <v>17</v>
       </c>
       <c r="D50" s="6" t="s">
         <v>57</v>
       </c>
-      <c r="E50" s="15">
+      <c r="E50" s="11">
         <v>2.5000000000000001E-2</v>
       </c>
       <c r="F50" s="6" t="s">
@@ -2732,15 +2732,15 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="12"/>
+      <c r="A51" s="37"/>
+      <c r="B51" s="45"/>
       <c r="C51" s="6" t="s">
         <v>35</v>
       </c>
       <c r="D51" s="6" t="s">
         <v>59</v>
       </c>
-      <c r="E51" s="15">
+      <c r="E51" s="11">
         <v>0.93500000000000005</v>
       </c>
       <c r="F51" s="6" t="s">
@@ -2748,15 +2748,15 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="12"/>
+      <c r="A52" s="37"/>
+      <c r="B52" s="45"/>
       <c r="C52" s="6" t="s">
         <v>36</v>
       </c>
       <c r="D52" s="6" t="s">
         <v>60</v>
       </c>
-      <c r="E52" s="15">
+      <c r="E52" s="11">
         <v>0.93500000000000005</v>
       </c>
       <c r="F52" s="6" t="s">
@@ -2764,15 +2764,15 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="12"/>
+      <c r="A53" s="37"/>
+      <c r="B53" s="45"/>
       <c r="C53" s="6" t="s">
         <v>89</v>
       </c>
       <c r="D53" s="6" t="s">
         <v>58</v>
       </c>
-      <c r="E53" s="13">
+      <c r="E53" s="9">
         <v>0.25</v>
       </c>
       <c r="F53" s="6" t="s">
@@ -2780,31 +2780,31 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="12"/>
+      <c r="A54" s="37"/>
+      <c r="B54" s="45"/>
       <c r="C54" s="6" t="s">
         <v>88</v>
       </c>
       <c r="D54" s="6" t="s">
         <v>61</v>
       </c>
-      <c r="E54" s="15">
+      <c r="E54" s="11">
         <v>0</v>
       </c>
       <c r="F54" s="6" t="s">
-        <v>95</v>
+        <v>94</v>
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="12"/>
+      <c r="A55" s="37"/>
+      <c r="B55" s="45"/>
       <c r="C55" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D55" s="6" t="s">
         <v>54</v>
       </c>
-      <c r="E55" s="16">
+      <c r="E55" s="12">
         <v>15</v>
       </c>
       <c r="F55" s="6" t="s">
@@ -2812,80 +2812,80 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="29"/>
-      <c r="B56" s="30"/>
-      <c r="C56" s="31" t="s">
+      <c r="A56" s="38"/>
+      <c r="B56" s="46"/>
+      <c r="C56" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D56" s="31" t="s">
+      <c r="D56" s="19" t="s">
         <v>53</v>
       </c>
-      <c r="E56" s="32">
+      <c r="E56" s="20">
         <v>0.1</v>
       </c>
-      <c r="F56" s="31" t="s">
+      <c r="F56" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="7" t="s">
+      <c r="A57" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="48" t="s">
+      <c r="B57" s="33" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="43" t="s">
+      <c r="C57" s="28" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="43" t="s">
+      <c r="D57" s="28" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="44">
+      <c r="E57" s="29">
         <v>0.1699</v>
       </c>
-      <c r="F57" s="43" t="s">
+      <c r="F57" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="39"/>
-      <c r="B58" s="49" t="s">
+      <c r="B58" s="34" t="s">
+        <v>341</v>
+      </c>
+      <c r="C58" s="21" t="s">
+        <v>342</v>
+      </c>
+      <c r="D58" s="21" t="s">
         <v>343</v>
       </c>
-      <c r="C58" s="34" t="s">
-        <v>344</v>
-      </c>
-      <c r="D58" s="34" t="s">
-        <v>345</v>
-      </c>
-      <c r="E58" s="50">
+      <c r="E58" s="35">
         <v>0</v>
       </c>
-      <c r="F58" s="34" t="s">
-        <v>214</v>
+      <c r="F58" s="21" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="27" t="s">
+      <c r="A59" s="37"/>
+      <c r="B59" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C59" s="18" t="s">
+      <c r="C59" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D59" s="18" t="s">
+      <c r="D59" s="13" t="s">
         <v>46</v>
       </c>
-      <c r="E59" s="28">
+      <c r="E59" s="18">
         <v>0.99</v>
       </c>
-      <c r="F59" s="18" t="s">
+      <c r="F59" s="13" t="s">
         <v>9</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="23"/>
+      <c r="A60" s="37"/>
+      <c r="B60" s="41"/>
       <c r="C60" s="6" t="s">
         <v>10</v>
       </c>
@@ -2900,8 +2900,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="23"/>
+      <c r="A61" s="37"/>
+      <c r="B61" s="41"/>
       <c r="C61" s="6" t="s">
         <v>17</v>
       </c>
@@ -2916,15 +2916,15 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="23"/>
+      <c r="A62" s="37"/>
+      <c r="B62" s="41"/>
       <c r="C62" s="6" t="s">
         <v>18</v>
       </c>
       <c r="D62" s="6" t="s">
         <v>45</v>
       </c>
-      <c r="E62" s="13">
+      <c r="E62" s="9">
         <v>0</v>
       </c>
       <c r="F62" s="6" t="s">
@@ -2932,15 +2932,15 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="23"/>
+      <c r="A63" s="37"/>
+      <c r="B63" s="41"/>
       <c r="C63" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D63" s="6" t="s">
         <v>42</v>
       </c>
-      <c r="E63" s="16">
+      <c r="E63" s="12">
         <v>25</v>
       </c>
       <c r="F63" s="6" t="s">
@@ -2948,15 +2948,15 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="23"/>
+      <c r="A64" s="37"/>
+      <c r="B64" s="41"/>
       <c r="C64" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D64" s="6" t="s">
         <v>67</v>
       </c>
-      <c r="E64" s="13">
+      <c r="E64" s="9">
         <v>1000000</v>
       </c>
       <c r="F64" s="6" t="s">
@@ -2964,42 +2964,42 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="26"/>
-      <c r="C65" s="21" t="s">
+      <c r="A65" s="37"/>
+      <c r="B65" s="42"/>
+      <c r="C65" s="15" t="s">
         <v>15</v>
       </c>
-      <c r="D65" s="21" t="s">
+      <c r="D65" s="15" t="s">
         <v>41</v>
       </c>
-      <c r="E65" s="22">
+      <c r="E65" s="16">
         <v>5.2999999999999999E-2</v>
       </c>
-      <c r="F65" s="21" t="s">
+      <c r="F65" s="15" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="27" t="s">
+      <c r="A66" s="37"/>
+      <c r="B66" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C66" s="18" t="s">
+      <c r="C66" s="13" t="s">
         <v>8</v>
       </c>
-      <c r="D66" s="18" t="s">
+      <c r="D66" s="13" t="s">
         <v>47</v>
       </c>
-      <c r="E66" s="28">
+      <c r="E66" s="18">
         <v>0.997</v>
       </c>
-      <c r="F66" s="18" t="s">
+      <c r="F66" s="13" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="23"/>
+      <c r="A67" s="37"/>
+      <c r="B67" s="41"/>
       <c r="C67" s="6" t="s">
         <v>10</v>
       </c>
@@ -3014,8 +3014,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="23"/>
+      <c r="A68" s="37"/>
+      <c r="B68" s="41"/>
       <c r="C68" s="6" t="s">
         <v>17</v>
       </c>
@@ -3030,8 +3030,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="11"/>
-      <c r="B69" s="23"/>
+      <c r="A69" s="37"/>
+      <c r="B69" s="41"/>
       <c r="C69" s="6" t="s">
         <v>18</v>
       </c>
@@ -3046,15 +3046,15 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="23"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="41"/>
       <c r="C70" s="6" t="s">
         <v>13</v>
       </c>
       <c r="D70" s="6" t="s">
         <v>50</v>
       </c>
-      <c r="E70" s="16">
+      <c r="E70" s="12">
         <v>25</v>
       </c>
       <c r="F70" s="6" t="s">
@@ -3062,15 +3062,15 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="11"/>
-      <c r="B71" s="23"/>
+      <c r="A71" s="37"/>
+      <c r="B71" s="41"/>
       <c r="C71" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E71" s="37">
+      <c r="E71" s="24">
         <v>1000000</v>
       </c>
       <c r="F71" s="6" t="s">
@@ -3078,93 +3078,93 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="29"/>
-      <c r="B72" s="38"/>
-      <c r="C72" s="31" t="s">
+      <c r="A72" s="38"/>
+      <c r="B72" s="44"/>
+      <c r="C72" s="19" t="s">
         <v>15</v>
       </c>
-      <c r="D72" s="31" t="s">
+      <c r="D72" s="19" t="s">
         <v>51</v>
       </c>
-      <c r="E72" s="32">
+      <c r="E72" s="20">
         <v>5.8000000000000003E-2</v>
       </c>
-      <c r="F72" s="31" t="s">
+      <c r="F72" s="19" t="s">
         <v>22</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="7" t="s">
+      <c r="A73" s="36" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="42" t="s">
+      <c r="B73" s="27" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="43" t="s">
+      <c r="C73" s="28" t="s">
         <v>77</v>
       </c>
-      <c r="D73" s="43" t="s">
+      <c r="D73" s="28" t="s">
         <v>78</v>
       </c>
-      <c r="E73" s="44">
+      <c r="E73" s="29">
         <v>-1E-4</v>
       </c>
-      <c r="F73" s="43" t="s">
+      <c r="F73" s="28" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="40" t="s">
+      <c r="A74" s="37"/>
+      <c r="B74" s="25" t="s">
+        <v>297</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>298</v>
+      </c>
+      <c r="D74" s="6" t="s">
         <v>299</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>300</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>301</v>
-      </c>
-      <c r="E74" s="15">
+      <c r="E74" s="11">
         <v>-1E-4</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>326</v>
+        <v>324</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="11"/>
-      <c r="B75" s="45" t="s">
+      <c r="A75" s="37"/>
+      <c r="B75" s="30" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="46" t="s">
+      <c r="C75" s="31" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="46" t="s">
+      <c r="D75" s="31" t="s">
         <v>81</v>
       </c>
-      <c r="E75" s="47">
+      <c r="E75" s="32">
         <v>-1.5</v>
       </c>
-      <c r="F75" s="46" t="s">
+      <c r="F75" s="31" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="29"/>
+      <c r="A76" s="38"/>
       <c r="B76" s="4" t="s">
-        <v>262</v>
-      </c>
-      <c r="C76" s="31" t="s">
-        <v>274</v>
-      </c>
-      <c r="D76" s="31" t="s">
+        <v>260</v>
+      </c>
+      <c r="C76" s="19" t="s">
         <v>272</v>
       </c>
-      <c r="E76" s="32">
+      <c r="D76" s="19" t="s">
+        <v>270</v>
+      </c>
+      <c r="E76" s="20">
         <v>-0.6</v>
       </c>
-      <c r="F76" s="31" t="s">
-        <v>275</v>
+      <c r="F76" s="19" t="s">
+        <v>273</v>
       </c>
     </row>
   </sheetData>
@@ -3224,1135 +3224,1135 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="7" t="s">
+      <c r="A2" s="36" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="8" t="s">
+      <c r="B2" s="47" t="s">
         <v>0</v>
       </c>
-      <c r="C2" s="9" t="s">
+      <c r="C2" s="7" t="s">
+        <v>96</v>
+      </c>
+      <c r="D2" s="7" t="s">
         <v>97</v>
       </c>
-      <c r="D2" s="9" t="s">
+      <c r="E2" s="8"/>
+      <c r="F2" s="7" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="10"/>
-      <c r="F2" s="9" t="s">
-        <v>99</v>
-      </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="11"/>
-      <c r="B3" s="12"/>
+      <c r="A3" s="37"/>
+      <c r="B3" s="45"/>
       <c r="C3" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D3" s="6" t="s">
-        <v>116</v>
-      </c>
-      <c r="E3" s="13"/>
+        <v>115</v>
+      </c>
+      <c r="E3" s="9"/>
       <c r="F3" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="11"/>
-      <c r="B4" s="12"/>
+      <c r="A4" s="37"/>
+      <c r="B4" s="45"/>
       <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D4" s="6" t="s">
-        <v>124</v>
-      </c>
-      <c r="E4" s="14"/>
+        <v>123</v>
+      </c>
+      <c r="E4" s="10"/>
       <c r="F4" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="11"/>
-      <c r="B5" s="12"/>
+      <c r="A5" s="37"/>
+      <c r="B5" s="45"/>
       <c r="C5" s="6" t="s">
+        <v>138</v>
+      </c>
+      <c r="D5" s="6" t="s">
+        <v>137</v>
+      </c>
+      <c r="E5" s="11"/>
+      <c r="F5" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A6" s="37"/>
+      <c r="B6" s="45"/>
+      <c r="C6" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D6" s="6" t="s">
+        <v>143</v>
+      </c>
+      <c r="E6" s="12"/>
+      <c r="F6" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A7" s="37"/>
+      <c r="B7" s="45"/>
+      <c r="C7" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D7" s="6" t="s">
+        <v>158</v>
+      </c>
+      <c r="E7" s="12"/>
+      <c r="F7" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A8" s="37"/>
+      <c r="B8" s="45"/>
+      <c r="C8" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D8" s="6" t="s">
+        <v>195</v>
+      </c>
+      <c r="E8" s="12"/>
+      <c r="F8" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A9" s="37"/>
+      <c r="B9" s="45"/>
+      <c r="C9" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D9" s="6" t="s">
+        <v>166</v>
+      </c>
+      <c r="E9" s="12"/>
+      <c r="F9" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A10" s="37"/>
+      <c r="B10" s="45"/>
+      <c r="C10" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D10" s="6" t="s">
+        <v>194</v>
+      </c>
+      <c r="E10" s="12"/>
+      <c r="F10" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A11" s="37"/>
+      <c r="B11" s="45"/>
+      <c r="E11" s="11"/>
+    </row>
+    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A12" s="37"/>
+      <c r="B12" s="48" t="s">
+        <v>229</v>
+      </c>
+      <c r="C12" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D12" s="13" t="s">
+        <v>245</v>
+      </c>
+      <c r="E12" s="14"/>
+      <c r="F12" s="13" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A13" s="37"/>
+      <c r="B13" s="45"/>
+      <c r="C13" s="6" t="s">
+        <v>253</v>
+      </c>
+      <c r="D13" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="E13" s="9"/>
+      <c r="F13" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A14" s="37"/>
+      <c r="B14" s="45"/>
+      <c r="C14" s="6" t="s">
         <v>139</v>
       </c>
-      <c r="D5" s="6" t="s">
-        <v>138</v>
-      </c>
-      <c r="E5" s="15"/>
-      <c r="F5" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="11"/>
-      <c r="B6" s="12"/>
-      <c r="C6" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D6" s="6" t="s">
-        <v>144</v>
-      </c>
-      <c r="E6" s="16"/>
-      <c r="F6" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="11"/>
-      <c r="B7" s="12"/>
-      <c r="C7" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D7" s="6" t="s">
-        <v>159</v>
-      </c>
-      <c r="E7" s="16"/>
-      <c r="F7" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="11"/>
-      <c r="B8" s="12"/>
-      <c r="C8" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D8" s="6" t="s">
-        <v>197</v>
-      </c>
-      <c r="E8" s="16"/>
-      <c r="F8" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="11"/>
-      <c r="B9" s="12"/>
-      <c r="C9" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D9" s="6" t="s">
-        <v>167</v>
-      </c>
-      <c r="E9" s="16"/>
-      <c r="F9" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="11"/>
-      <c r="B10" s="12"/>
-      <c r="C10" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D10" s="6" t="s">
-        <v>196</v>
-      </c>
-      <c r="E10" s="16"/>
-      <c r="F10" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="11"/>
-      <c r="B11" s="12"/>
-      <c r="E11" s="15"/>
-    </row>
-    <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="11"/>
-      <c r="B12" s="17" t="s">
-        <v>231</v>
-      </c>
-      <c r="C12" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D12" s="18" t="s">
-        <v>247</v>
-      </c>
-      <c r="E12" s="19"/>
-      <c r="F12" s="18" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="11"/>
-      <c r="B13" s="12"/>
-      <c r="C13" s="6" t="s">
+      <c r="D14" s="6" t="s">
+        <v>246</v>
+      </c>
+      <c r="E14" s="9"/>
+      <c r="F14" s="9" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A15" s="37"/>
+      <c r="B15" s="45"/>
+      <c r="C15" s="6" t="s">
+        <v>254</v>
+      </c>
+      <c r="D15" s="6" t="s">
         <v>255</v>
       </c>
-      <c r="D13" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="E13" s="13"/>
-      <c r="F13" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="11"/>
-      <c r="B14" s="12"/>
-      <c r="C14" s="6" t="s">
-        <v>140</v>
-      </c>
-      <c r="D14" s="6" t="s">
-        <v>248</v>
-      </c>
-      <c r="E14" s="13"/>
-      <c r="F14" s="13" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="11"/>
-      <c r="B15" s="12"/>
-      <c r="C15" s="6" t="s">
-        <v>256</v>
-      </c>
-      <c r="D15" s="6" t="s">
+      <c r="E15" s="11"/>
+      <c r="F15" s="6" t="s">
         <v>257</v>
       </c>
-      <c r="E15" s="15"/>
-      <c r="F15" s="6" t="s">
-        <v>259</v>
-      </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="11"/>
-      <c r="B16" s="12"/>
+      <c r="A16" s="37"/>
+      <c r="B16" s="45"/>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D16" s="6" t="s">
+        <v>247</v>
+      </c>
+      <c r="E16" s="9"/>
+      <c r="F16" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A17" s="37"/>
+      <c r="B17" s="45"/>
+      <c r="C17" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D17" s="6" t="s">
+        <v>248</v>
+      </c>
+      <c r="E17" s="9"/>
+      <c r="F17" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A18" s="37"/>
+      <c r="B18" s="45"/>
+      <c r="C18" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D18" s="6" t="s">
         <v>249</v>
       </c>
-      <c r="E16" s="13"/>
-      <c r="F16" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="11"/>
-      <c r="B17" s="12"/>
-      <c r="C17" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D17" s="6" t="s">
+      <c r="E18" s="12"/>
+      <c r="F18" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A19" s="37"/>
+      <c r="B19" s="45"/>
+      <c r="C19" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D19" s="6" t="s">
         <v>250</v>
       </c>
-      <c r="E17" s="13"/>
-      <c r="F17" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="11"/>
-      <c r="B18" s="12"/>
-      <c r="C18" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D18" s="6" t="s">
+      <c r="E19" s="12"/>
+      <c r="F19" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A20" s="37"/>
+      <c r="B20" s="45"/>
+      <c r="C20" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D20" s="6" t="s">
         <v>251</v>
       </c>
-      <c r="E18" s="16"/>
-      <c r="F18" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="11"/>
-      <c r="B19" s="12"/>
-      <c r="C19" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D19" s="6" t="s">
+      <c r="E20" s="12"/>
+      <c r="F20" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A21" s="37"/>
+      <c r="B21" s="45"/>
+      <c r="C21" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D21" s="6" t="s">
         <v>252</v>
       </c>
-      <c r="E19" s="16"/>
-      <c r="F19" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="11"/>
-      <c r="B20" s="12"/>
-      <c r="C20" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D20" s="6" t="s">
-        <v>253</v>
-      </c>
-      <c r="E20" s="16"/>
-      <c r="F20" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="11"/>
-      <c r="B21" s="12"/>
-      <c r="C21" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D21" s="6" t="s">
-        <v>254</v>
-      </c>
-      <c r="E21" s="16"/>
+      <c r="E21" s="12"/>
       <c r="F21" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="11"/>
-      <c r="B22" s="20"/>
-      <c r="C22" s="21"/>
-      <c r="D22" s="21"/>
-      <c r="E22" s="22"/>
-      <c r="F22" s="21"/>
+      <c r="A22" s="37"/>
+      <c r="B22" s="49"/>
+      <c r="C22" s="15"/>
+      <c r="D22" s="15"/>
+      <c r="E22" s="16"/>
+      <c r="F22" s="15"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="11"/>
-      <c r="B23" s="17" t="s">
-        <v>273</v>
+      <c r="A23" s="37"/>
+      <c r="B23" s="48" t="s">
+        <v>271</v>
       </c>
       <c r="C23" s="6" t="s">
-        <v>97</v>
+        <v>96</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>285</v>
-      </c>
-      <c r="E23" s="13"/>
+        <v>283</v>
+      </c>
+      <c r="E23" s="9"/>
       <c r="F23" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="11"/>
-      <c r="B24" s="12"/>
+      <c r="A24" s="37"/>
+      <c r="B24" s="45"/>
       <c r="C24" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>286</v>
-      </c>
-      <c r="E24" s="13"/>
+        <v>284</v>
+      </c>
+      <c r="E24" s="9"/>
       <c r="F24" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="11"/>
-      <c r="B25" s="12"/>
+      <c r="A25" s="37"/>
+      <c r="B25" s="45"/>
       <c r="C25" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D25" s="6" t="s">
+        <v>285</v>
+      </c>
+      <c r="E25" s="11"/>
+      <c r="F25" s="6" t="s">
+        <v>295</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A26" s="37"/>
+      <c r="B26" s="45"/>
+      <c r="C26" s="6" t="s">
+        <v>293</v>
+      </c>
+      <c r="D26" s="6" t="s">
+        <v>294</v>
+      </c>
+      <c r="E26" s="12"/>
+      <c r="F26" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A27" s="37"/>
+      <c r="B27" s="45"/>
+      <c r="C27" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D27" s="6" t="s">
+        <v>286</v>
+      </c>
+      <c r="E27" s="12"/>
+      <c r="F27" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A28" s="37"/>
+      <c r="B28" s="45"/>
+      <c r="C28" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D28" s="6" t="s">
         <v>287</v>
       </c>
-      <c r="E25" s="15"/>
-      <c r="F25" s="6" t="s">
-        <v>297</v>
-      </c>
-    </row>
-    <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="11"/>
-      <c r="B26" s="12"/>
-      <c r="C26" s="6" t="s">
-        <v>295</v>
-      </c>
-      <c r="D26" s="6" t="s">
-        <v>296</v>
-      </c>
-      <c r="E26" s="16"/>
-      <c r="F26" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="11"/>
-      <c r="B27" s="12"/>
-      <c r="C27" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D27" s="6" t="s">
+      <c r="E28" s="12"/>
+      <c r="F28" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A29" s="37"/>
+      <c r="B29" s="45"/>
+      <c r="C29" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D29" s="6" t="s">
         <v>288</v>
       </c>
-      <c r="E27" s="16"/>
-      <c r="F27" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="11"/>
-      <c r="B28" s="12"/>
-      <c r="C28" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D28" s="6" t="s">
+      <c r="E29" s="12"/>
+      <c r="F29" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A30" s="37"/>
+      <c r="B30" s="45"/>
+      <c r="C30" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D30" s="6" t="s">
         <v>289</v>
       </c>
-      <c r="E28" s="16"/>
-      <c r="F28" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="11"/>
-      <c r="B29" s="12"/>
-      <c r="C29" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D29" s="6" t="s">
+      <c r="E30" s="11"/>
+      <c r="F30" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A31" s="37"/>
+      <c r="B31" s="45"/>
+      <c r="C31" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D31" s="6" t="s">
         <v>290</v>
       </c>
-      <c r="E29" s="16"/>
-      <c r="F29" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="11"/>
-      <c r="B30" s="12"/>
-      <c r="C30" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D30" s="6" t="s">
-        <v>291</v>
-      </c>
-      <c r="E30" s="15"/>
-      <c r="F30" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="11"/>
-      <c r="B31" s="12"/>
-      <c r="C31" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D31" s="6" t="s">
-        <v>292</v>
-      </c>
-      <c r="E31" s="15"/>
+      <c r="E31" s="11"/>
       <c r="F31" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="11"/>
-      <c r="B32" s="20"/>
-      <c r="C32" s="21"/>
-      <c r="D32" s="21"/>
-      <c r="E32" s="22"/>
-      <c r="F32" s="21"/>
+      <c r="A32" s="37"/>
+      <c r="B32" s="49"/>
+      <c r="C32" s="15"/>
+      <c r="D32" s="15"/>
+      <c r="E32" s="16"/>
+      <c r="F32" s="15"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="11"/>
-      <c r="B33" s="23" t="s">
+      <c r="A33" s="37"/>
+      <c r="B33" s="41" t="s">
+        <v>358</v>
+      </c>
+      <c r="C33" s="6" t="s">
+        <v>96</v>
+      </c>
+      <c r="D33" s="6" t="s">
+        <v>359</v>
+      </c>
+      <c r="E33" s="9"/>
+      <c r="F33" s="6" t="s">
+        <v>104</v>
+      </c>
+    </row>
+    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A34" s="37"/>
+      <c r="B34" s="41"/>
+      <c r="C34" s="6" t="s">
+        <v>107</v>
+      </c>
+      <c r="D34" s="6" t="s">
         <v>360</v>
       </c>
-      <c r="C33" s="6" t="s">
-        <v>97</v>
-      </c>
-      <c r="D33" s="6" t="s">
-        <v>361</v>
-      </c>
-      <c r="E33" s="13"/>
-      <c r="F33" s="6" t="s">
-        <v>105</v>
-      </c>
-    </row>
-    <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="11"/>
-      <c r="B34" s="23"/>
-      <c r="C34" s="6" t="s">
-        <v>108</v>
-      </c>
-      <c r="D34" s="6" t="s">
-        <v>362</v>
-      </c>
-      <c r="E34" s="13"/>
+      <c r="E34" s="9"/>
       <c r="F34" s="6" t="s">
-        <v>187</v>
+        <v>186</v>
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="11"/>
-      <c r="B35" s="23"/>
+      <c r="A35" s="37"/>
+      <c r="B35" s="41"/>
       <c r="C35" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D35" s="6" t="s">
+        <v>361</v>
+      </c>
+      <c r="E35" s="11"/>
+      <c r="F35" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A36" s="37"/>
+      <c r="B36" s="41"/>
+      <c r="C36" s="6" t="s">
+        <v>281</v>
+      </c>
+      <c r="D36" s="6" t="s">
         <v>363</v>
       </c>
-      <c r="E35" s="15"/>
-      <c r="F35" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="11"/>
-      <c r="B36" s="23"/>
-      <c r="C36" s="6" t="s">
-        <v>283</v>
-      </c>
-      <c r="D36" s="6" t="s">
+      <c r="E36" s="11"/>
+      <c r="F36" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A37" s="37"/>
+      <c r="B37" s="41"/>
+      <c r="C37" s="6" t="s">
+        <v>370</v>
+      </c>
+      <c r="D37" s="6" t="s">
+        <v>373</v>
+      </c>
+      <c r="E37" s="11"/>
+      <c r="F37" s="6" t="s">
+        <v>374</v>
+      </c>
+    </row>
+    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A38" s="37"/>
+      <c r="B38" s="41"/>
+      <c r="C38" s="6" t="s">
+        <v>258</v>
+      </c>
+      <c r="D38" s="6" t="s">
+        <v>362</v>
+      </c>
+      <c r="E38" s="12"/>
+      <c r="F38" s="6" t="s">
+        <v>257</v>
+      </c>
+    </row>
+    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A39" s="37"/>
+      <c r="B39" s="41"/>
+      <c r="C39" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D39" s="6" t="s">
+        <v>364</v>
+      </c>
+      <c r="E39" s="12"/>
+      <c r="F39" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A40" s="37"/>
+      <c r="B40" s="41"/>
+      <c r="C40" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D40" s="6" t="s">
+        <v>367</v>
+      </c>
+      <c r="E40" s="12"/>
+      <c r="F40" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A41" s="37"/>
+      <c r="B41" s="41"/>
+      <c r="C41" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D41" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="E41" s="12"/>
+      <c r="F41" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A42" s="37"/>
+      <c r="B42" s="41"/>
+      <c r="C42" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D42" s="6" t="s">
         <v>365</v>
       </c>
-      <c r="E36" s="15"/>
-      <c r="F36" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="11"/>
-      <c r="B37" s="23"/>
-      <c r="C37" s="6" t="s">
-        <v>372</v>
-      </c>
-      <c r="D37" s="6" t="s">
-        <v>375</v>
-      </c>
-      <c r="E37" s="15"/>
-      <c r="F37" s="6" t="s">
-        <v>376</v>
-      </c>
-    </row>
-    <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="11"/>
-      <c r="B38" s="23"/>
-      <c r="C38" s="6" t="s">
-        <v>260</v>
-      </c>
-      <c r="D38" s="6" t="s">
-        <v>364</v>
-      </c>
-      <c r="E38" s="16"/>
-      <c r="F38" s="6" t="s">
-        <v>259</v>
-      </c>
-    </row>
-    <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="11"/>
-      <c r="B39" s="23"/>
-      <c r="C39" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D39" s="6" t="s">
+      <c r="E42" s="12"/>
+      <c r="F42" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A43" s="37"/>
+      <c r="B43" s="41"/>
+      <c r="C43" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D43" s="6" t="s">
         <v>366</v>
       </c>
-      <c r="E39" s="16"/>
-      <c r="F39" s="6" t="s">
+      <c r="E43" s="11"/>
+      <c r="F43" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A44" s="37"/>
+      <c r="B44" s="41"/>
+      <c r="C44" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D44" s="6" t="s">
+        <v>368</v>
+      </c>
+      <c r="E44" s="11"/>
+      <c r="F44" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A45" s="37"/>
+      <c r="B45" s="41"/>
+      <c r="E45" s="11"/>
+    </row>
+    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
+      <c r="A46" s="36" t="s">
+        <v>71</v>
+      </c>
+      <c r="B46" s="40" t="s">
+        <v>3</v>
+      </c>
+      <c r="C46" s="7" t="s">
+        <v>113</v>
+      </c>
+      <c r="D46" s="7" t="s">
+        <v>103</v>
+      </c>
+      <c r="E46" s="17"/>
+      <c r="F46" s="7" t="s">
+        <v>386</v>
+      </c>
+    </row>
+    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A47" s="37"/>
+      <c r="B47" s="41"/>
+      <c r="C47" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D47" s="6" t="s">
+        <v>110</v>
+      </c>
+      <c r="E47" s="11"/>
+      <c r="F47" s="6" t="s">
+        <v>387</v>
+      </c>
+    </row>
+    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A48" s="37"/>
+      <c r="B48" s="41"/>
+      <c r="C48" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D48" s="6" t="s">
+        <v>133</v>
+      </c>
+      <c r="E48" s="12"/>
+      <c r="F48" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A49" s="37"/>
+      <c r="B49" s="41"/>
+      <c r="C49" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D49" s="6" t="s">
+        <v>134</v>
+      </c>
+      <c r="E49" s="11"/>
+      <c r="F49" s="6" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A50" s="37"/>
+      <c r="B50" s="41"/>
+      <c r="C50" s="6" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="11"/>
-      <c r="B40" s="23"/>
-      <c r="C40" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D40" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="E40" s="16"/>
-      <c r="F40" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="11"/>
-      <c r="B41" s="23"/>
-      <c r="C41" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D41" s="6" t="s">
-        <v>381</v>
-      </c>
-      <c r="E41" s="16"/>
-      <c r="F41" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="11"/>
-      <c r="B42" s="23"/>
-      <c r="C42" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D42" s="6" t="s">
-        <v>367</v>
-      </c>
-      <c r="E42" s="16"/>
-      <c r="F42" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="11"/>
-      <c r="B43" s="23"/>
-      <c r="C43" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D43" s="6" t="s">
-        <v>368</v>
-      </c>
-      <c r="E43" s="15"/>
-      <c r="F43" s="6" t="s">
+      <c r="D50" s="6" t="s">
+        <v>146</v>
+      </c>
+      <c r="E50" s="11"/>
+      <c r="F50" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A51" s="37"/>
+      <c r="B51" s="41"/>
+      <c r="C51" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D51" s="6" t="s">
+        <v>159</v>
+      </c>
+      <c r="E51" s="11"/>
+      <c r="F51" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A52" s="37"/>
+      <c r="B52" s="41"/>
+      <c r="C52" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D52" s="6" t="s">
+        <v>199</v>
+      </c>
+      <c r="E52" s="11"/>
+      <c r="F52" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A53" s="37"/>
+      <c r="B53" s="41"/>
+      <c r="C53" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D53" s="6" t="s">
+        <v>171</v>
+      </c>
+      <c r="E53" s="11"/>
+      <c r="F53" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A54" s="37"/>
+      <c r="B54" s="41"/>
+      <c r="C54" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D54" s="6" t="s">
+        <v>193</v>
+      </c>
+      <c r="E54" s="11"/>
+      <c r="F54" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A55" s="37"/>
+      <c r="B55" s="42"/>
+      <c r="C55" s="15"/>
+      <c r="D55" s="15"/>
+      <c r="E55" s="16"/>
+      <c r="F55" s="15"/>
+    </row>
+    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A56" s="37"/>
+      <c r="B56" s="41" t="s">
+        <v>315</v>
+      </c>
+      <c r="C56" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D56" s="6" t="s">
+        <v>325</v>
+      </c>
+      <c r="E56" s="9"/>
+      <c r="F56" s="6" t="s">
+        <v>338</v>
+      </c>
+    </row>
+    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A57" s="37"/>
+      <c r="B57" s="41"/>
+      <c r="C57" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D57" s="6" t="s">
+        <v>326</v>
+      </c>
+      <c r="E57" s="11"/>
+      <c r="F57" s="6" t="s">
+        <v>339</v>
+      </c>
+    </row>
+    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A58" s="37"/>
+      <c r="B58" s="41"/>
+      <c r="C58" s="6" t="s">
+        <v>135</v>
+      </c>
+      <c r="D58" s="6" t="s">
+        <v>327</v>
+      </c>
+      <c r="E58" s="12"/>
+      <c r="F58" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A59" s="37"/>
+      <c r="B59" s="41"/>
+      <c r="C59" s="6" t="s">
+        <v>136</v>
+      </c>
+      <c r="D59" s="6" t="s">
+        <v>328</v>
+      </c>
+      <c r="E59" s="11"/>
+      <c r="F59" s="6" t="s">
+        <v>385</v>
+      </c>
+    </row>
+    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A60" s="37"/>
+      <c r="B60" s="41"/>
+      <c r="C60" s="6" t="s">
         <v>141</v>
       </c>
-    </row>
-    <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="11"/>
-      <c r="B44" s="23"/>
-      <c r="C44" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D44" s="6" t="s">
-        <v>370</v>
-      </c>
-      <c r="E44" s="15"/>
-      <c r="F44" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="11"/>
-      <c r="B45" s="23"/>
-      <c r="E45" s="15"/>
-    </row>
-    <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="7" t="s">
-        <v>71</v>
-      </c>
-      <c r="B46" s="24" t="s">
-        <v>3</v>
-      </c>
-      <c r="C46" s="9" t="s">
+      <c r="D60" s="6" t="s">
+        <v>329</v>
+      </c>
+      <c r="E60" s="11"/>
+      <c r="F60" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A61" s="37"/>
+      <c r="B61" s="41"/>
+      <c r="C61" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D61" s="6" t="s">
+        <v>330</v>
+      </c>
+      <c r="E61" s="11"/>
+      <c r="F61" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A62" s="37"/>
+      <c r="B62" s="41"/>
+      <c r="C62" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D62" s="6" t="s">
+        <v>331</v>
+      </c>
+      <c r="E62" s="11"/>
+      <c r="F62" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A63" s="37"/>
+      <c r="B63" s="41"/>
+      <c r="C63" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D63" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="E63" s="11"/>
+      <c r="F63" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A64" s="37"/>
+      <c r="B64" s="41"/>
+      <c r="C64" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D64" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="E64" s="11"/>
+      <c r="F64" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A65" s="37"/>
+      <c r="B65" s="42"/>
+      <c r="E65" s="11"/>
+    </row>
+    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A66" s="37"/>
+      <c r="B66" s="43" t="s">
+        <v>6</v>
+      </c>
+      <c r="C66" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D66" s="13" t="s">
+        <v>100</v>
+      </c>
+      <c r="E66" s="18"/>
+      <c r="F66" s="13" t="s">
+        <v>98</v>
+      </c>
+    </row>
+    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A67" s="37"/>
+      <c r="B67" s="41"/>
+      <c r="C67" s="6" t="s">
+        <v>113</v>
+      </c>
+      <c r="D67" s="6" t="s">
+        <v>102</v>
+      </c>
+      <c r="E67" s="11"/>
+      <c r="F67" s="6" t="s">
+        <v>105</v>
+      </c>
+    </row>
+    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A68" s="37"/>
+      <c r="B68" s="45"/>
+      <c r="C68" s="6" t="s">
+        <v>111</v>
+      </c>
+      <c r="D68" s="6" t="s">
+        <v>112</v>
+      </c>
+      <c r="E68" s="9"/>
+      <c r="F68" s="6" t="s">
         <v>114</v>
       </c>
-      <c r="D46" s="9" t="s">
-        <v>104</v>
-      </c>
-      <c r="E46" s="25"/>
-      <c r="F46" s="9" t="s">
-        <v>188</v>
-      </c>
-    </row>
-    <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="11"/>
-      <c r="B47" s="23"/>
-      <c r="C47" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D47" s="6" t="s">
-        <v>111</v>
-      </c>
-      <c r="E47" s="15"/>
-      <c r="F47" s="6" t="s">
-        <v>30</v>
-      </c>
-    </row>
-    <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="11"/>
-      <c r="B48" s="23"/>
-      <c r="C48" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D48" s="6" t="s">
-        <v>134</v>
-      </c>
-      <c r="E48" s="16"/>
-      <c r="F48" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="11"/>
-      <c r="B49" s="23"/>
-      <c r="C49" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D49" s="6" t="s">
-        <v>135</v>
-      </c>
-      <c r="E49" s="15"/>
-      <c r="F49" s="6" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="11"/>
-      <c r="B50" s="23"/>
-      <c r="C50" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D50" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E50" s="15"/>
-      <c r="F50" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="11"/>
-      <c r="B51" s="23"/>
-      <c r="C51" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D51" s="6" t="s">
-        <v>160</v>
-      </c>
-      <c r="E51" s="15"/>
-      <c r="F51" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="11"/>
-      <c r="B52" s="23"/>
-      <c r="C52" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D52" s="6" t="s">
-        <v>201</v>
-      </c>
-      <c r="E52" s="15"/>
-      <c r="F52" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="11"/>
-      <c r="B53" s="23"/>
-      <c r="C53" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D53" s="6" t="s">
-        <v>172</v>
-      </c>
-      <c r="E53" s="15"/>
-      <c r="F53" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="11"/>
-      <c r="B54" s="23"/>
-      <c r="C54" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D54" s="6" t="s">
-        <v>195</v>
-      </c>
-      <c r="E54" s="15"/>
-      <c r="F54" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="11"/>
-      <c r="B55" s="26"/>
-      <c r="C55" s="21"/>
-      <c r="D55" s="21"/>
-      <c r="E55" s="22"/>
-      <c r="F55" s="21"/>
-    </row>
-    <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="11"/>
-      <c r="B56" s="23" t="s">
-        <v>317</v>
-      </c>
-      <c r="C56" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D56" s="6" t="s">
-        <v>327</v>
-      </c>
-      <c r="E56" s="13"/>
-      <c r="F56" s="6" t="s">
-        <v>340</v>
-      </c>
-    </row>
-    <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="11"/>
-      <c r="B57" s="23"/>
-      <c r="C57" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D57" s="6" t="s">
-        <v>328</v>
-      </c>
-      <c r="E57" s="15"/>
-      <c r="F57" s="6" t="s">
-        <v>341</v>
-      </c>
-    </row>
-    <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="11"/>
-      <c r="B58" s="23"/>
-      <c r="C58" s="6" t="s">
-        <v>136</v>
-      </c>
-      <c r="D58" s="6" t="s">
-        <v>329</v>
-      </c>
-      <c r="E58" s="16"/>
-      <c r="F58" s="6" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="11"/>
-      <c r="B59" s="23"/>
-      <c r="C59" s="6" t="s">
-        <v>137</v>
-      </c>
-      <c r="D59" s="6" t="s">
-        <v>330</v>
-      </c>
-      <c r="E59" s="15"/>
-      <c r="F59" s="6" t="s">
-        <v>387</v>
-      </c>
-    </row>
-    <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="11"/>
-      <c r="B60" s="23"/>
-      <c r="C60" s="6" t="s">
-        <v>142</v>
-      </c>
-      <c r="D60" s="6" t="s">
-        <v>331</v>
-      </c>
-      <c r="E60" s="15"/>
-      <c r="F60" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="11"/>
-      <c r="B61" s="23"/>
-      <c r="C61" s="6" t="s">
-        <v>156</v>
-      </c>
-      <c r="D61" s="6" t="s">
-        <v>332</v>
-      </c>
-      <c r="E61" s="15"/>
-      <c r="F61" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="11"/>
-      <c r="B62" s="23"/>
-      <c r="C62" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D62" s="6" t="s">
-        <v>333</v>
-      </c>
-      <c r="E62" s="15"/>
-      <c r="F62" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="11"/>
-      <c r="B63" s="23"/>
-      <c r="C63" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D63" s="6" t="s">
-        <v>334</v>
-      </c>
-      <c r="E63" s="15"/>
-      <c r="F63" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="11"/>
-      <c r="B64" s="23"/>
-      <c r="C64" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D64" s="6" t="s">
-        <v>335</v>
-      </c>
-      <c r="E64" s="15"/>
-      <c r="F64" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="11"/>
-      <c r="B65" s="26"/>
-      <c r="E65" s="15"/>
-    </row>
-    <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="11"/>
-      <c r="B66" s="27" t="s">
-        <v>6</v>
-      </c>
-      <c r="C66" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D66" s="18" t="s">
-        <v>101</v>
-      </c>
-      <c r="E66" s="28"/>
-      <c r="F66" s="18" t="s">
-        <v>99</v>
-      </c>
-    </row>
-    <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="11"/>
-      <c r="B67" s="23"/>
-      <c r="C67" s="6" t="s">
-        <v>114</v>
-      </c>
-      <c r="D67" s="6" t="s">
-        <v>103</v>
-      </c>
-      <c r="E67" s="15"/>
-      <c r="F67" s="6" t="s">
-        <v>106</v>
-      </c>
-    </row>
-    <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="11"/>
-      <c r="B68" s="12"/>
-      <c r="C68" s="6" t="s">
-        <v>112</v>
-      </c>
-      <c r="D68" s="6" t="s">
-        <v>113</v>
-      </c>
-      <c r="E68" s="13"/>
-      <c r="F68" s="6" t="s">
-        <v>115</v>
-      </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="11"/>
-      <c r="B69" s="12"/>
+      <c r="A69" s="37"/>
+      <c r="B69" s="45"/>
       <c r="C69" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D69" s="6" t="s">
-        <v>186</v>
-      </c>
-      <c r="E69" s="13"/>
+        <v>185</v>
+      </c>
+      <c r="E69" s="9"/>
       <c r="F69" s="6" t="s">
         <v>66</v>
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="11"/>
-      <c r="B70" s="12"/>
+      <c r="A70" s="37"/>
+      <c r="B70" s="45"/>
       <c r="C70" s="6" t="s">
+        <v>126</v>
+      </c>
+      <c r="D70" s="6" t="s">
+        <v>124</v>
+      </c>
+      <c r="E70" s="9"/>
+      <c r="F70" s="6" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A71" s="37"/>
+      <c r="B71" s="45"/>
+      <c r="C71" s="6" t="s">
         <v>127</v>
       </c>
-      <c r="D70" s="6" t="s">
+      <c r="D71" s="6" t="s">
         <v>125</v>
       </c>
-      <c r="E70" s="13"/>
-      <c r="F70" s="6" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="11"/>
-      <c r="B71" s="12"/>
-      <c r="C71" s="6" t="s">
-        <v>128</v>
-      </c>
-      <c r="D71" s="6" t="s">
-        <v>126</v>
-      </c>
-      <c r="E71" s="15"/>
+      <c r="E71" s="11"/>
       <c r="F71" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="11"/>
-      <c r="B72" s="12"/>
+      <c r="A72" s="37"/>
+      <c r="B72" s="45"/>
       <c r="C72" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D72" s="6" t="s">
-        <v>146</v>
-      </c>
-      <c r="E72" s="13"/>
+        <v>145</v>
+      </c>
+      <c r="E72" s="9"/>
       <c r="F72" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="11"/>
-      <c r="B73" s="12"/>
+      <c r="A73" s="37"/>
+      <c r="B73" s="45"/>
       <c r="C73" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D73" s="6" t="s">
-        <v>158</v>
-      </c>
-      <c r="E73" s="15"/>
+        <v>157</v>
+      </c>
+      <c r="E73" s="11"/>
       <c r="F73" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="11"/>
-      <c r="B74" s="12"/>
+      <c r="A74" s="37"/>
+      <c r="B74" s="45"/>
       <c r="C74" s="6" t="s">
-        <v>198</v>
+        <v>196</v>
       </c>
       <c r="D74" s="6" t="s">
-        <v>202</v>
-      </c>
-      <c r="E74" s="15"/>
+        <v>200</v>
+      </c>
+      <c r="E74" s="11"/>
       <c r="F74" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="11"/>
-      <c r="B75" s="12"/>
+      <c r="A75" s="37"/>
+      <c r="B75" s="45"/>
       <c r="C75" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D75" s="6" t="s">
-        <v>171</v>
-      </c>
-      <c r="E75" s="15"/>
+        <v>170</v>
+      </c>
+      <c r="E75" s="11"/>
       <c r="F75" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="11"/>
-      <c r="B76" s="12"/>
+      <c r="A76" s="37"/>
+      <c r="B76" s="45"/>
       <c r="C76" s="6" t="s">
-        <v>190</v>
+        <v>188</v>
       </c>
       <c r="D76" s="6" t="s">
-        <v>194</v>
-      </c>
-      <c r="E76" s="15"/>
+        <v>192</v>
+      </c>
+      <c r="E76" s="11"/>
       <c r="F76" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="29"/>
-      <c r="B77" s="30"/>
-      <c r="C77" s="31"/>
-      <c r="D77" s="31"/>
-      <c r="E77" s="32"/>
-      <c r="F77" s="31"/>
+      <c r="A77" s="38"/>
+      <c r="B77" s="46"/>
+      <c r="C77" s="19"/>
+      <c r="D77" s="19"/>
+      <c r="E77" s="20"/>
+      <c r="F77" s="19"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="7" t="s">
+      <c r="A78" s="36" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="8" t="s">
+      <c r="B78" s="47" t="s">
         <v>73</v>
       </c>
-      <c r="C78" s="9" t="s">
+      <c r="C78" s="7" t="s">
+        <v>117</v>
+      </c>
+      <c r="D78" s="7" t="s">
+        <v>116</v>
+      </c>
+      <c r="E78" s="17"/>
+      <c r="F78" s="7" t="s">
         <v>118</v>
       </c>
-      <c r="D78" s="9" t="s">
-        <v>117</v>
-      </c>
-      <c r="E78" s="25"/>
-      <c r="F78" s="9" t="s">
-        <v>119</v>
-      </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="11"/>
-      <c r="B79" s="33"/>
-      <c r="C79" s="34" t="s">
-        <v>154</v>
-      </c>
-      <c r="D79" s="34" t="s">
+      <c r="A79" s="37"/>
+      <c r="B79" s="50"/>
+      <c r="C79" s="21" t="s">
         <v>153</v>
       </c>
-      <c r="E79" s="35"/>
-      <c r="F79" s="34" t="s">
-        <v>150</v>
+      <c r="D79" s="21" t="s">
+        <v>152</v>
+      </c>
+      <c r="E79" s="22"/>
+      <c r="F79" s="21" t="s">
+        <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="11"/>
-      <c r="B80" s="20"/>
-      <c r="C80" s="21"/>
-      <c r="D80" s="21"/>
-      <c r="E80" s="36"/>
-      <c r="F80" s="21"/>
+      <c r="A80" s="37"/>
+      <c r="B80" s="49"/>
+      <c r="C80" s="15"/>
+      <c r="D80" s="15"/>
+      <c r="E80" s="23"/>
+      <c r="F80" s="15"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="11"/>
-      <c r="B81" s="33" t="s">
-        <v>343</v>
-      </c>
-      <c r="C81" s="34" t="s">
+      <c r="A81" s="37"/>
+      <c r="B81" s="50" t="s">
+        <v>341</v>
+      </c>
+      <c r="C81" s="21" t="s">
+        <v>344</v>
+      </c>
+      <c r="D81" s="21" t="s">
+        <v>347</v>
+      </c>
+      <c r="E81" s="22"/>
+      <c r="F81" s="21" t="s">
         <v>346</v>
       </c>
-      <c r="D81" s="34" t="s">
-        <v>349</v>
-      </c>
-      <c r="E81" s="35"/>
-      <c r="F81" s="34" t="s">
+    </row>
+    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A82" s="37"/>
+      <c r="B82" s="50"/>
+      <c r="C82" s="6" t="s">
+        <v>345</v>
+      </c>
+      <c r="D82" s="6" t="s">
         <v>348</v>
       </c>
-    </row>
-    <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="11"/>
-      <c r="B82" s="33"/>
-      <c r="C82" s="6" t="s">
-        <v>347</v>
-      </c>
-      <c r="D82" s="6" t="s">
-        <v>350</v>
-      </c>
-      <c r="E82" s="13"/>
+      <c r="E82" s="9"/>
       <c r="F82" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="11"/>
-      <c r="B83" s="33"/>
-      <c r="E83" s="13"/>
+      <c r="A83" s="37"/>
+      <c r="B83" s="50"/>
+      <c r="E83" s="9"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="11"/>
-      <c r="B84" s="27" t="s">
+      <c r="A84" s="37"/>
+      <c r="B84" s="43" t="s">
         <v>4</v>
       </c>
-      <c r="C84" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D84" s="18" t="s">
-        <v>100</v>
-      </c>
-      <c r="E84" s="28"/>
-      <c r="F84" s="18" t="s">
+      <c r="C84" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D84" s="13" t="s">
         <v>99</v>
       </c>
+      <c r="E84" s="18"/>
+      <c r="F84" s="13" t="s">
+        <v>98</v>
+      </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="11"/>
-      <c r="B85" s="23"/>
+      <c r="A85" s="37"/>
+      <c r="B85" s="41"/>
       <c r="C85" s="6" t="s">
-        <v>108</v>
+        <v>107</v>
       </c>
       <c r="D85" s="6" t="s">
-        <v>110</v>
+        <v>109</v>
       </c>
       <c r="E85" s="1"/>
       <c r="F85" s="6" t="s">
@@ -4360,131 +4360,131 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="11"/>
-      <c r="B86" s="23"/>
+      <c r="A86" s="37"/>
+      <c r="B86" s="41"/>
       <c r="C86" s="6" t="s">
-        <v>123</v>
+        <v>122</v>
       </c>
       <c r="D86" s="6" t="s">
-        <v>122</v>
+        <v>121</v>
       </c>
       <c r="E86" s="1"/>
       <c r="F86" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="11"/>
-      <c r="B87" s="23"/>
+      <c r="A87" s="37"/>
+      <c r="B87" s="41"/>
       <c r="C87" s="6" t="s">
-        <v>142</v>
+        <v>141</v>
       </c>
       <c r="D87" s="6" t="s">
-        <v>145</v>
-      </c>
-      <c r="E87" s="13"/>
+        <v>144</v>
+      </c>
+      <c r="E87" s="9"/>
       <c r="F87" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="11"/>
-      <c r="B88" s="23"/>
+      <c r="A88" s="37"/>
+      <c r="B88" s="41"/>
       <c r="C88" s="6" t="s">
+        <v>155</v>
+      </c>
+      <c r="D88" s="6" t="s">
         <v>156</v>
       </c>
-      <c r="D88" s="6" t="s">
-        <v>157</v>
-      </c>
-      <c r="E88" s="16"/>
+      <c r="E88" s="12"/>
       <c r="F88" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="11"/>
-      <c r="B89" s="23"/>
+      <c r="A89" s="37"/>
+      <c r="B89" s="41"/>
       <c r="C89" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D89" s="6" t="s">
         <v>162</v>
       </c>
-      <c r="D89" s="6" t="s">
-        <v>163</v>
-      </c>
-      <c r="E89" s="13"/>
+      <c r="E89" s="9"/>
       <c r="F89" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="11"/>
-      <c r="B90" s="23"/>
+      <c r="A90" s="37"/>
+      <c r="B90" s="41"/>
       <c r="C90" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D90" s="6" t="s">
         <v>198</v>
       </c>
-      <c r="D90" s="6" t="s">
-        <v>200</v>
-      </c>
-      <c r="E90" s="13"/>
+      <c r="E90" s="9"/>
       <c r="F90" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="11"/>
-      <c r="B91" s="23"/>
+      <c r="A91" s="37"/>
+      <c r="B91" s="41"/>
       <c r="C91" s="6" t="s">
-        <v>168</v>
+        <v>167</v>
       </c>
       <c r="D91" s="6" t="s">
-        <v>170</v>
-      </c>
-      <c r="E91" s="15"/>
+        <v>169</v>
+      </c>
+      <c r="E91" s="11"/>
       <c r="F91" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="11"/>
-      <c r="B92" s="23"/>
+      <c r="A92" s="37"/>
+      <c r="B92" s="41"/>
       <c r="C92" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D92" s="6" t="s">
         <v>190</v>
       </c>
-      <c r="D92" s="6" t="s">
-        <v>192</v>
-      </c>
-      <c r="E92" s="15"/>
+      <c r="E92" s="11"/>
       <c r="F92" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="11"/>
-      <c r="B93" s="26"/>
+      <c r="A93" s="37"/>
+      <c r="B93" s="42"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="11"/>
-      <c r="B94" s="27" t="s">
+      <c r="A94" s="37"/>
+      <c r="B94" s="43" t="s">
         <v>5</v>
       </c>
-      <c r="C94" s="18" t="s">
-        <v>97</v>
-      </c>
-      <c r="D94" s="18" t="s">
-        <v>102</v>
-      </c>
-      <c r="E94" s="28"/>
-      <c r="F94" s="18" t="s">
-        <v>99</v>
+      <c r="C94" s="13" t="s">
+        <v>96</v>
+      </c>
+      <c r="D94" s="13" t="s">
+        <v>101</v>
+      </c>
+      <c r="E94" s="18"/>
+      <c r="F94" s="13" t="s">
+        <v>98</v>
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="11"/>
-      <c r="B95" s="23"/>
+      <c r="A95" s="37"/>
+      <c r="B95" s="41"/>
       <c r="C95" s="6" t="s">
-        <v>109</v>
+        <v>108</v>
       </c>
       <c r="D95" s="6" t="s">
-        <v>107</v>
+        <v>106</v>
       </c>
       <c r="E95" s="1"/>
       <c r="F95" s="6" t="s">
@@ -4492,671 +4492,671 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="11"/>
-      <c r="B96" s="23"/>
+      <c r="A96" s="37"/>
+      <c r="B96" s="41"/>
       <c r="C96" s="6" t="s">
-        <v>121</v>
+        <v>120</v>
       </c>
       <c r="D96" s="6" t="s">
-        <v>120</v>
+        <v>119</v>
       </c>
       <c r="E96" s="1"/>
       <c r="F96" s="6" t="s">
-        <v>119</v>
+        <v>118</v>
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="11"/>
-      <c r="B97" s="23"/>
+      <c r="A97" s="37"/>
+      <c r="B97" s="41"/>
       <c r="C97" s="6" t="s">
+        <v>141</v>
+      </c>
+      <c r="D97" s="6" t="s">
         <v>142</v>
-      </c>
-      <c r="D97" s="6" t="s">
-        <v>143</v>
       </c>
       <c r="E97" s="1"/>
       <c r="F97" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="11"/>
-      <c r="B98" s="23"/>
+      <c r="A98" s="37"/>
+      <c r="B98" s="41"/>
       <c r="C98" s="6" t="s">
-        <v>156</v>
+        <v>155</v>
       </c>
       <c r="D98" s="6" t="s">
-        <v>155</v>
-      </c>
-      <c r="E98" s="16"/>
+        <v>154</v>
+      </c>
+      <c r="E98" s="12"/>
       <c r="F98" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A99" s="37"/>
+      <c r="B99" s="41"/>
+      <c r="C99" s="6" t="s">
+        <v>161</v>
+      </c>
+      <c r="D99" s="6" t="s">
+        <v>160</v>
+      </c>
+      <c r="E99" s="24"/>
+      <c r="F99" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A100" s="37"/>
+      <c r="B100" s="41"/>
+      <c r="C100" s="6" t="s">
+        <v>196</v>
+      </c>
+      <c r="D100" s="6" t="s">
+        <v>197</v>
+      </c>
+      <c r="E100" s="24"/>
+      <c r="F100" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A101" s="37"/>
+      <c r="B101" s="41"/>
+      <c r="C101" s="6" t="s">
+        <v>167</v>
+      </c>
+      <c r="D101" s="6" t="s">
+        <v>168</v>
+      </c>
+      <c r="E101" s="11"/>
+      <c r="F101" s="6" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A102" s="37"/>
+      <c r="B102" s="41"/>
+      <c r="C102" s="6" t="s">
+        <v>188</v>
+      </c>
+      <c r="D102" s="6" t="s">
+        <v>189</v>
+      </c>
+      <c r="E102" s="11"/>
+      <c r="F102" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A103" s="38"/>
+      <c r="B103" s="44"/>
+    </row>
+    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A104" s="36" t="s">
+        <v>76</v>
+      </c>
+      <c r="B104" s="47" t="s">
+        <v>73</v>
+      </c>
+      <c r="C104" s="7" t="s">
+        <v>129</v>
+      </c>
+      <c r="D104" s="7" t="s">
+        <v>128</v>
+      </c>
+      <c r="E104" s="8"/>
+      <c r="F104" s="7" t="s">
+        <v>118</v>
+      </c>
+    </row>
+    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A105" s="37"/>
+      <c r="B105" s="45"/>
+      <c r="C105" s="6" t="s">
+        <v>228</v>
+      </c>
+      <c r="D105" s="6" t="s">
+        <v>227</v>
+      </c>
+      <c r="E105" s="11"/>
+      <c r="F105" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A106" s="37"/>
+      <c r="B106" s="45"/>
+      <c r="C106" s="6" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="11"/>
-      <c r="B99" s="23"/>
-      <c r="C99" s="6" t="s">
-        <v>162</v>
-      </c>
-      <c r="D99" s="6" t="s">
-        <v>161</v>
-      </c>
-      <c r="E99" s="37"/>
-      <c r="F99" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="11"/>
-      <c r="B100" s="23"/>
-      <c r="C100" s="6" t="s">
-        <v>198</v>
-      </c>
-      <c r="D100" s="6" t="s">
-        <v>199</v>
-      </c>
-      <c r="E100" s="37"/>
-      <c r="F100" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="11"/>
-      <c r="B101" s="23"/>
-      <c r="C101" s="6" t="s">
-        <v>168</v>
-      </c>
-      <c r="D101" s="6" t="s">
-        <v>169</v>
-      </c>
-      <c r="E101" s="15"/>
-      <c r="F101" s="6" t="s">
-        <v>141</v>
-      </c>
-    </row>
-    <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="11"/>
-      <c r="B102" s="23"/>
-      <c r="C102" s="6" t="s">
-        <v>190</v>
-      </c>
-      <c r="D102" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="E102" s="15"/>
-      <c r="F102" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="29"/>
-      <c r="B103" s="38"/>
-    </row>
-    <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="7" t="s">
-        <v>76</v>
-      </c>
-      <c r="B104" s="8" t="s">
-        <v>73</v>
-      </c>
-      <c r="C104" s="9" t="s">
+      <c r="D106" s="6" t="s">
+        <v>147</v>
+      </c>
+      <c r="E106" s="11"/>
+      <c r="F106" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A107" s="37"/>
+      <c r="B107" s="49"/>
+      <c r="C107" s="15"/>
+      <c r="D107" s="15"/>
+      <c r="E107" s="16"/>
+      <c r="F107" s="15"/>
+    </row>
+    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A108" s="37"/>
+      <c r="B108" s="48" t="s">
+        <v>301</v>
+      </c>
+      <c r="C108" s="6" t="s">
+        <v>302</v>
+      </c>
+      <c r="D108" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="E108" s="11"/>
+      <c r="F108" s="6" t="s">
+        <v>292</v>
+      </c>
+    </row>
+    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A109" s="37"/>
+      <c r="B109" s="45"/>
+      <c r="C109" s="6" t="s">
+        <v>306</v>
+      </c>
+      <c r="D109" s="6" t="s">
+        <v>304</v>
+      </c>
+      <c r="E109" s="11"/>
+      <c r="F109" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A110" s="37"/>
+      <c r="B110" s="45"/>
+      <c r="C110" s="6" t="s">
+        <v>307</v>
+      </c>
+      <c r="D110" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="E110" s="11"/>
+      <c r="F110" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A111" s="37"/>
+      <c r="B111" s="49"/>
+      <c r="E111" s="11"/>
+    </row>
+    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A112" s="37"/>
+      <c r="B112" s="48" t="s">
+        <v>79</v>
+      </c>
+      <c r="C112" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D112" s="13" t="s">
         <v>130</v>
       </c>
-      <c r="D104" s="9" t="s">
-        <v>129</v>
-      </c>
-      <c r="E104" s="10"/>
-      <c r="F104" s="9" t="s">
-        <v>119</v>
-      </c>
-    </row>
-    <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="11"/>
-      <c r="B105" s="12"/>
-      <c r="C105" s="6" t="s">
-        <v>230</v>
-      </c>
-      <c r="D105" s="6" t="s">
-        <v>229</v>
-      </c>
-      <c r="E105" s="15"/>
-      <c r="F105" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="11"/>
-      <c r="B106" s="12"/>
-      <c r="C106" s="6" t="s">
+      <c r="E112" s="18"/>
+      <c r="F112" s="13" t="s">
+        <v>132</v>
+      </c>
+    </row>
+    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A113" s="37"/>
+      <c r="B113" s="45"/>
+      <c r="C113" s="6" t="s">
         <v>151</v>
       </c>
-      <c r="D106" s="6" t="s">
+      <c r="D113" s="6" t="s">
         <v>148</v>
       </c>
-      <c r="E106" s="15"/>
-      <c r="F106" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="11"/>
-      <c r="B107" s="20"/>
-      <c r="C107" s="21"/>
-      <c r="D107" s="21"/>
-      <c r="E107" s="22"/>
-      <c r="F107" s="21"/>
-    </row>
-    <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="11"/>
-      <c r="B108" s="17" t="s">
-        <v>303</v>
-      </c>
-      <c r="C108" s="6" t="s">
-        <v>304</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="E108" s="15"/>
-      <c r="F108" s="6" t="s">
-        <v>294</v>
-      </c>
-    </row>
-    <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="11"/>
-      <c r="B109" s="12"/>
-      <c r="C109" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="E109" s="15"/>
-      <c r="F109" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="11"/>
-      <c r="B110" s="12"/>
-      <c r="C110" s="6" t="s">
-        <v>309</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="E110" s="15"/>
-      <c r="F110" s="6" t="s">
-        <v>150</v>
-      </c>
-    </row>
-    <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="11"/>
-      <c r="B111" s="20"/>
-      <c r="E111" s="15"/>
-    </row>
-    <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="11"/>
-      <c r="B112" s="17" t="s">
-        <v>79</v>
-      </c>
-      <c r="C112" s="18" t="s">
-        <v>132</v>
-      </c>
-      <c r="D112" s="18" t="s">
-        <v>131</v>
-      </c>
-      <c r="E112" s="28"/>
-      <c r="F112" s="18" t="s">
-        <v>133</v>
-      </c>
-    </row>
-    <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="11"/>
-      <c r="B113" s="12"/>
-      <c r="C113" s="6" t="s">
-        <v>152</v>
-      </c>
-      <c r="D113" s="6" t="s">
+      <c r="E113" s="11"/>
+      <c r="F113" s="6" t="s">
         <v>149</v>
       </c>
-      <c r="E113" s="15"/>
-      <c r="F113" s="6" t="s">
-        <v>150</v>
-      </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="11"/>
-      <c r="B114" s="20"/>
-      <c r="C114" s="21"/>
-      <c r="D114" s="21"/>
-      <c r="E114" s="22"/>
-      <c r="F114" s="21"/>
+      <c r="A114" s="37"/>
+      <c r="B114" s="49"/>
+      <c r="C114" s="15"/>
+      <c r="D114" s="15"/>
+      <c r="E114" s="16"/>
+      <c r="F114" s="15"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="11"/>
-      <c r="B115" s="17" t="s">
+      <c r="A115" s="37"/>
+      <c r="B115" s="48" t="s">
+        <v>260</v>
+      </c>
+      <c r="C115" s="6" t="s">
+        <v>259</v>
+      </c>
+      <c r="D115" s="6" t="s">
         <v>262</v>
       </c>
-      <c r="C115" s="6" t="s">
+      <c r="E115" s="11"/>
+      <c r="F115" s="6" t="s">
+        <v>256</v>
+      </c>
+    </row>
+    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A116" s="37"/>
+      <c r="B116" s="45"/>
+      <c r="C116" s="6" t="s">
         <v>261</v>
       </c>
-      <c r="D115" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="E115" s="15"/>
-      <c r="F115" s="6" t="s">
-        <v>258</v>
-      </c>
-    </row>
-    <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="11"/>
-      <c r="B116" s="12"/>
-      <c r="C116" s="6" t="s">
+      <c r="D116" s="6" t="s">
         <v>263</v>
       </c>
-      <c r="D116" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="E116" s="15"/>
+      <c r="E116" s="11"/>
       <c r="F116" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="29"/>
-      <c r="B117" s="30"/>
-      <c r="C117" s="31"/>
-      <c r="D117" s="31"/>
-      <c r="E117" s="32"/>
-      <c r="F117" s="31"/>
+      <c r="A117" s="38"/>
+      <c r="B117" s="46"/>
+      <c r="C117" s="19"/>
+      <c r="D117" s="19"/>
+      <c r="E117" s="20"/>
+      <c r="F117" s="19"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="7" t="s">
-        <v>164</v>
-      </c>
-      <c r="B118" s="8" t="s">
+      <c r="A118" s="36" t="s">
+        <v>163</v>
+      </c>
+      <c r="B118" s="47" t="s">
         <v>13</v>
       </c>
-      <c r="C118" s="9" t="s">
-        <v>174</v>
-      </c>
-      <c r="D118" s="9" t="s">
+      <c r="C118" s="7" t="s">
         <v>173</v>
       </c>
-      <c r="E118" s="9"/>
-      <c r="F118" s="9" t="s">
-        <v>141</v>
+      <c r="D118" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E118" s="7"/>
+      <c r="F118" s="7" t="s">
+        <v>140</v>
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="39"/>
-      <c r="B119" s="12"/>
+      <c r="B119" s="45"/>
       <c r="C119" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D119" s="6" t="s">
         <v>175</v>
       </c>
-      <c r="D119" s="6" t="s">
-        <v>176</v>
-      </c>
       <c r="F119" s="6" t="s">
-        <v>141</v>
+        <v>140</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="39"/>
-      <c r="B120" s="20"/>
-      <c r="C120" s="21"/>
-      <c r="D120" s="21"/>
-      <c r="E120" s="21"/>
-      <c r="F120" s="21"/>
+      <c r="B120" s="49"/>
+      <c r="C120" s="15"/>
+      <c r="D120" s="15"/>
+      <c r="E120" s="15"/>
+      <c r="F120" s="15"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="39"/>
-      <c r="B121" s="17" t="s">
-        <v>184</v>
+      <c r="B121" s="48" t="s">
+        <v>183</v>
       </c>
       <c r="C121" s="6" t="s">
-        <v>166</v>
+        <v>165</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>165</v>
+        <v>164</v>
       </c>
       <c r="F121" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A122" s="39"/>
-      <c r="B122" s="12"/>
+      <c r="B122" s="45"/>
       <c r="C122" s="6" t="s">
-        <v>182</v>
+        <v>181</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>311</v>
+        <v>309</v>
       </c>
       <c r="F122" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A123" s="39"/>
-      <c r="B123" s="12"/>
+      <c r="B123" s="45"/>
       <c r="C123" s="6" t="s">
-        <v>178</v>
+        <v>177</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>177</v>
+        <v>176</v>
       </c>
       <c r="F123" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A124" s="39"/>
-      <c r="B124" s="12"/>
+      <c r="B124" s="45"/>
       <c r="C124" s="6" t="s">
-        <v>180</v>
+        <v>179</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>179</v>
+        <v>178</v>
       </c>
       <c r="F124" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="39"/>
-      <c r="B125" s="12"/>
+      <c r="B125" s="45"/>
       <c r="C125" s="6" t="s">
-        <v>183</v>
+        <v>182</v>
       </c>
       <c r="D125" s="6" t="s">
-        <v>181</v>
+        <v>180</v>
       </c>
       <c r="F125" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="39"/>
-      <c r="B126" s="12"/>
+      <c r="B126" s="45"/>
       <c r="C126" s="6" t="s">
-        <v>193</v>
+        <v>191</v>
       </c>
       <c r="D126" s="6" t="s">
-        <v>189</v>
+        <v>187</v>
       </c>
       <c r="F126" s="6" t="s">
-        <v>150</v>
+        <v>149</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="39"/>
-      <c r="B127" s="12"/>
+      <c r="B127" s="45"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="39"/>
-      <c r="B128" s="17" t="s">
+      <c r="B128" s="48" t="s">
+        <v>206</v>
+      </c>
+      <c r="C128" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D128" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E128" s="13"/>
+      <c r="F128" s="13" t="s">
         <v>208</v>
-      </c>
-      <c r="C128" s="18" t="s">
-        <v>205</v>
-      </c>
-      <c r="D128" s="18" t="s">
-        <v>209</v>
-      </c>
-      <c r="E128" s="18"/>
-      <c r="F128" s="18" t="s">
-        <v>210</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="39"/>
-      <c r="B129" s="12"/>
+      <c r="B129" s="45"/>
       <c r="C129" s="6" t="s">
-        <v>206</v>
+        <v>204</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>212</v>
+        <v>210</v>
       </c>
       <c r="F129" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A130" s="39"/>
-      <c r="B130" s="12"/>
+      <c r="B130" s="45"/>
       <c r="C130" s="6" t="s">
-        <v>217</v>
+        <v>215</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>216</v>
+        <v>214</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>221</v>
+        <v>219</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="39"/>
-      <c r="B131" s="12"/>
+      <c r="B131" s="45"/>
       <c r="C131" s="6" t="s">
-        <v>207</v>
+        <v>205</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>211</v>
+        <v>209</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>210</v>
+        <v>208</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="39"/>
-      <c r="B132" s="12"/>
+      <c r="B132" s="45"/>
       <c r="C132" s="6" t="s">
-        <v>312</v>
+        <v>310</v>
       </c>
       <c r="D132" s="6" t="s">
-        <v>313</v>
+        <v>311</v>
       </c>
       <c r="F132" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="39"/>
-      <c r="B133" s="12"/>
+      <c r="B133" s="45"/>
       <c r="C133" s="6" t="s">
-        <v>336</v>
+        <v>334</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>337</v>
+        <v>335</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="39"/>
-      <c r="B134" s="12"/>
+      <c r="B134" s="45"/>
       <c r="C134" s="6" t="s">
-        <v>338</v>
+        <v>336</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>339</v>
+        <v>337</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>316</v>
+        <v>314</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="39"/>
-      <c r="B135" s="12"/>
+      <c r="B135" s="45"/>
       <c r="C135" s="6" t="s">
-        <v>219</v>
+        <v>217</v>
       </c>
       <c r="D135" s="6" t="s">
+        <v>216</v>
+      </c>
+      <c r="F135" s="6" t="s">
         <v>218</v>
-      </c>
-      <c r="F135" s="6" t="s">
-        <v>220</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="39"/>
-      <c r="B136" s="12"/>
+      <c r="B136" s="45"/>
       <c r="C136" s="6" t="s">
-        <v>223</v>
+        <v>221</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>213</v>
+        <v>211</v>
       </c>
       <c r="F136" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A137" s="39"/>
-      <c r="B137" s="12"/>
+      <c r="B137" s="45"/>
       <c r="C137" s="6" t="s">
-        <v>204</v>
+        <v>202</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>222</v>
+        <v>220</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="39"/>
-      <c r="B138" s="12"/>
+      <c r="B138" s="45"/>
       <c r="C138" s="6" t="s">
-        <v>266</v>
+        <v>264</v>
       </c>
       <c r="D138" s="6" t="s">
-        <v>371</v>
+        <v>369</v>
       </c>
       <c r="F138" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="39"/>
-      <c r="B139" s="12"/>
+      <c r="B139" s="45"/>
       <c r="C139" s="6" t="s">
-        <v>268</v>
+        <v>266</v>
       </c>
       <c r="D139" s="6" t="s">
-        <v>267</v>
+        <v>265</v>
       </c>
       <c r="F139" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="39"/>
-      <c r="B140" s="12"/>
+      <c r="B140" s="45"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="39"/>
-      <c r="B141" s="17" t="s">
+      <c r="B141" s="48" t="s">
+        <v>222</v>
+      </c>
+      <c r="C141" s="13" t="s">
         <v>224</v>
       </c>
-      <c r="C141" s="18" t="s">
-        <v>226</v>
-      </c>
-      <c r="D141" s="18" t="s">
-        <v>225</v>
-      </c>
-      <c r="E141" s="18"/>
-      <c r="F141" s="18" t="s">
-        <v>210</v>
+      <c r="D141" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E141" s="13"/>
+      <c r="F141" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="39"/>
-      <c r="B142" s="33"/>
+      <c r="B142" s="50"/>
       <c r="C142" s="6" t="s">
+        <v>312</v>
+      </c>
+      <c r="D142" s="6" t="s">
+        <v>313</v>
+      </c>
+      <c r="F142" s="6" t="s">
         <v>314</v>
-      </c>
-      <c r="D142" s="6" t="s">
-        <v>315</v>
-      </c>
-      <c r="F142" s="6" t="s">
-        <v>316</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="39"/>
-      <c r="B143" s="33"/>
+      <c r="B143" s="50"/>
       <c r="C143" s="6" t="s">
-        <v>227</v>
+        <v>225</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>228</v>
+        <v>226</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="39"/>
-      <c r="B144" s="33"/>
+      <c r="B144" s="50"/>
       <c r="C144" s="6" t="s">
-        <v>269</v>
+        <v>267</v>
       </c>
       <c r="D144" s="6" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="F144" s="6" t="s">
-        <v>214</v>
+        <v>212</v>
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="39"/>
-      <c r="B145" s="33"/>
+      <c r="B145" s="50"/>
       <c r="C145" s="6" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="D145" s="6" t="s">
-        <v>310</v>
+        <v>308</v>
       </c>
       <c r="F145" s="6" t="s">
-        <v>215</v>
+        <v>213</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="39"/>
-      <c r="B146" s="20"/>
+      <c r="B146" s="49"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="39"/>
-      <c r="B147" s="17" t="s">
+      <c r="B147" s="48" t="s">
+        <v>380</v>
+      </c>
+      <c r="C147" s="13" t="s">
+        <v>381</v>
+      </c>
+      <c r="D147" s="13" t="s">
         <v>382</v>
       </c>
-      <c r="C147" s="18" t="s">
-        <v>383</v>
-      </c>
-      <c r="D147" s="18" t="s">
-        <v>384</v>
-      </c>
-      <c r="E147" s="18"/>
-      <c r="F147" s="18" t="s">
-        <v>275</v>
+      <c r="E147" s="13"/>
+      <c r="F147" s="13" t="s">
+        <v>273</v>
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A148" s="39"/>
-      <c r="B148" s="12"/>
+      <c r="B148" s="45"/>
       <c r="C148" s="6" t="s">
-        <v>385</v>
+        <v>383</v>
       </c>
       <c r="D148" s="6" t="s">
-        <v>386</v>
+        <v>384</v>
       </c>
       <c r="F148" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
@@ -5164,6 +5164,15 @@
     </row>
   </sheetData>
   <mergeCells count="25">
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A117"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="B78:B80"/>
     <mergeCell ref="B147:B148"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="A118:A149"/>
@@ -5180,15 +5189,6 @@
     <mergeCell ref="B115:B117"/>
     <mergeCell ref="B121:B127"/>
     <mergeCell ref="B128:B140"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A117"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B78:B80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Bio_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_Brownfield_Leuna/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Leuna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{523E8C33-20C8-41EC-A865-1569DF69AC8E}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0E4E71-4D41-4D6A-B7BD-F5383D5091DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -1343,10 +1343,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="164" formatCode="0.0000"/>
-    <numFmt numFmtId="165" formatCode="0.000"/>
-    <numFmt numFmtId="166" formatCode="0.00000"/>
+    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="165" formatCode="0.0000"/>
+    <numFmt numFmtId="166" formatCode="0.000"/>
+    <numFmt numFmtId="167" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1478,94 +1478,85 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="51">
+  <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
+    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="center"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" vertical="top"/>
-    </xf>
-    <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
   </cellXfs>
@@ -1894,7 +1885,7 @@
   <sheetFormatPr baseColWidth="10" defaultColWidth="8.88671875" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="10.88671875" style="6" customWidth="1"/>
-    <col min="2" max="2" width="18.6640625" style="25" customWidth="1"/>
+    <col min="2" max="2" width="18.6640625" style="23" customWidth="1"/>
     <col min="3" max="3" width="36.21875" style="6" bestFit="1" customWidth="1"/>
     <col min="4" max="4" width="21" style="6" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="19" style="11" bestFit="1" customWidth="1"/>
@@ -1926,13 +1917,13 @@
       <c r="F1" s="4" t="s">
         <v>1</v>
       </c>
-      <c r="G1" s="25"/>
+      <c r="G1" s="23"/>
     </row>
     <row r="2" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="43" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -1949,8 +1940,8 @@
       </c>
     </row>
     <row r="3" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A3" s="37"/>
-      <c r="B3" s="45"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="6" t="s">
         <v>84</v>
       </c>
@@ -1965,8 +1956,8 @@
       </c>
     </row>
     <row r="4" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
-      <c r="B4" s="45"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="6" t="s">
         <v>10</v>
       </c>
@@ -1974,15 +1965,15 @@
         <v>26</v>
       </c>
       <c r="E4" s="10">
-        <v>1000</v>
+        <v>1500</v>
       </c>
       <c r="F4" s="6" t="s">
         <v>83</v>
       </c>
     </row>
     <row r="5" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
-      <c r="B5" s="45"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="6" t="s">
         <v>11</v>
       </c>
@@ -1997,8 +1988,8 @@
       </c>
     </row>
     <row r="6" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
-      <c r="B6" s="45"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="6" t="s">
         <v>13</v>
       </c>
@@ -2013,8 +2004,8 @@
       </c>
     </row>
     <row r="7" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="45"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="6" t="s">
         <v>15</v>
       </c>
@@ -2029,8 +2020,8 @@
       </c>
     </row>
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="B8" s="48" t="s">
+      <c r="A8" s="34"/>
+      <c r="B8" s="44" t="s">
         <v>229</v>
       </c>
       <c r="C8" s="13" t="s">
@@ -2047,8 +2038,8 @@
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
-      <c r="B9" s="45"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="6" t="s">
         <v>85</v>
       </c>
@@ -2063,8 +2054,8 @@
       </c>
     </row>
     <row r="10" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="6" t="s">
         <v>10</v>
       </c>
@@ -2079,8 +2070,8 @@
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
-      <c r="B11" s="45"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="41"/>
       <c r="C11" s="6" t="s">
         <v>11</v>
       </c>
@@ -2095,8 +2086,8 @@
       </c>
     </row>
     <row r="12" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
-      <c r="B12" s="45"/>
+      <c r="A12" s="34"/>
+      <c r="B12" s="41"/>
       <c r="C12" s="6" t="s">
         <v>86</v>
       </c>
@@ -2111,8 +2102,8 @@
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="6" t="s">
         <v>244</v>
       </c>
@@ -2127,8 +2118,8 @@
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
-      <c r="B14" s="45"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="6" t="s">
         <v>13</v>
       </c>
@@ -2143,8 +2134,8 @@
       </c>
     </row>
     <row r="15" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
-      <c r="B15" s="49"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="45"/>
       <c r="C15" s="15" t="s">
         <v>15</v>
       </c>
@@ -2159,8 +2150,8 @@
       </c>
     </row>
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
-      <c r="B16" s="48" t="s">
+      <c r="A16" s="34"/>
+      <c r="B16" s="44" t="s">
         <v>271</v>
       </c>
       <c r="C16" s="13" t="s">
@@ -2177,8 +2168,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
-      <c r="B17" s="45"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="41"/>
       <c r="C17" s="6" t="s">
         <v>84</v>
       </c>
@@ -2193,8 +2184,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="6" t="s">
         <v>10</v>
       </c>
@@ -2209,8 +2200,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="45"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="6" t="s">
         <v>11</v>
       </c>
@@ -2225,8 +2216,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="45"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="41"/>
       <c r="C20" s="6" t="s">
         <v>13</v>
       </c>
@@ -2241,8 +2232,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
-      <c r="B21" s="49"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="45"/>
       <c r="C21" s="15" t="s">
         <v>15</v>
       </c>
@@ -2257,8 +2248,8 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
-      <c r="B22" s="41" t="s">
+      <c r="A22" s="34"/>
+      <c r="B22" s="37" t="s">
         <v>340</v>
       </c>
       <c r="C22" s="6" t="s">
@@ -2275,8 +2266,8 @@
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
-      <c r="B23" s="41"/>
+      <c r="A23" s="34"/>
+      <c r="B23" s="37"/>
       <c r="C23" s="6" t="s">
         <v>281</v>
       </c>
@@ -2291,8 +2282,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
-      <c r="B24" s="41"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="37"/>
       <c r="C24" s="6" t="s">
         <v>10</v>
       </c>
@@ -2307,8 +2298,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" s="41"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="37"/>
       <c r="C25" s="6" t="s">
         <v>377</v>
       </c>
@@ -2323,8 +2314,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
-      <c r="B26" s="41"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="37"/>
       <c r="C26" s="6" t="s">
         <v>370</v>
       </c>
@@ -2339,8 +2330,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
-      <c r="B27" s="41"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="37"/>
       <c r="C27" s="6" t="s">
         <v>353</v>
       </c>
@@ -2355,8 +2346,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
-      <c r="B28" s="41"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="37"/>
       <c r="C28" s="6" t="s">
         <v>378</v>
       </c>
@@ -2371,8 +2362,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
-      <c r="B29" s="41"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="37"/>
       <c r="C29" s="6" t="s">
         <v>13</v>
       </c>
@@ -2387,8 +2378,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A30" s="37"/>
-      <c r="B30" s="41"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="37"/>
       <c r="C30" s="6" t="s">
         <v>15</v>
       </c>
@@ -2403,10 +2394,10 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="36" t="s">
+      <c r="A31" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="B31" s="40" t="s">
+      <c r="B31" s="36" t="s">
         <v>3</v>
       </c>
       <c r="C31" s="7" t="s">
@@ -2423,8 +2414,8 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
-      <c r="B32" s="41"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="37"/>
       <c r="C32" s="6" t="s">
         <v>11</v>
       </c>
@@ -2439,8 +2430,8 @@
       </c>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
-      <c r="B33" s="41"/>
+      <c r="A33" s="34"/>
+      <c r="B33" s="37"/>
       <c r="C33" s="6" t="s">
         <v>13</v>
       </c>
@@ -2455,15 +2446,15 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
-      <c r="B34" s="41"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="6" t="s">
         <v>20</v>
       </c>
       <c r="D34" s="6" t="s">
         <v>34</v>
       </c>
-      <c r="E34" s="26">
+      <c r="E34" s="24">
         <v>1.0000000000000001E-5</v>
       </c>
       <c r="F34" s="6" t="s">
@@ -2471,8 +2462,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
-      <c r="B35" s="41"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="6" t="s">
         <v>35</v>
       </c>
@@ -2487,8 +2478,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
-      <c r="B36" s="41"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="6" t="s">
         <v>36</v>
       </c>
@@ -2503,8 +2494,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
-      <c r="B37" s="41"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="6" t="s">
         <v>15</v>
       </c>
@@ -2519,8 +2510,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A38" s="37"/>
-      <c r="B38" s="42"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="38"/>
       <c r="C38" s="15" t="s">
         <v>88</v>
       </c>
@@ -2535,8 +2526,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
-      <c r="B39" s="43" t="s">
+      <c r="A39" s="34"/>
+      <c r="B39" s="39" t="s">
         <v>315</v>
       </c>
       <c r="C39" s="7" t="s">
@@ -2553,8 +2544,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
-      <c r="B40" s="41"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="6" t="s">
         <v>11</v>
       </c>
@@ -2569,8 +2560,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
-      <c r="B41" s="41"/>
+      <c r="A41" s="34"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="6" t="s">
         <v>13</v>
       </c>
@@ -2585,8 +2576,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
-      <c r="B42" s="41"/>
+      <c r="A42" s="34"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="6" t="s">
         <v>20</v>
       </c>
@@ -2601,8 +2592,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="37"/>
-      <c r="B43" s="41"/>
+      <c r="A43" s="34"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="6" t="s">
         <v>35</v>
       </c>
@@ -2617,8 +2608,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
-      <c r="B44" s="41"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="6" t="s">
         <v>36</v>
       </c>
@@ -2633,8 +2624,8 @@
       </c>
     </row>
     <row r="45" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A45" s="37"/>
-      <c r="B45" s="41"/>
+      <c r="A45" s="34"/>
+      <c r="B45" s="37"/>
       <c r="C45" s="6" t="s">
         <v>15</v>
       </c>
@@ -2649,8 +2640,8 @@
       </c>
     </row>
     <row r="46" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A46" s="37"/>
-      <c r="B46" s="41"/>
+      <c r="A46" s="34"/>
+      <c r="B46" s="37"/>
       <c r="C46" s="15" t="s">
         <v>88</v>
       </c>
@@ -2665,8 +2656,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
-      <c r="B47" s="43" t="s">
+      <c r="A47" s="34"/>
+      <c r="B47" s="39" t="s">
         <v>201</v>
       </c>
       <c r="C47" s="13" t="s">
@@ -2683,8 +2674,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
-      <c r="B48" s="45"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="41"/>
       <c r="C48" s="6" t="s">
         <v>21</v>
       </c>
@@ -2700,8 +2691,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
-      <c r="B49" s="45"/>
+      <c r="A49" s="34"/>
+      <c r="B49" s="41"/>
       <c r="C49" s="6" t="s">
         <v>16</v>
       </c>
@@ -2716,8 +2707,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
-      <c r="B50" s="45"/>
+      <c r="A50" s="34"/>
+      <c r="B50" s="41"/>
       <c r="C50" s="6" t="s">
         <v>17</v>
       </c>
@@ -2732,8 +2723,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
-      <c r="B51" s="45"/>
+      <c r="A51" s="34"/>
+      <c r="B51" s="41"/>
       <c r="C51" s="6" t="s">
         <v>35</v>
       </c>
@@ -2748,8 +2739,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
-      <c r="B52" s="45"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="41"/>
       <c r="C52" s="6" t="s">
         <v>36</v>
       </c>
@@ -2764,8 +2755,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
-      <c r="B53" s="45"/>
+      <c r="A53" s="34"/>
+      <c r="B53" s="41"/>
       <c r="C53" s="6" t="s">
         <v>89</v>
       </c>
@@ -2780,8 +2771,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="37"/>
-      <c r="B54" s="45"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="41"/>
       <c r="C54" s="6" t="s">
         <v>88</v>
       </c>
@@ -2796,8 +2787,8 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="37"/>
-      <c r="B55" s="45"/>
+      <c r="A55" s="34"/>
+      <c r="B55" s="41"/>
       <c r="C55" s="6" t="s">
         <v>13</v>
       </c>
@@ -2812,8 +2803,8 @@
       </c>
     </row>
     <row r="56" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A56" s="38"/>
-      <c r="B56" s="46"/>
+      <c r="A56" s="35"/>
+      <c r="B56" s="42"/>
       <c r="C56" s="19" t="s">
         <v>15</v>
       </c>
@@ -2828,46 +2819,46 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="36" t="s">
+      <c r="A57" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="B57" s="33" t="s">
+      <c r="B57" s="31" t="s">
         <v>73</v>
       </c>
-      <c r="C57" s="28" t="s">
+      <c r="C57" s="26" t="s">
         <v>74</v>
       </c>
-      <c r="D57" s="28" t="s">
+      <c r="D57" s="26" t="s">
         <v>75</v>
       </c>
-      <c r="E57" s="29">
+      <c r="E57" s="27">
         <v>0.1699</v>
       </c>
-      <c r="F57" s="28" t="s">
+      <c r="F57" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="39"/>
-      <c r="B58" s="34" t="s">
+      <c r="A58" s="34"/>
+      <c r="B58" s="32" t="s">
         <v>341</v>
       </c>
-      <c r="C58" s="21" t="s">
+      <c r="C58" s="6" t="s">
         <v>342</v>
       </c>
-      <c r="D58" s="21" t="s">
+      <c r="D58" s="6" t="s">
         <v>343</v>
       </c>
-      <c r="E58" s="35">
+      <c r="E58" s="11">
         <v>0</v>
       </c>
-      <c r="F58" s="21" t="s">
+      <c r="F58" s="6" t="s">
         <v>212</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="37"/>
-      <c r="B59" s="43" t="s">
+      <c r="A59" s="34"/>
+      <c r="B59" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C59" s="13" t="s">
@@ -2884,8 +2875,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
-      <c r="B60" s="41"/>
+      <c r="A60" s="34"/>
+      <c r="B60" s="37"/>
       <c r="C60" s="6" t="s">
         <v>10</v>
       </c>
@@ -2900,8 +2891,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
-      <c r="B61" s="41"/>
+      <c r="A61" s="34"/>
+      <c r="B61" s="37"/>
       <c r="C61" s="6" t="s">
         <v>17</v>
       </c>
@@ -2916,8 +2907,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="37"/>
-      <c r="B62" s="41"/>
+      <c r="A62" s="34"/>
+      <c r="B62" s="37"/>
       <c r="C62" s="6" t="s">
         <v>18</v>
       </c>
@@ -2932,8 +2923,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
-      <c r="B63" s="41"/>
+      <c r="A63" s="34"/>
+      <c r="B63" s="37"/>
       <c r="C63" s="6" t="s">
         <v>13</v>
       </c>
@@ -2948,8 +2939,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
-      <c r="B64" s="41"/>
+      <c r="A64" s="34"/>
+      <c r="B64" s="37"/>
       <c r="C64" s="6" t="s">
         <v>68</v>
       </c>
@@ -2964,8 +2955,8 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
-      <c r="B65" s="42"/>
+      <c r="A65" s="34"/>
+      <c r="B65" s="38"/>
       <c r="C65" s="15" t="s">
         <v>15</v>
       </c>
@@ -2980,8 +2971,8 @@
       </c>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
-      <c r="B66" s="43" t="s">
+      <c r="A66" s="34"/>
+      <c r="B66" s="39" t="s">
         <v>5</v>
       </c>
       <c r="C66" s="13" t="s">
@@ -2998,8 +2989,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
-      <c r="B67" s="41"/>
+      <c r="A67" s="34"/>
+      <c r="B67" s="37"/>
       <c r="C67" s="6" t="s">
         <v>10</v>
       </c>
@@ -3014,8 +3005,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
-      <c r="B68" s="41"/>
+      <c r="A68" s="34"/>
+      <c r="B68" s="37"/>
       <c r="C68" s="6" t="s">
         <v>17</v>
       </c>
@@ -3030,8 +3021,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
-      <c r="B69" s="41"/>
+      <c r="A69" s="34"/>
+      <c r="B69" s="37"/>
       <c r="C69" s="6" t="s">
         <v>18</v>
       </c>
@@ -3046,8 +3037,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
-      <c r="B70" s="41"/>
+      <c r="A70" s="34"/>
+      <c r="B70" s="37"/>
       <c r="C70" s="6" t="s">
         <v>13</v>
       </c>
@@ -3062,15 +3053,15 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
-      <c r="B71" s="41"/>
+      <c r="A71" s="34"/>
+      <c r="B71" s="37"/>
       <c r="C71" s="6" t="s">
         <v>68</v>
       </c>
       <c r="D71" s="6" t="s">
         <v>65</v>
       </c>
-      <c r="E71" s="24">
+      <c r="E71" s="22">
         <v>1000000</v>
       </c>
       <c r="F71" s="6" t="s">
@@ -3078,8 +3069,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="38"/>
-      <c r="B72" s="44"/>
+      <c r="A72" s="35"/>
+      <c r="B72" s="40"/>
       <c r="C72" s="19" t="s">
         <v>15</v>
       </c>
@@ -3094,28 +3085,28 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="36" t="s">
+      <c r="A73" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="B73" s="27" t="s">
+      <c r="B73" s="25" t="s">
         <v>73</v>
       </c>
-      <c r="C73" s="28" t="s">
+      <c r="C73" s="26" t="s">
         <v>77</v>
       </c>
-      <c r="D73" s="28" t="s">
+      <c r="D73" s="26" t="s">
         <v>78</v>
       </c>
-      <c r="E73" s="29">
+      <c r="E73" s="27">
         <v>-1E-4</v>
       </c>
-      <c r="F73" s="28" t="s">
+      <c r="F73" s="26" t="s">
         <v>19</v>
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
-      <c r="B74" s="25" t="s">
+      <c r="A74" s="34"/>
+      <c r="B74" s="23" t="s">
         <v>297</v>
       </c>
       <c r="C74" s="6" t="s">
@@ -3132,25 +3123,25 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
-      <c r="B75" s="30" t="s">
+      <c r="A75" s="34"/>
+      <c r="B75" s="28" t="s">
         <v>79</v>
       </c>
-      <c r="C75" s="31" t="s">
+      <c r="C75" s="29" t="s">
         <v>80</v>
       </c>
-      <c r="D75" s="31" t="s">
+      <c r="D75" s="29" t="s">
         <v>81</v>
       </c>
-      <c r="E75" s="32">
+      <c r="E75" s="30">
         <v>-1.5</v>
       </c>
-      <c r="F75" s="31" t="s">
+      <c r="F75" s="29" t="s">
         <v>82</v>
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="38"/>
+      <c r="A76" s="35"/>
       <c r="B76" s="4" t="s">
         <v>260</v>
       </c>
@@ -3224,10 +3215,10 @@
       </c>
     </row>
     <row r="2" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A2" s="36" t="s">
+      <c r="A2" s="33" t="s">
         <v>70</v>
       </c>
-      <c r="B2" s="47" t="s">
+      <c r="B2" s="43" t="s">
         <v>0</v>
       </c>
       <c r="C2" s="7" t="s">
@@ -3242,8 +3233,8 @@
       </c>
     </row>
     <row r="3" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A3" s="37"/>
-      <c r="B3" s="45"/>
+      <c r="A3" s="34"/>
+      <c r="B3" s="41"/>
       <c r="C3" s="6" t="s">
         <v>107</v>
       </c>
@@ -3256,8 +3247,8 @@
       </c>
     </row>
     <row r="4" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A4" s="37"/>
-      <c r="B4" s="45"/>
+      <c r="A4" s="34"/>
+      <c r="B4" s="41"/>
       <c r="C4" s="6" t="s">
         <v>84</v>
       </c>
@@ -3270,8 +3261,8 @@
       </c>
     </row>
     <row r="5" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A5" s="37"/>
-      <c r="B5" s="45"/>
+      <c r="A5" s="34"/>
+      <c r="B5" s="41"/>
       <c r="C5" s="6" t="s">
         <v>138</v>
       </c>
@@ -3284,8 +3275,8 @@
       </c>
     </row>
     <row r="6" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A6" s="37"/>
-      <c r="B6" s="45"/>
+      <c r="A6" s="34"/>
+      <c r="B6" s="41"/>
       <c r="C6" s="6" t="s">
         <v>141</v>
       </c>
@@ -3298,8 +3289,8 @@
       </c>
     </row>
     <row r="7" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A7" s="37"/>
-      <c r="B7" s="45"/>
+      <c r="A7" s="34"/>
+      <c r="B7" s="41"/>
       <c r="C7" s="6" t="s">
         <v>155</v>
       </c>
@@ -3312,8 +3303,8 @@
       </c>
     </row>
     <row r="8" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A8" s="37"/>
-      <c r="B8" s="45"/>
+      <c r="A8" s="34"/>
+      <c r="B8" s="41"/>
       <c r="C8" s="6" t="s">
         <v>196</v>
       </c>
@@ -3326,8 +3317,8 @@
       </c>
     </row>
     <row r="9" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A9" s="37"/>
-      <c r="B9" s="45"/>
+      <c r="A9" s="34"/>
+      <c r="B9" s="41"/>
       <c r="C9" s="6" t="s">
         <v>167</v>
       </c>
@@ -3340,8 +3331,8 @@
       </c>
     </row>
     <row r="10" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A10" s="37"/>
-      <c r="B10" s="45"/>
+      <c r="A10" s="34"/>
+      <c r="B10" s="41"/>
       <c r="C10" s="6" t="s">
         <v>188</v>
       </c>
@@ -3354,13 +3345,13 @@
       </c>
     </row>
     <row r="11" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A11" s="37"/>
-      <c r="B11" s="45"/>
+      <c r="A11" s="34"/>
+      <c r="B11" s="41"/>
       <c r="E11" s="11"/>
     </row>
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A12" s="37"/>
-      <c r="B12" s="48" t="s">
+      <c r="A12" s="34"/>
+      <c r="B12" s="44" t="s">
         <v>229</v>
       </c>
       <c r="C12" s="13" t="s">
@@ -3375,8 +3366,8 @@
       </c>
     </row>
     <row r="13" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A13" s="37"/>
-      <c r="B13" s="45"/>
+      <c r="A13" s="34"/>
+      <c r="B13" s="41"/>
       <c r="C13" s="6" t="s">
         <v>253</v>
       </c>
@@ -3389,8 +3380,8 @@
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A14" s="37"/>
-      <c r="B14" s="45"/>
+      <c r="A14" s="34"/>
+      <c r="B14" s="41"/>
       <c r="C14" s="6" t="s">
         <v>139</v>
       </c>
@@ -3403,8 +3394,8 @@
       </c>
     </row>
     <row r="15" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A15" s="37"/>
-      <c r="B15" s="45"/>
+      <c r="A15" s="34"/>
+      <c r="B15" s="41"/>
       <c r="C15" s="6" t="s">
         <v>254</v>
       </c>
@@ -3417,8 +3408,8 @@
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A16" s="37"/>
-      <c r="B16" s="45"/>
+      <c r="A16" s="34"/>
+      <c r="B16" s="41"/>
       <c r="C16" s="6" t="s">
         <v>84</v>
       </c>
@@ -3431,8 +3422,8 @@
       </c>
     </row>
     <row r="17" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A17" s="37"/>
-      <c r="B17" s="45"/>
+      <c r="A17" s="34"/>
+      <c r="B17" s="41"/>
       <c r="C17" s="6" t="s">
         <v>141</v>
       </c>
@@ -3445,8 +3436,8 @@
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A18" s="37"/>
-      <c r="B18" s="45"/>
+      <c r="A18" s="34"/>
+      <c r="B18" s="41"/>
       <c r="C18" s="6" t="s">
         <v>155</v>
       </c>
@@ -3459,8 +3450,8 @@
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A19" s="37"/>
-      <c r="B19" s="45"/>
+      <c r="A19" s="34"/>
+      <c r="B19" s="41"/>
       <c r="C19" s="6" t="s">
         <v>196</v>
       </c>
@@ -3473,8 +3464,8 @@
       </c>
     </row>
     <row r="20" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A20" s="37"/>
-      <c r="B20" s="45"/>
+      <c r="A20" s="34"/>
+      <c r="B20" s="41"/>
       <c r="C20" s="6" t="s">
         <v>167</v>
       </c>
@@ -3487,8 +3478,8 @@
       </c>
     </row>
     <row r="21" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A21" s="37"/>
-      <c r="B21" s="45"/>
+      <c r="A21" s="34"/>
+      <c r="B21" s="41"/>
       <c r="C21" s="6" t="s">
         <v>188</v>
       </c>
@@ -3501,16 +3492,16 @@
       </c>
     </row>
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A22" s="37"/>
-      <c r="B22" s="49"/>
+      <c r="A22" s="34"/>
+      <c r="B22" s="45"/>
       <c r="C22" s="15"/>
       <c r="D22" s="15"/>
       <c r="E22" s="16"/>
       <c r="F22" s="15"/>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A23" s="37"/>
-      <c r="B23" s="48" t="s">
+      <c r="A23" s="34"/>
+      <c r="B23" s="44" t="s">
         <v>271</v>
       </c>
       <c r="C23" s="6" t="s">
@@ -3525,8 +3516,8 @@
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A24" s="37"/>
-      <c r="B24" s="45"/>
+      <c r="A24" s="34"/>
+      <c r="B24" s="41"/>
       <c r="C24" s="6" t="s">
         <v>107</v>
       </c>
@@ -3539,8 +3530,8 @@
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A25" s="37"/>
-      <c r="B25" s="45"/>
+      <c r="A25" s="34"/>
+      <c r="B25" s="41"/>
       <c r="C25" s="6" t="s">
         <v>84</v>
       </c>
@@ -3553,8 +3544,8 @@
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A26" s="37"/>
-      <c r="B26" s="45"/>
+      <c r="A26" s="34"/>
+      <c r="B26" s="41"/>
       <c r="C26" s="6" t="s">
         <v>293</v>
       </c>
@@ -3567,8 +3558,8 @@
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A27" s="37"/>
-      <c r="B27" s="45"/>
+      <c r="A27" s="34"/>
+      <c r="B27" s="41"/>
       <c r="C27" s="6" t="s">
         <v>141</v>
       </c>
@@ -3581,8 +3572,8 @@
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A28" s="37"/>
-      <c r="B28" s="45"/>
+      <c r="A28" s="34"/>
+      <c r="B28" s="41"/>
       <c r="C28" s="6" t="s">
         <v>155</v>
       </c>
@@ -3595,8 +3586,8 @@
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A29" s="37"/>
-      <c r="B29" s="45"/>
+      <c r="A29" s="34"/>
+      <c r="B29" s="41"/>
       <c r="C29" s="6" t="s">
         <v>196</v>
       </c>
@@ -3609,8 +3600,8 @@
       </c>
     </row>
     <row r="30" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A30" s="37"/>
-      <c r="B30" s="45"/>
+      <c r="A30" s="34"/>
+      <c r="B30" s="41"/>
       <c r="C30" s="6" t="s">
         <v>167</v>
       </c>
@@ -3623,8 +3614,8 @@
       </c>
     </row>
     <row r="31" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A31" s="37"/>
-      <c r="B31" s="45"/>
+      <c r="A31" s="34"/>
+      <c r="B31" s="41"/>
       <c r="C31" s="6" t="s">
         <v>188</v>
       </c>
@@ -3637,16 +3628,16 @@
       </c>
     </row>
     <row r="32" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A32" s="37"/>
-      <c r="B32" s="49"/>
+      <c r="A32" s="34"/>
+      <c r="B32" s="45"/>
       <c r="C32" s="15"/>
       <c r="D32" s="15"/>
       <c r="E32" s="16"/>
       <c r="F32" s="15"/>
     </row>
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A33" s="37"/>
-      <c r="B33" s="41" t="s">
+      <c r="A33" s="34"/>
+      <c r="B33" s="37" t="s">
         <v>358</v>
       </c>
       <c r="C33" s="6" t="s">
@@ -3661,8 +3652,8 @@
       </c>
     </row>
     <row r="34" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A34" s="37"/>
-      <c r="B34" s="41"/>
+      <c r="A34" s="34"/>
+      <c r="B34" s="37"/>
       <c r="C34" s="6" t="s">
         <v>107</v>
       </c>
@@ -3675,8 +3666,8 @@
       </c>
     </row>
     <row r="35" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A35" s="37"/>
-      <c r="B35" s="41"/>
+      <c r="A35" s="34"/>
+      <c r="B35" s="37"/>
       <c r="C35" s="6" t="s">
         <v>84</v>
       </c>
@@ -3689,8 +3680,8 @@
       </c>
     </row>
     <row r="36" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A36" s="37"/>
-      <c r="B36" s="41"/>
+      <c r="A36" s="34"/>
+      <c r="B36" s="37"/>
       <c r="C36" s="6" t="s">
         <v>281</v>
       </c>
@@ -3703,8 +3694,8 @@
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A37" s="37"/>
-      <c r="B37" s="41"/>
+      <c r="A37" s="34"/>
+      <c r="B37" s="37"/>
       <c r="C37" s="6" t="s">
         <v>370</v>
       </c>
@@ -3717,8 +3708,8 @@
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A38" s="37"/>
-      <c r="B38" s="41"/>
+      <c r="A38" s="34"/>
+      <c r="B38" s="37"/>
       <c r="C38" s="6" t="s">
         <v>258</v>
       </c>
@@ -3731,8 +3722,8 @@
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A39" s="37"/>
-      <c r="B39" s="41"/>
+      <c r="A39" s="34"/>
+      <c r="B39" s="37"/>
       <c r="C39" s="6" t="s">
         <v>141</v>
       </c>
@@ -3745,8 +3736,8 @@
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A40" s="37"/>
-      <c r="B40" s="41"/>
+      <c r="A40" s="34"/>
+      <c r="B40" s="37"/>
       <c r="C40" s="6" t="s">
         <v>155</v>
       </c>
@@ -3759,8 +3750,8 @@
       </c>
     </row>
     <row r="41" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A41" s="37"/>
-      <c r="B41" s="41"/>
+      <c r="A41" s="34"/>
+      <c r="B41" s="37"/>
       <c r="C41" s="6" t="s">
         <v>161</v>
       </c>
@@ -3773,8 +3764,8 @@
       </c>
     </row>
     <row r="42" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A42" s="37"/>
-      <c r="B42" s="41"/>
+      <c r="A42" s="34"/>
+      <c r="B42" s="37"/>
       <c r="C42" s="6" t="s">
         <v>196</v>
       </c>
@@ -3787,8 +3778,8 @@
       </c>
     </row>
     <row r="43" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A43" s="37"/>
-      <c r="B43" s="41"/>
+      <c r="A43" s="34"/>
+      <c r="B43" s="37"/>
       <c r="C43" s="6" t="s">
         <v>167</v>
       </c>
@@ -3801,8 +3792,8 @@
       </c>
     </row>
     <row r="44" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A44" s="37"/>
-      <c r="B44" s="41"/>
+      <c r="A44" s="34"/>
+      <c r="B44" s="37"/>
       <c r="C44" s="6" t="s">
         <v>188</v>
       </c>
@@ -3815,15 +3806,15 @@
       </c>
     </row>
     <row r="45" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A45" s="37"/>
-      <c r="B45" s="41"/>
+      <c r="A45" s="34"/>
+      <c r="B45" s="37"/>
       <c r="E45" s="11"/>
     </row>
     <row r="46" spans="1:6" ht="14.4" customHeight="1" x14ac:dyDescent="0.3">
-      <c r="A46" s="36" t="s">
+      <c r="A46" s="33" t="s">
         <v>71</v>
       </c>
-      <c r="B46" s="40" t="s">
+      <c r="B46" s="36" t="s">
         <v>3</v>
       </c>
       <c r="C46" s="7" t="s">
@@ -3838,8 +3829,8 @@
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A47" s="37"/>
-      <c r="B47" s="41"/>
+      <c r="A47" s="34"/>
+      <c r="B47" s="37"/>
       <c r="C47" s="6" t="s">
         <v>111</v>
       </c>
@@ -3852,8 +3843,8 @@
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A48" s="37"/>
-      <c r="B48" s="41"/>
+      <c r="A48" s="34"/>
+      <c r="B48" s="37"/>
       <c r="C48" s="6" t="s">
         <v>135</v>
       </c>
@@ -3866,8 +3857,8 @@
       </c>
     </row>
     <row r="49" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A49" s="37"/>
-      <c r="B49" s="41"/>
+      <c r="A49" s="34"/>
+      <c r="B49" s="37"/>
       <c r="C49" s="6" t="s">
         <v>136</v>
       </c>
@@ -3880,8 +3871,8 @@
       </c>
     </row>
     <row r="50" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A50" s="37"/>
-      <c r="B50" s="41"/>
+      <c r="A50" s="34"/>
+      <c r="B50" s="37"/>
       <c r="C50" s="6" t="s">
         <v>141</v>
       </c>
@@ -3894,8 +3885,8 @@
       </c>
     </row>
     <row r="51" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A51" s="37"/>
-      <c r="B51" s="41"/>
+      <c r="A51" s="34"/>
+      <c r="B51" s="37"/>
       <c r="C51" s="6" t="s">
         <v>155</v>
       </c>
@@ -3908,8 +3899,8 @@
       </c>
     </row>
     <row r="52" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A52" s="37"/>
-      <c r="B52" s="41"/>
+      <c r="A52" s="34"/>
+      <c r="B52" s="37"/>
       <c r="C52" s="6" t="s">
         <v>196</v>
       </c>
@@ -3922,8 +3913,8 @@
       </c>
     </row>
     <row r="53" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A53" s="37"/>
-      <c r="B53" s="41"/>
+      <c r="A53" s="34"/>
+      <c r="B53" s="37"/>
       <c r="C53" s="6" t="s">
         <v>167</v>
       </c>
@@ -3936,8 +3927,8 @@
       </c>
     </row>
     <row r="54" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A54" s="37"/>
-      <c r="B54" s="41"/>
+      <c r="A54" s="34"/>
+      <c r="B54" s="37"/>
       <c r="C54" s="6" t="s">
         <v>188</v>
       </c>
@@ -3950,16 +3941,16 @@
       </c>
     </row>
     <row r="55" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A55" s="37"/>
-      <c r="B55" s="42"/>
+      <c r="A55" s="34"/>
+      <c r="B55" s="38"/>
       <c r="C55" s="15"/>
       <c r="D55" s="15"/>
       <c r="E55" s="16"/>
       <c r="F55" s="15"/>
     </row>
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A56" s="37"/>
-      <c r="B56" s="41" t="s">
+      <c r="A56" s="34"/>
+      <c r="B56" s="37" t="s">
         <v>315</v>
       </c>
       <c r="C56" s="6" t="s">
@@ -3974,8 +3965,8 @@
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A57" s="37"/>
-      <c r="B57" s="41"/>
+      <c r="A57" s="34"/>
+      <c r="B57" s="37"/>
       <c r="C57" s="6" t="s">
         <v>111</v>
       </c>
@@ -3988,8 +3979,8 @@
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A58" s="37"/>
-      <c r="B58" s="41"/>
+      <c r="A58" s="34"/>
+      <c r="B58" s="37"/>
       <c r="C58" s="6" t="s">
         <v>135</v>
       </c>
@@ -4002,8 +3993,8 @@
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A59" s="37"/>
-      <c r="B59" s="41"/>
+      <c r="A59" s="34"/>
+      <c r="B59" s="37"/>
       <c r="C59" s="6" t="s">
         <v>136</v>
       </c>
@@ -4016,8 +4007,8 @@
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A60" s="37"/>
-      <c r="B60" s="41"/>
+      <c r="A60" s="34"/>
+      <c r="B60" s="37"/>
       <c r="C60" s="6" t="s">
         <v>141</v>
       </c>
@@ -4030,8 +4021,8 @@
       </c>
     </row>
     <row r="61" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A61" s="37"/>
-      <c r="B61" s="41"/>
+      <c r="A61" s="34"/>
+      <c r="B61" s="37"/>
       <c r="C61" s="6" t="s">
         <v>155</v>
       </c>
@@ -4044,8 +4035,8 @@
       </c>
     </row>
     <row r="62" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A62" s="37"/>
-      <c r="B62" s="41"/>
+      <c r="A62" s="34"/>
+      <c r="B62" s="37"/>
       <c r="C62" s="6" t="s">
         <v>196</v>
       </c>
@@ -4058,8 +4049,8 @@
       </c>
     </row>
     <row r="63" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A63" s="37"/>
-      <c r="B63" s="41"/>
+      <c r="A63" s="34"/>
+      <c r="B63" s="37"/>
       <c r="C63" s="6" t="s">
         <v>167</v>
       </c>
@@ -4072,8 +4063,8 @@
       </c>
     </row>
     <row r="64" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A64" s="37"/>
-      <c r="B64" s="41"/>
+      <c r="A64" s="34"/>
+      <c r="B64" s="37"/>
       <c r="C64" s="6" t="s">
         <v>188</v>
       </c>
@@ -4086,13 +4077,13 @@
       </c>
     </row>
     <row r="65" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A65" s="37"/>
-      <c r="B65" s="42"/>
+      <c r="A65" s="34"/>
+      <c r="B65" s="38"/>
       <c r="E65" s="11"/>
     </row>
     <row r="66" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A66" s="37"/>
-      <c r="B66" s="43" t="s">
+      <c r="A66" s="34"/>
+      <c r="B66" s="39" t="s">
         <v>6</v>
       </c>
       <c r="C66" s="13" t="s">
@@ -4107,8 +4098,8 @@
       </c>
     </row>
     <row r="67" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A67" s="37"/>
-      <c r="B67" s="41"/>
+      <c r="A67" s="34"/>
+      <c r="B67" s="37"/>
       <c r="C67" s="6" t="s">
         <v>113</v>
       </c>
@@ -4121,8 +4112,8 @@
       </c>
     </row>
     <row r="68" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A68" s="37"/>
-      <c r="B68" s="45"/>
+      <c r="A68" s="34"/>
+      <c r="B68" s="41"/>
       <c r="C68" s="6" t="s">
         <v>111</v>
       </c>
@@ -4135,8 +4126,8 @@
       </c>
     </row>
     <row r="69" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A69" s="37"/>
-      <c r="B69" s="45"/>
+      <c r="A69" s="34"/>
+      <c r="B69" s="41"/>
       <c r="C69" s="6" t="s">
         <v>107</v>
       </c>
@@ -4149,8 +4140,8 @@
       </c>
     </row>
     <row r="70" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A70" s="37"/>
-      <c r="B70" s="45"/>
+      <c r="A70" s="34"/>
+      <c r="B70" s="41"/>
       <c r="C70" s="6" t="s">
         <v>126</v>
       </c>
@@ -4163,8 +4154,8 @@
       </c>
     </row>
     <row r="71" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A71" s="37"/>
-      <c r="B71" s="45"/>
+      <c r="A71" s="34"/>
+      <c r="B71" s="41"/>
       <c r="C71" s="6" t="s">
         <v>127</v>
       </c>
@@ -4177,8 +4168,8 @@
       </c>
     </row>
     <row r="72" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A72" s="37"/>
-      <c r="B72" s="45"/>
+      <c r="A72" s="34"/>
+      <c r="B72" s="41"/>
       <c r="C72" s="6" t="s">
         <v>141</v>
       </c>
@@ -4191,8 +4182,8 @@
       </c>
     </row>
     <row r="73" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A73" s="37"/>
-      <c r="B73" s="45"/>
+      <c r="A73" s="34"/>
+      <c r="B73" s="41"/>
       <c r="C73" s="6" t="s">
         <v>155</v>
       </c>
@@ -4205,8 +4196,8 @@
       </c>
     </row>
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A74" s="37"/>
-      <c r="B74" s="45"/>
+      <c r="A74" s="34"/>
+      <c r="B74" s="41"/>
       <c r="C74" s="6" t="s">
         <v>196</v>
       </c>
@@ -4219,8 +4210,8 @@
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A75" s="37"/>
-      <c r="B75" s="45"/>
+      <c r="A75" s="34"/>
+      <c r="B75" s="41"/>
       <c r="C75" s="6" t="s">
         <v>167</v>
       </c>
@@ -4233,8 +4224,8 @@
       </c>
     </row>
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A76" s="37"/>
-      <c r="B76" s="45"/>
+      <c r="A76" s="34"/>
+      <c r="B76" s="41"/>
       <c r="C76" s="6" t="s">
         <v>188</v>
       </c>
@@ -4247,18 +4238,18 @@
       </c>
     </row>
     <row r="77" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A77" s="38"/>
-      <c r="B77" s="46"/>
+      <c r="A77" s="35"/>
+      <c r="B77" s="42"/>
       <c r="C77" s="19"/>
       <c r="D77" s="19"/>
       <c r="E77" s="20"/>
       <c r="F77" s="19"/>
     </row>
     <row r="78" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A78" s="36" t="s">
+      <c r="A78" s="33" t="s">
         <v>72</v>
       </c>
-      <c r="B78" s="47" t="s">
+      <c r="B78" s="43" t="s">
         <v>73</v>
       </c>
       <c r="C78" s="7" t="s">
@@ -4273,46 +4264,46 @@
       </c>
     </row>
     <row r="79" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A79" s="37"/>
-      <c r="B79" s="50"/>
-      <c r="C79" s="21" t="s">
+      <c r="A79" s="34"/>
+      <c r="B79" s="41"/>
+      <c r="C79" s="6" t="s">
         <v>153</v>
       </c>
-      <c r="D79" s="21" t="s">
+      <c r="D79" s="6" t="s">
         <v>152</v>
       </c>
-      <c r="E79" s="22"/>
-      <c r="F79" s="21" t="s">
+      <c r="E79" s="9"/>
+      <c r="F79" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="80" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A80" s="37"/>
-      <c r="B80" s="49"/>
+      <c r="A80" s="34"/>
+      <c r="B80" s="45"/>
       <c r="C80" s="15"/>
       <c r="D80" s="15"/>
-      <c r="E80" s="23"/>
+      <c r="E80" s="21"/>
       <c r="F80" s="15"/>
     </row>
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A81" s="37"/>
-      <c r="B81" s="50" t="s">
+      <c r="A81" s="34"/>
+      <c r="B81" s="41" t="s">
         <v>341</v>
       </c>
-      <c r="C81" s="21" t="s">
+      <c r="C81" s="6" t="s">
         <v>344</v>
       </c>
-      <c r="D81" s="21" t="s">
+      <c r="D81" s="6" t="s">
         <v>347</v>
       </c>
-      <c r="E81" s="22"/>
-      <c r="F81" s="21" t="s">
+      <c r="E81" s="9"/>
+      <c r="F81" s="6" t="s">
         <v>346</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A82" s="37"/>
-      <c r="B82" s="50"/>
+      <c r="A82" s="34"/>
+      <c r="B82" s="41"/>
       <c r="C82" s="6" t="s">
         <v>345</v>
       </c>
@@ -4325,13 +4316,13 @@
       </c>
     </row>
     <row r="83" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A83" s="37"/>
-      <c r="B83" s="50"/>
+      <c r="A83" s="34"/>
+      <c r="B83" s="41"/>
       <c r="E83" s="9"/>
     </row>
     <row r="84" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A84" s="37"/>
-      <c r="B84" s="43" t="s">
+      <c r="A84" s="34"/>
+      <c r="B84" s="39" t="s">
         <v>4</v>
       </c>
       <c r="C84" s="13" t="s">
@@ -4346,8 +4337,8 @@
       </c>
     </row>
     <row r="85" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A85" s="37"/>
-      <c r="B85" s="41"/>
+      <c r="A85" s="34"/>
+      <c r="B85" s="37"/>
       <c r="C85" s="6" t="s">
         <v>107</v>
       </c>
@@ -4360,8 +4351,8 @@
       </c>
     </row>
     <row r="86" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A86" s="37"/>
-      <c r="B86" s="41"/>
+      <c r="A86" s="34"/>
+      <c r="B86" s="37"/>
       <c r="C86" s="6" t="s">
         <v>122</v>
       </c>
@@ -4374,8 +4365,8 @@
       </c>
     </row>
     <row r="87" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A87" s="37"/>
-      <c r="B87" s="41"/>
+      <c r="A87" s="34"/>
+      <c r="B87" s="37"/>
       <c r="C87" s="6" t="s">
         <v>141</v>
       </c>
@@ -4388,8 +4379,8 @@
       </c>
     </row>
     <row r="88" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A88" s="37"/>
-      <c r="B88" s="41"/>
+      <c r="A88" s="34"/>
+      <c r="B88" s="37"/>
       <c r="C88" s="6" t="s">
         <v>155</v>
       </c>
@@ -4402,8 +4393,8 @@
       </c>
     </row>
     <row r="89" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A89" s="37"/>
-      <c r="B89" s="41"/>
+      <c r="A89" s="34"/>
+      <c r="B89" s="37"/>
       <c r="C89" s="6" t="s">
         <v>161</v>
       </c>
@@ -4416,8 +4407,8 @@
       </c>
     </row>
     <row r="90" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A90" s="37"/>
-      <c r="B90" s="41"/>
+      <c r="A90" s="34"/>
+      <c r="B90" s="37"/>
       <c r="C90" s="6" t="s">
         <v>196</v>
       </c>
@@ -4430,8 +4421,8 @@
       </c>
     </row>
     <row r="91" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A91" s="37"/>
-      <c r="B91" s="41"/>
+      <c r="A91" s="34"/>
+      <c r="B91" s="37"/>
       <c r="C91" s="6" t="s">
         <v>167</v>
       </c>
@@ -4444,8 +4435,8 @@
       </c>
     </row>
     <row r="92" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A92" s="37"/>
-      <c r="B92" s="41"/>
+      <c r="A92" s="34"/>
+      <c r="B92" s="37"/>
       <c r="C92" s="6" t="s">
         <v>188</v>
       </c>
@@ -4458,12 +4449,12 @@
       </c>
     </row>
     <row r="93" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A93" s="37"/>
-      <c r="B93" s="42"/>
+      <c r="A93" s="34"/>
+      <c r="B93" s="38"/>
     </row>
     <row r="94" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A94" s="37"/>
-      <c r="B94" s="43" t="s">
+      <c r="A94" s="34"/>
+      <c r="B94" s="39" t="s">
         <v>5</v>
       </c>
       <c r="C94" s="13" t="s">
@@ -4478,8 +4469,8 @@
       </c>
     </row>
     <row r="95" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A95" s="37"/>
-      <c r="B95" s="41"/>
+      <c r="A95" s="34"/>
+      <c r="B95" s="37"/>
       <c r="C95" s="6" t="s">
         <v>108</v>
       </c>
@@ -4492,8 +4483,8 @@
       </c>
     </row>
     <row r="96" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A96" s="37"/>
-      <c r="B96" s="41"/>
+      <c r="A96" s="34"/>
+      <c r="B96" s="37"/>
       <c r="C96" s="6" t="s">
         <v>120</v>
       </c>
@@ -4506,8 +4497,8 @@
       </c>
     </row>
     <row r="97" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A97" s="37"/>
-      <c r="B97" s="41"/>
+      <c r="A97" s="34"/>
+      <c r="B97" s="37"/>
       <c r="C97" s="6" t="s">
         <v>141</v>
       </c>
@@ -4520,8 +4511,8 @@
       </c>
     </row>
     <row r="98" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A98" s="37"/>
-      <c r="B98" s="41"/>
+      <c r="A98" s="34"/>
+      <c r="B98" s="37"/>
       <c r="C98" s="6" t="s">
         <v>155</v>
       </c>
@@ -4534,36 +4525,36 @@
       </c>
     </row>
     <row r="99" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A99" s="37"/>
-      <c r="B99" s="41"/>
+      <c r="A99" s="34"/>
+      <c r="B99" s="37"/>
       <c r="C99" s="6" t="s">
         <v>161</v>
       </c>
       <c r="D99" s="6" t="s">
         <v>160</v>
       </c>
-      <c r="E99" s="24"/>
+      <c r="E99" s="22"/>
       <c r="F99" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="100" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A100" s="37"/>
-      <c r="B100" s="41"/>
+      <c r="A100" s="34"/>
+      <c r="B100" s="37"/>
       <c r="C100" s="6" t="s">
         <v>196</v>
       </c>
       <c r="D100" s="6" t="s">
         <v>197</v>
       </c>
-      <c r="E100" s="24"/>
+      <c r="E100" s="22"/>
       <c r="F100" s="6" t="s">
         <v>149</v>
       </c>
     </row>
     <row r="101" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A101" s="37"/>
-      <c r="B101" s="41"/>
+      <c r="A101" s="34"/>
+      <c r="B101" s="37"/>
       <c r="C101" s="6" t="s">
         <v>167</v>
       </c>
@@ -4576,8 +4567,8 @@
       </c>
     </row>
     <row r="102" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A102" s="37"/>
-      <c r="B102" s="41"/>
+      <c r="A102" s="34"/>
+      <c r="B102" s="37"/>
       <c r="C102" s="6" t="s">
         <v>188</v>
       </c>
@@ -4590,14 +4581,14 @@
       </c>
     </row>
     <row r="103" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A103" s="38"/>
-      <c r="B103" s="44"/>
+      <c r="A103" s="35"/>
+      <c r="B103" s="40"/>
     </row>
     <row r="104" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A104" s="36" t="s">
+      <c r="A104" s="33" t="s">
         <v>76</v>
       </c>
-      <c r="B104" s="47" t="s">
+      <c r="B104" s="43" t="s">
         <v>73</v>
       </c>
       <c r="C104" s="7" t="s">
@@ -4612,8 +4603,8 @@
       </c>
     </row>
     <row r="105" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A105" s="37"/>
-      <c r="B105" s="45"/>
+      <c r="A105" s="34"/>
+      <c r="B105" s="41"/>
       <c r="C105" s="6" t="s">
         <v>228</v>
       </c>
@@ -4626,8 +4617,8 @@
       </c>
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A106" s="37"/>
-      <c r="B106" s="45"/>
+      <c r="A106" s="34"/>
+      <c r="B106" s="41"/>
       <c r="C106" s="6" t="s">
         <v>150</v>
       </c>
@@ -4640,16 +4631,16 @@
       </c>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A107" s="37"/>
-      <c r="B107" s="49"/>
+      <c r="A107" s="34"/>
+      <c r="B107" s="45"/>
       <c r="C107" s="15"/>
       <c r="D107" s="15"/>
       <c r="E107" s="16"/>
       <c r="F107" s="15"/>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A108" s="37"/>
-      <c r="B108" s="48" t="s">
+      <c r="A108" s="34"/>
+      <c r="B108" s="44" t="s">
         <v>301</v>
       </c>
       <c r="C108" s="6" t="s">
@@ -4664,8 +4655,8 @@
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A109" s="37"/>
-      <c r="B109" s="45"/>
+      <c r="A109" s="34"/>
+      <c r="B109" s="41"/>
       <c r="C109" s="6" t="s">
         <v>306</v>
       </c>
@@ -4678,8 +4669,8 @@
       </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A110" s="37"/>
-      <c r="B110" s="45"/>
+      <c r="A110" s="34"/>
+      <c r="B110" s="41"/>
       <c r="C110" s="6" t="s">
         <v>307</v>
       </c>
@@ -4692,13 +4683,13 @@
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A111" s="37"/>
-      <c r="B111" s="49"/>
+      <c r="A111" s="34"/>
+      <c r="B111" s="45"/>
       <c r="E111" s="11"/>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A112" s="37"/>
-      <c r="B112" s="48" t="s">
+      <c r="A112" s="34"/>
+      <c r="B112" s="44" t="s">
         <v>79</v>
       </c>
       <c r="C112" s="13" t="s">
@@ -4713,8 +4704,8 @@
       </c>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A113" s="37"/>
-      <c r="B113" s="45"/>
+      <c r="A113" s="34"/>
+      <c r="B113" s="41"/>
       <c r="C113" s="6" t="s">
         <v>151</v>
       </c>
@@ -4727,16 +4718,16 @@
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A114" s="37"/>
-      <c r="B114" s="49"/>
+      <c r="A114" s="34"/>
+      <c r="B114" s="45"/>
       <c r="C114" s="15"/>
       <c r="D114" s="15"/>
       <c r="E114" s="16"/>
       <c r="F114" s="15"/>
     </row>
     <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="37"/>
-      <c r="B115" s="48" t="s">
+      <c r="A115" s="34"/>
+      <c r="B115" s="44" t="s">
         <v>260</v>
       </c>
       <c r="C115" s="6" t="s">
@@ -4751,8 +4742,8 @@
       </c>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="37"/>
-      <c r="B116" s="45"/>
+      <c r="A116" s="34"/>
+      <c r="B116" s="41"/>
       <c r="C116" s="6" t="s">
         <v>261</v>
       </c>
@@ -4765,18 +4756,18 @@
       </c>
     </row>
     <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="38"/>
-      <c r="B117" s="46"/>
+      <c r="A117" s="35"/>
+      <c r="B117" s="42"/>
       <c r="C117" s="19"/>
       <c r="D117" s="19"/>
       <c r="E117" s="20"/>
       <c r="F117" s="19"/>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="36" t="s">
+      <c r="A118" s="33" t="s">
         <v>163</v>
       </c>
-      <c r="B118" s="47" t="s">
+      <c r="B118" s="43" t="s">
         <v>13</v>
       </c>
       <c r="C118" s="7" t="s">
@@ -4791,8 +4782,8 @@
       </c>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A119" s="39"/>
-      <c r="B119" s="45"/>
+      <c r="A119" s="34"/>
+      <c r="B119" s="41"/>
       <c r="C119" s="6" t="s">
         <v>174</v>
       </c>
@@ -4804,16 +4795,16 @@
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A120" s="39"/>
-      <c r="B120" s="49"/>
+      <c r="A120" s="34"/>
+      <c r="B120" s="45"/>
       <c r="C120" s="15"/>
       <c r="D120" s="15"/>
       <c r="E120" s="15"/>
       <c r="F120" s="15"/>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A121" s="39"/>
-      <c r="B121" s="48" t="s">
+      <c r="A121" s="34"/>
+      <c r="B121" s="44" t="s">
         <v>183</v>
       </c>
       <c r="C121" s="6" t="s">
@@ -4827,8 +4818,8 @@
       </c>
     </row>
     <row r="122" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A122" s="39"/>
-      <c r="B122" s="45"/>
+      <c r="A122" s="34"/>
+      <c r="B122" s="41"/>
       <c r="C122" s="6" t="s">
         <v>181</v>
       </c>
@@ -4840,8 +4831,8 @@
       </c>
     </row>
     <row r="123" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A123" s="39"/>
-      <c r="B123" s="45"/>
+      <c r="A123" s="34"/>
+      <c r="B123" s="41"/>
       <c r="C123" s="6" t="s">
         <v>177</v>
       </c>
@@ -4853,8 +4844,8 @@
       </c>
     </row>
     <row r="124" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A124" s="39"/>
-      <c r="B124" s="45"/>
+      <c r="A124" s="34"/>
+      <c r="B124" s="41"/>
       <c r="C124" s="6" t="s">
         <v>179</v>
       </c>
@@ -4866,8 +4857,8 @@
       </c>
     </row>
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A125" s="39"/>
-      <c r="B125" s="45"/>
+      <c r="A125" s="34"/>
+      <c r="B125" s="41"/>
       <c r="C125" s="6" t="s">
         <v>182</v>
       </c>
@@ -4879,8 +4870,8 @@
       </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A126" s="39"/>
-      <c r="B126" s="45"/>
+      <c r="A126" s="34"/>
+      <c r="B126" s="41"/>
       <c r="C126" s="6" t="s">
         <v>191</v>
       </c>
@@ -4892,12 +4883,12 @@
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A127" s="39"/>
-      <c r="B127" s="45"/>
+      <c r="A127" s="34"/>
+      <c r="B127" s="41"/>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A128" s="39"/>
-      <c r="B128" s="48" t="s">
+      <c r="A128" s="34"/>
+      <c r="B128" s="44" t="s">
         <v>206</v>
       </c>
       <c r="C128" s="13" t="s">
@@ -4912,8 +4903,8 @@
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A129" s="39"/>
-      <c r="B129" s="45"/>
+      <c r="A129" s="34"/>
+      <c r="B129" s="41"/>
       <c r="C129" s="6" t="s">
         <v>204</v>
       </c>
@@ -4925,8 +4916,8 @@
       </c>
     </row>
     <row r="130" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A130" s="39"/>
-      <c r="B130" s="45"/>
+      <c r="A130" s="34"/>
+      <c r="B130" s="41"/>
       <c r="C130" s="6" t="s">
         <v>215</v>
       </c>
@@ -4938,8 +4929,8 @@
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A131" s="39"/>
-      <c r="B131" s="45"/>
+      <c r="A131" s="34"/>
+      <c r="B131" s="41"/>
       <c r="C131" s="6" t="s">
         <v>205</v>
       </c>
@@ -4951,8 +4942,8 @@
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A132" s="39"/>
-      <c r="B132" s="45"/>
+      <c r="A132" s="34"/>
+      <c r="B132" s="41"/>
       <c r="C132" s="6" t="s">
         <v>310</v>
       </c>
@@ -4964,8 +4955,8 @@
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A133" s="39"/>
-      <c r="B133" s="45"/>
+      <c r="A133" s="34"/>
+      <c r="B133" s="41"/>
       <c r="C133" s="6" t="s">
         <v>334</v>
       </c>
@@ -4977,8 +4968,8 @@
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A134" s="39"/>
-      <c r="B134" s="45"/>
+      <c r="A134" s="34"/>
+      <c r="B134" s="41"/>
       <c r="C134" s="6" t="s">
         <v>336</v>
       </c>
@@ -4990,8 +4981,8 @@
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A135" s="39"/>
-      <c r="B135" s="45"/>
+      <c r="A135" s="34"/>
+      <c r="B135" s="41"/>
       <c r="C135" s="6" t="s">
         <v>217</v>
       </c>
@@ -5003,8 +4994,8 @@
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A136" s="39"/>
-      <c r="B136" s="45"/>
+      <c r="A136" s="34"/>
+      <c r="B136" s="41"/>
       <c r="C136" s="6" t="s">
         <v>221</v>
       </c>
@@ -5016,8 +5007,8 @@
       </c>
     </row>
     <row r="137" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A137" s="39"/>
-      <c r="B137" s="45"/>
+      <c r="A137" s="34"/>
+      <c r="B137" s="41"/>
       <c r="C137" s="6" t="s">
         <v>202</v>
       </c>
@@ -5029,8 +5020,8 @@
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A138" s="39"/>
-      <c r="B138" s="45"/>
+      <c r="A138" s="34"/>
+      <c r="B138" s="41"/>
       <c r="C138" s="6" t="s">
         <v>264</v>
       </c>
@@ -5042,8 +5033,8 @@
       </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A139" s="39"/>
-      <c r="B139" s="45"/>
+      <c r="A139" s="34"/>
+      <c r="B139" s="41"/>
       <c r="C139" s="6" t="s">
         <v>266</v>
       </c>
@@ -5055,12 +5046,12 @@
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A140" s="39"/>
-      <c r="B140" s="45"/>
+      <c r="A140" s="34"/>
+      <c r="B140" s="41"/>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A141" s="39"/>
-      <c r="B141" s="48" t="s">
+      <c r="A141" s="34"/>
+      <c r="B141" s="44" t="s">
         <v>222</v>
       </c>
       <c r="C141" s="13" t="s">
@@ -5075,8 +5066,8 @@
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A142" s="39"/>
-      <c r="B142" s="50"/>
+      <c r="A142" s="34"/>
+      <c r="B142" s="41"/>
       <c r="C142" s="6" t="s">
         <v>312</v>
       </c>
@@ -5088,8 +5079,8 @@
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A143" s="39"/>
-      <c r="B143" s="50"/>
+      <c r="A143" s="34"/>
+      <c r="B143" s="41"/>
       <c r="C143" s="6" t="s">
         <v>225</v>
       </c>
@@ -5101,8 +5092,8 @@
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A144" s="39"/>
-      <c r="B144" s="50"/>
+      <c r="A144" s="34"/>
+      <c r="B144" s="41"/>
       <c r="C144" s="6" t="s">
         <v>267</v>
       </c>
@@ -5114,8 +5105,8 @@
       </c>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A145" s="39"/>
-      <c r="B145" s="50"/>
+      <c r="A145" s="34"/>
+      <c r="B145" s="41"/>
       <c r="C145" s="6" t="s">
         <v>269</v>
       </c>
@@ -5127,12 +5118,12 @@
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A146" s="39"/>
-      <c r="B146" s="49"/>
+      <c r="A146" s="34"/>
+      <c r="B146" s="45"/>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A147" s="39"/>
-      <c r="B147" s="48" t="s">
+      <c r="A147" s="34"/>
+      <c r="B147" s="44" t="s">
         <v>380</v>
       </c>
       <c r="C147" s="13" t="s">
@@ -5147,8 +5138,8 @@
       </c>
     </row>
     <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="39"/>
-      <c r="B148" s="45"/>
+      <c r="A148" s="34"/>
+      <c r="B148" s="41"/>
       <c r="C148" s="6" t="s">
         <v>383</v>
       </c>
@@ -5160,19 +5151,10 @@
       </c>
     </row>
     <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="39"/>
+      <c r="A149" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A117"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B78:B80"/>
     <mergeCell ref="B147:B148"/>
     <mergeCell ref="B141:B146"/>
     <mergeCell ref="A118:A149"/>
@@ -5189,6 +5171,15 @@
     <mergeCell ref="B115:B117"/>
     <mergeCell ref="B121:B127"/>
     <mergeCell ref="B128:B140"/>
+    <mergeCell ref="B118:B120"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A117"/>
+    <mergeCell ref="B112:B114"/>
+    <mergeCell ref="B104:B107"/>
+    <mergeCell ref="B108:B111"/>
+    <mergeCell ref="B78:B80"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>

--- a/Methanol/Methanol_Bio_Brownfield_Leuna/Datenbank.xlsx
+++ b/Methanol/Methanol_Bio_Brownfield_Leuna/Datenbank.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="29426"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\hem38994\Documents\GitHub\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Leuna\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\01-Arbeit\06-FENES\09-P2X3\FENES_P2X\Methanol\Methanol_Bio_Brownfield_Leuna\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5B0E4E71-4D41-4D6A-B7BD-F5383D5091DB}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5F7B7D9E-DB65-4F88-8C3D-53B6146FF9E2}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="38640" windowHeight="23520" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Datenauswahl" sheetId="1" r:id="rId1"/>
@@ -170,7 +170,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="665" uniqueCount="388">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="659" uniqueCount="384">
   <si>
     <t>PEM Elektrolyse</t>
   </si>
@@ -855,12 +855,6 @@
     <t>calc_cost_h2</t>
   </si>
   <si>
-    <t>calc_einnahmen_stromverkauf_schattenvariable</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Stromverkauf</t>
-  </si>
-  <si>
     <t>Methanolsynthese</t>
   </si>
   <si>
@@ -1086,13 +1080,7 @@
     <t>result_qverkauf_flowsum</t>
   </si>
   <si>
-    <t>calc_einnahmen_qverkauf_schattenvariable</t>
-  </si>
-  <si>
     <t>calc_einnnahmen_qverkauf</t>
-  </si>
-  <si>
-    <t>Schattenvariable Einnahmen Wärmeverkauf</t>
   </si>
   <si>
     <t>Einnahmen aus Wärmeverkauf</t>
@@ -1343,10 +1331,10 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="4">
-    <numFmt numFmtId="164" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
-    <numFmt numFmtId="165" formatCode="0.0000"/>
-    <numFmt numFmtId="166" formatCode="0.000"/>
-    <numFmt numFmtId="167" formatCode="0.00000"/>
+    <numFmt numFmtId="44" formatCode="_-&quot;€&quot;\ * #,##0.00_-;\-&quot;€&quot;\ * #,##0.00_-;_-&quot;€&quot;\ * &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="164" formatCode="0.0000"/>
+    <numFmt numFmtId="165" formatCode="0.000"/>
+    <numFmt numFmtId="166" formatCode="0.00000"/>
   </numFmts>
   <fonts count="6" x14ac:knownFonts="1">
     <font>
@@ -1478,42 +1466,42 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="164" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="44" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
   <cellXfs count="46">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="1" applyNumberFormat="1" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="right"/>
     </xf>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="1" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="3" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="2" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="4" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="2" fillId="0" borderId="3" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="4" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="167" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
+    <xf numFmtId="166" fontId="2" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="7" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="165" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="164" fontId="2" fillId="0" borderId="5" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -2022,19 +2010,19 @@
     <row r="8" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A8" s="34"/>
       <c r="B8" s="44" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C8" s="13" t="s">
         <v>84</v>
       </c>
       <c r="D8" s="13" t="s">
-        <v>231</v>
+        <v>229</v>
       </c>
       <c r="E8" s="14">
         <v>1.5</v>
       </c>
       <c r="F8" s="13" t="s">
-        <v>230</v>
+        <v>228</v>
       </c>
     </row>
     <row r="9" spans="1:7" x14ac:dyDescent="0.3">
@@ -2044,7 +2032,7 @@
         <v>85</v>
       </c>
       <c r="D9" s="6" t="s">
-        <v>232</v>
+        <v>230</v>
       </c>
       <c r="E9" s="9">
         <v>285.39999999999998</v>
@@ -2060,13 +2048,13 @@
         <v>10</v>
       </c>
       <c r="D10" s="6" t="s">
-        <v>233</v>
+        <v>231</v>
       </c>
       <c r="E10" s="9">
         <v>5110</v>
       </c>
       <c r="F10" s="9" t="s">
-        <v>238</v>
+        <v>236</v>
       </c>
     </row>
     <row r="11" spans="1:7" x14ac:dyDescent="0.3">
@@ -2076,7 +2064,7 @@
         <v>11</v>
       </c>
       <c r="D11" s="6" t="s">
-        <v>234</v>
+        <v>232</v>
       </c>
       <c r="E11" s="11">
         <v>0.05</v>
@@ -2092,29 +2080,29 @@
         <v>86</v>
       </c>
       <c r="D12" s="6" t="s">
-        <v>235</v>
+        <v>233</v>
       </c>
       <c r="E12" s="9">
         <v>0.189</v>
       </c>
       <c r="F12" s="6" t="s">
-        <v>239</v>
+        <v>237</v>
       </c>
     </row>
     <row r="13" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A13" s="34"/>
       <c r="B13" s="41"/>
       <c r="C13" s="6" t="s">
-        <v>244</v>
+        <v>242</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>240</v>
+        <v>238</v>
       </c>
       <c r="E13" s="9">
         <v>1.375</v>
       </c>
       <c r="F13" s="6" t="s">
-        <v>241</v>
+        <v>239</v>
       </c>
     </row>
     <row r="14" spans="1:7" x14ac:dyDescent="0.3">
@@ -2124,7 +2112,7 @@
         <v>13</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>236</v>
+        <v>234</v>
       </c>
       <c r="E14" s="12">
         <v>25</v>
@@ -2140,7 +2128,7 @@
         <v>15</v>
       </c>
       <c r="D15" s="15" t="s">
-        <v>237</v>
+        <v>235</v>
       </c>
       <c r="E15" s="16">
         <v>0.08</v>
@@ -2152,13 +2140,13 @@
     <row r="16" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A16" s="34"/>
       <c r="B16" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C16" s="13" t="s">
         <v>8</v>
       </c>
       <c r="D16" s="13" t="s">
-        <v>274</v>
+        <v>272</v>
       </c>
       <c r="E16" s="18">
         <v>3.7</v>
@@ -2174,13 +2162,13 @@
         <v>84</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>275</v>
+        <v>273</v>
       </c>
       <c r="E17" s="11">
         <v>0.27</v>
       </c>
       <c r="F17" s="6" t="s">
-        <v>300</v>
+        <v>298</v>
       </c>
     </row>
     <row r="18" spans="1:6" x14ac:dyDescent="0.3">
@@ -2190,13 +2178,13 @@
         <v>10</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>276</v>
+        <v>274</v>
       </c>
       <c r="E18" s="11">
         <v>700</v>
       </c>
       <c r="F18" s="6" t="s">
-        <v>280</v>
+        <v>278</v>
       </c>
     </row>
     <row r="19" spans="1:6" x14ac:dyDescent="0.3">
@@ -2206,7 +2194,7 @@
         <v>11</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>277</v>
+        <v>275</v>
       </c>
       <c r="E19" s="11">
         <v>0.02</v>
@@ -2222,7 +2210,7 @@
         <v>13</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>278</v>
+        <v>276</v>
       </c>
       <c r="E20" s="11">
         <v>20</v>
@@ -2238,7 +2226,7 @@
         <v>15</v>
       </c>
       <c r="D21" s="15" t="s">
-        <v>279</v>
+        <v>277</v>
       </c>
       <c r="E21" s="16">
         <v>0.05</v>
@@ -2250,35 +2238,35 @@
     <row r="22" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A22" s="34"/>
       <c r="B22" s="37" t="s">
-        <v>340</v>
+        <v>336</v>
       </c>
       <c r="C22" s="6" t="s">
         <v>84</v>
       </c>
       <c r="D22" s="6" t="s">
-        <v>349</v>
+        <v>345</v>
       </c>
       <c r="E22" s="9">
         <v>0.2</v>
       </c>
       <c r="F22" s="6" t="s">
-        <v>242</v>
+        <v>240</v>
       </c>
     </row>
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="34"/>
       <c r="B23" s="37"/>
       <c r="C23" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>350</v>
+        <v>346</v>
       </c>
       <c r="E23" s="9">
         <v>0.92800000000000005</v>
       </c>
       <c r="F23" s="6" t="s">
-        <v>282</v>
+        <v>280</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -2288,23 +2276,23 @@
         <v>10</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>351</v>
+        <v>347</v>
       </c>
       <c r="E24" s="9">
         <v>1640</v>
       </c>
       <c r="F24" s="6" t="s">
-        <v>243</v>
+        <v>241</v>
       </c>
     </row>
     <row r="25" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A25" s="34"/>
       <c r="B25" s="37"/>
       <c r="C25" s="6" t="s">
-        <v>377</v>
+        <v>373</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>352</v>
+        <v>348</v>
       </c>
       <c r="E25" s="11">
         <v>0.04</v>
@@ -2317,48 +2305,48 @@
       <c r="A26" s="34"/>
       <c r="B26" s="37"/>
       <c r="C26" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>371</v>
+        <v>367</v>
       </c>
       <c r="E26" s="11">
         <v>2.5</v>
       </c>
       <c r="F26" s="6" t="s">
-        <v>372</v>
+        <v>368</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A27" s="34"/>
       <c r="B27" s="37"/>
       <c r="C27" s="6" t="s">
-        <v>353</v>
+        <v>349</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>354</v>
+        <v>350</v>
       </c>
       <c r="E27" s="11">
         <v>1.5</v>
       </c>
       <c r="F27" s="6" t="s">
-        <v>355</v>
+        <v>351</v>
       </c>
     </row>
     <row r="28" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A28" s="34"/>
       <c r="B28" s="37"/>
       <c r="C28" s="6" t="s">
-        <v>378</v>
+        <v>374</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>375</v>
+        <v>371</v>
       </c>
       <c r="E28" s="11">
         <v>1.5E-3</v>
       </c>
       <c r="F28" s="6" t="s">
-        <v>376</v>
+        <v>372</v>
       </c>
     </row>
     <row r="29" spans="1:6" x14ac:dyDescent="0.3">
@@ -2368,7 +2356,7 @@
         <v>13</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>356</v>
+        <v>352</v>
       </c>
       <c r="E29" s="12">
         <v>25</v>
@@ -2384,7 +2372,7 @@
         <v>15</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>357</v>
+        <v>353</v>
       </c>
       <c r="E30" s="11">
         <v>0.08</v>
@@ -2528,19 +2516,19 @@
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A39" s="34"/>
       <c r="B39" s="39" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C39" s="7" t="s">
         <v>87</v>
       </c>
       <c r="D39" s="7" t="s">
-        <v>316</v>
+        <v>312</v>
       </c>
       <c r="E39" s="17">
         <v>2.83</v>
       </c>
       <c r="F39" s="7" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="40" spans="1:6" x14ac:dyDescent="0.3">
@@ -2550,7 +2538,7 @@
         <v>11</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>317</v>
+        <v>313</v>
       </c>
       <c r="E40" s="11">
         <v>0.03</v>
@@ -2566,7 +2554,7 @@
         <v>13</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>318</v>
+        <v>314</v>
       </c>
       <c r="E41" s="12">
         <v>30</v>
@@ -2582,7 +2570,7 @@
         <v>20</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>319</v>
+        <v>315</v>
       </c>
       <c r="E42" s="11">
         <v>7.3999999999999999E-4</v>
@@ -2598,7 +2586,7 @@
         <v>35</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>320</v>
+        <v>316</v>
       </c>
       <c r="E43" s="11">
         <v>0.98</v>
@@ -2614,7 +2602,7 @@
         <v>36</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>321</v>
+        <v>317</v>
       </c>
       <c r="E44" s="11">
         <v>0.98</v>
@@ -2630,7 +2618,7 @@
         <v>15</v>
       </c>
       <c r="D45" s="6" t="s">
-        <v>322</v>
+        <v>318</v>
       </c>
       <c r="E45" s="11">
         <v>0.05</v>
@@ -2646,7 +2634,7 @@
         <v>88</v>
       </c>
       <c r="D46" s="15" t="s">
-        <v>323</v>
+        <v>319</v>
       </c>
       <c r="E46" s="16">
         <v>0</v>
@@ -2841,13 +2829,13 @@
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A58" s="34"/>
       <c r="B58" s="32" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C58" s="6" t="s">
-        <v>342</v>
+        <v>338</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>343</v>
+        <v>339</v>
       </c>
       <c r="E58" s="11">
         <v>0</v>
@@ -3098,7 +3086,7 @@
         <v>78</v>
       </c>
       <c r="E73" s="27">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F73" s="26" t="s">
         <v>19</v>
@@ -3107,19 +3095,19 @@
     <row r="74" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A74" s="34"/>
       <c r="B74" s="23" t="s">
+        <v>295</v>
+      </c>
+      <c r="C74" s="6" t="s">
+        <v>296</v>
+      </c>
+      <c r="D74" s="6" t="s">
         <v>297</v>
       </c>
-      <c r="C74" s="6" t="s">
-        <v>298</v>
-      </c>
-      <c r="D74" s="6" t="s">
-        <v>299</v>
-      </c>
       <c r="E74" s="11">
-        <v>-1E-4</v>
+        <v>0</v>
       </c>
       <c r="F74" s="6" t="s">
-        <v>324</v>
+        <v>320</v>
       </c>
     </row>
     <row r="75" spans="1:6" x14ac:dyDescent="0.3">
@@ -3143,19 +3131,19 @@
     <row r="76" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A76" s="35"/>
       <c r="B76" s="4" t="s">
-        <v>260</v>
+        <v>258</v>
       </c>
       <c r="C76" s="19" t="s">
-        <v>272</v>
+        <v>270</v>
       </c>
       <c r="D76" s="19" t="s">
-        <v>270</v>
+        <v>268</v>
       </c>
       <c r="E76" s="20">
         <v>-0.6</v>
       </c>
       <c r="F76" s="19" t="s">
-        <v>273</v>
+        <v>271</v>
       </c>
     </row>
   </sheetData>
@@ -3182,7 +3170,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{83AB2E79-6F94-41B5-A552-C40EC4890194}">
-  <dimension ref="A1:F149"/>
+  <dimension ref="A1:F147"/>
   <sheetFormatPr baseColWidth="10" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="14.5546875" style="6" customWidth="1"/>
@@ -3352,13 +3340,13 @@
     <row r="12" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A12" s="34"/>
       <c r="B12" s="44" t="s">
-        <v>229</v>
+        <v>227</v>
       </c>
       <c r="C12" s="13" t="s">
         <v>96</v>
       </c>
       <c r="D12" s="13" t="s">
-        <v>245</v>
+        <v>243</v>
       </c>
       <c r="E12" s="14"/>
       <c r="F12" s="13" t="s">
@@ -3369,14 +3357,14 @@
       <c r="A13" s="34"/>
       <c r="B13" s="41"/>
       <c r="C13" s="6" t="s">
-        <v>253</v>
+        <v>251</v>
       </c>
       <c r="D13" s="6" t="s">
-        <v>296</v>
+        <v>294</v>
       </c>
       <c r="E13" s="9"/>
       <c r="F13" s="6" t="s">
-        <v>256</v>
+        <v>254</v>
       </c>
     </row>
     <row r="14" spans="1:6" x14ac:dyDescent="0.3">
@@ -3386,7 +3374,7 @@
         <v>139</v>
       </c>
       <c r="D14" s="6" t="s">
-        <v>246</v>
+        <v>244</v>
       </c>
       <c r="E14" s="9"/>
       <c r="F14" s="9" t="s">
@@ -3397,14 +3385,14 @@
       <c r="A15" s="34"/>
       <c r="B15" s="41"/>
       <c r="C15" s="6" t="s">
-        <v>254</v>
+        <v>252</v>
       </c>
       <c r="D15" s="6" t="s">
-        <v>255</v>
+        <v>253</v>
       </c>
       <c r="E15" s="11"/>
       <c r="F15" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="16" spans="1:6" x14ac:dyDescent="0.3">
@@ -3414,7 +3402,7 @@
         <v>84</v>
       </c>
       <c r="D16" s="6" t="s">
-        <v>247</v>
+        <v>245</v>
       </c>
       <c r="E16" s="9"/>
       <c r="F16" s="6" t="s">
@@ -3428,7 +3416,7 @@
         <v>141</v>
       </c>
       <c r="D17" s="6" t="s">
-        <v>248</v>
+        <v>246</v>
       </c>
       <c r="E17" s="9"/>
       <c r="F17" s="6" t="s">
@@ -3442,7 +3430,7 @@
         <v>155</v>
       </c>
       <c r="D18" s="6" t="s">
-        <v>249</v>
+        <v>247</v>
       </c>
       <c r="E18" s="12"/>
       <c r="F18" s="6" t="s">
@@ -3456,7 +3444,7 @@
         <v>196</v>
       </c>
       <c r="D19" s="6" t="s">
-        <v>250</v>
+        <v>248</v>
       </c>
       <c r="E19" s="12"/>
       <c r="F19" s="6" t="s">
@@ -3470,7 +3458,7 @@
         <v>167</v>
       </c>
       <c r="D20" s="6" t="s">
-        <v>251</v>
+        <v>249</v>
       </c>
       <c r="E20" s="12"/>
       <c r="F20" s="6" t="s">
@@ -3484,7 +3472,7 @@
         <v>188</v>
       </c>
       <c r="D21" s="6" t="s">
-        <v>252</v>
+        <v>250</v>
       </c>
       <c r="E21" s="12"/>
       <c r="F21" s="6" t="s">
@@ -3502,17 +3490,17 @@
     <row r="23" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A23" s="34"/>
       <c r="B23" s="44" t="s">
-        <v>271</v>
+        <v>269</v>
       </c>
       <c r="C23" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D23" s="6" t="s">
-        <v>283</v>
+        <v>281</v>
       </c>
       <c r="E23" s="9"/>
       <c r="F23" s="6" t="s">
-        <v>291</v>
+        <v>289</v>
       </c>
     </row>
     <row r="24" spans="1:6" x14ac:dyDescent="0.3">
@@ -3522,7 +3510,7 @@
         <v>107</v>
       </c>
       <c r="D24" s="6" t="s">
-        <v>284</v>
+        <v>282</v>
       </c>
       <c r="E24" s="9"/>
       <c r="F24" s="6" t="s">
@@ -3536,25 +3524,25 @@
         <v>84</v>
       </c>
       <c r="D25" s="6" t="s">
-        <v>285</v>
+        <v>283</v>
       </c>
       <c r="E25" s="11"/>
       <c r="F25" s="6" t="s">
-        <v>295</v>
+        <v>293</v>
       </c>
     </row>
     <row r="26" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A26" s="34"/>
       <c r="B26" s="41"/>
       <c r="C26" s="6" t="s">
-        <v>293</v>
+        <v>291</v>
       </c>
       <c r="D26" s="6" t="s">
-        <v>294</v>
+        <v>292</v>
       </c>
       <c r="E26" s="12"/>
       <c r="F26" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="27" spans="1:6" x14ac:dyDescent="0.3">
@@ -3564,7 +3552,7 @@
         <v>141</v>
       </c>
       <c r="D27" s="6" t="s">
-        <v>286</v>
+        <v>284</v>
       </c>
       <c r="E27" s="12"/>
       <c r="F27" s="6" t="s">
@@ -3578,7 +3566,7 @@
         <v>155</v>
       </c>
       <c r="D28" s="6" t="s">
-        <v>287</v>
+        <v>285</v>
       </c>
       <c r="E28" s="12"/>
       <c r="F28" s="6" t="s">
@@ -3592,7 +3580,7 @@
         <v>196</v>
       </c>
       <c r="D29" s="6" t="s">
-        <v>288</v>
+        <v>286</v>
       </c>
       <c r="E29" s="12"/>
       <c r="F29" s="6" t="s">
@@ -3606,7 +3594,7 @@
         <v>167</v>
       </c>
       <c r="D30" s="6" t="s">
-        <v>289</v>
+        <v>287</v>
       </c>
       <c r="E30" s="11"/>
       <c r="F30" s="6" t="s">
@@ -3620,7 +3608,7 @@
         <v>188</v>
       </c>
       <c r="D31" s="6" t="s">
-        <v>290</v>
+        <v>288</v>
       </c>
       <c r="E31" s="11"/>
       <c r="F31" s="6" t="s">
@@ -3638,13 +3626,13 @@
     <row r="33" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A33" s="34"/>
       <c r="B33" s="37" t="s">
-        <v>358</v>
+        <v>354</v>
       </c>
       <c r="C33" s="6" t="s">
         <v>96</v>
       </c>
       <c r="D33" s="6" t="s">
-        <v>359</v>
+        <v>355</v>
       </c>
       <c r="E33" s="9"/>
       <c r="F33" s="6" t="s">
@@ -3658,7 +3646,7 @@
         <v>107</v>
       </c>
       <c r="D34" s="6" t="s">
-        <v>360</v>
+        <v>356</v>
       </c>
       <c r="E34" s="9"/>
       <c r="F34" s="6" t="s">
@@ -3672,7 +3660,7 @@
         <v>84</v>
       </c>
       <c r="D35" s="6" t="s">
-        <v>361</v>
+        <v>357</v>
       </c>
       <c r="E35" s="11"/>
       <c r="F35" s="6" t="s">
@@ -3683,42 +3671,42 @@
       <c r="A36" s="34"/>
       <c r="B36" s="37"/>
       <c r="C36" s="6" t="s">
-        <v>281</v>
+        <v>279</v>
       </c>
       <c r="D36" s="6" t="s">
-        <v>363</v>
+        <v>359</v>
       </c>
       <c r="E36" s="11"/>
       <c r="F36" s="6" t="s">
-        <v>292</v>
+        <v>290</v>
       </c>
     </row>
     <row r="37" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A37" s="34"/>
       <c r="B37" s="37"/>
       <c r="C37" s="6" t="s">
-        <v>370</v>
+        <v>366</v>
       </c>
       <c r="D37" s="6" t="s">
-        <v>373</v>
+        <v>369</v>
       </c>
       <c r="E37" s="11"/>
       <c r="F37" s="6" t="s">
-        <v>374</v>
+        <v>370</v>
       </c>
     </row>
     <row r="38" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A38" s="34"/>
       <c r="B38" s="37"/>
       <c r="C38" s="6" t="s">
-        <v>258</v>
+        <v>256</v>
       </c>
       <c r="D38" s="6" t="s">
-        <v>362</v>
+        <v>358</v>
       </c>
       <c r="E38" s="12"/>
       <c r="F38" s="6" t="s">
-        <v>257</v>
+        <v>255</v>
       </c>
     </row>
     <row r="39" spans="1:6" x14ac:dyDescent="0.3">
@@ -3728,7 +3716,7 @@
         <v>141</v>
       </c>
       <c r="D39" s="6" t="s">
-        <v>364</v>
+        <v>360</v>
       </c>
       <c r="E39" s="12"/>
       <c r="F39" s="6" t="s">
@@ -3742,7 +3730,7 @@
         <v>155</v>
       </c>
       <c r="D40" s="6" t="s">
-        <v>367</v>
+        <v>363</v>
       </c>
       <c r="E40" s="12"/>
       <c r="F40" s="6" t="s">
@@ -3756,7 +3744,7 @@
         <v>161</v>
       </c>
       <c r="D41" s="6" t="s">
-        <v>379</v>
+        <v>375</v>
       </c>
       <c r="E41" s="12"/>
       <c r="F41" s="6" t="s">
@@ -3770,7 +3758,7 @@
         <v>196</v>
       </c>
       <c r="D42" s="6" t="s">
-        <v>365</v>
+        <v>361</v>
       </c>
       <c r="E42" s="12"/>
       <c r="F42" s="6" t="s">
@@ -3784,7 +3772,7 @@
         <v>167</v>
       </c>
       <c r="D43" s="6" t="s">
-        <v>366</v>
+        <v>362</v>
       </c>
       <c r="E43" s="11"/>
       <c r="F43" s="6" t="s">
@@ -3798,7 +3786,7 @@
         <v>188</v>
       </c>
       <c r="D44" s="6" t="s">
-        <v>368</v>
+        <v>364</v>
       </c>
       <c r="E44" s="11"/>
       <c r="F44" s="6" t="s">
@@ -3825,7 +3813,7 @@
       </c>
       <c r="E46" s="17"/>
       <c r="F46" s="7" t="s">
-        <v>386</v>
+        <v>382</v>
       </c>
     </row>
     <row r="47" spans="1:6" x14ac:dyDescent="0.3">
@@ -3839,7 +3827,7 @@
       </c>
       <c r="E47" s="11"/>
       <c r="F47" s="6" t="s">
-        <v>387</v>
+        <v>383</v>
       </c>
     </row>
     <row r="48" spans="1:6" x14ac:dyDescent="0.3">
@@ -3951,17 +3939,17 @@
     <row r="56" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A56" s="34"/>
       <c r="B56" s="37" t="s">
-        <v>315</v>
+        <v>311</v>
       </c>
       <c r="C56" s="6" t="s">
         <v>113</v>
       </c>
       <c r="D56" s="6" t="s">
-        <v>325</v>
+        <v>321</v>
       </c>
       <c r="E56" s="9"/>
       <c r="F56" s="6" t="s">
-        <v>338</v>
+        <v>334</v>
       </c>
     </row>
     <row r="57" spans="1:6" x14ac:dyDescent="0.3">
@@ -3971,11 +3959,11 @@
         <v>111</v>
       </c>
       <c r="D57" s="6" t="s">
-        <v>326</v>
+        <v>322</v>
       </c>
       <c r="E57" s="11"/>
       <c r="F57" s="6" t="s">
-        <v>339</v>
+        <v>335</v>
       </c>
     </row>
     <row r="58" spans="1:6" x14ac:dyDescent="0.3">
@@ -3985,11 +3973,11 @@
         <v>135</v>
       </c>
       <c r="D58" s="6" t="s">
-        <v>327</v>
+        <v>323</v>
       </c>
       <c r="E58" s="12"/>
       <c r="F58" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="59" spans="1:6" x14ac:dyDescent="0.3">
@@ -3999,11 +3987,11 @@
         <v>136</v>
       </c>
       <c r="D59" s="6" t="s">
-        <v>328</v>
+        <v>324</v>
       </c>
       <c r="E59" s="11"/>
       <c r="F59" s="6" t="s">
-        <v>385</v>
+        <v>381</v>
       </c>
     </row>
     <row r="60" spans="1:6" x14ac:dyDescent="0.3">
@@ -4013,7 +4001,7 @@
         <v>141</v>
       </c>
       <c r="D60" s="6" t="s">
-        <v>329</v>
+        <v>325</v>
       </c>
       <c r="E60" s="11"/>
       <c r="F60" s="6" t="s">
@@ -4027,7 +4015,7 @@
         <v>155</v>
       </c>
       <c r="D61" s="6" t="s">
-        <v>330</v>
+        <v>326</v>
       </c>
       <c r="E61" s="11"/>
       <c r="F61" s="6" t="s">
@@ -4041,7 +4029,7 @@
         <v>196</v>
       </c>
       <c r="D62" s="6" t="s">
-        <v>331</v>
+        <v>327</v>
       </c>
       <c r="E62" s="11"/>
       <c r="F62" s="6" t="s">
@@ -4055,7 +4043,7 @@
         <v>167</v>
       </c>
       <c r="D63" s="6" t="s">
-        <v>332</v>
+        <v>328</v>
       </c>
       <c r="E63" s="11"/>
       <c r="F63" s="6" t="s">
@@ -4069,7 +4057,7 @@
         <v>188</v>
       </c>
       <c r="D64" s="6" t="s">
-        <v>333</v>
+        <v>329</v>
       </c>
       <c r="E64" s="11"/>
       <c r="F64" s="6" t="s">
@@ -4288,27 +4276,27 @@
     <row r="81" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A81" s="34"/>
       <c r="B81" s="41" t="s">
-        <v>341</v>
+        <v>337</v>
       </c>
       <c r="C81" s="6" t="s">
-        <v>344</v>
+        <v>340</v>
       </c>
       <c r="D81" s="6" t="s">
-        <v>347</v>
+        <v>343</v>
       </c>
       <c r="E81" s="9"/>
       <c r="F81" s="6" t="s">
-        <v>346</v>
+        <v>342</v>
       </c>
     </row>
     <row r="82" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A82" s="34"/>
       <c r="B82" s="41"/>
       <c r="C82" s="6" t="s">
-        <v>345</v>
+        <v>341</v>
       </c>
       <c r="D82" s="6" t="s">
-        <v>348</v>
+        <v>344</v>
       </c>
       <c r="E82" s="9"/>
       <c r="F82" s="6" t="s">
@@ -4606,10 +4594,10 @@
       <c r="A105" s="34"/>
       <c r="B105" s="41"/>
       <c r="C105" s="6" t="s">
-        <v>228</v>
+        <v>150</v>
       </c>
       <c r="D105" s="6" t="s">
-        <v>227</v>
+        <v>147</v>
       </c>
       <c r="E105" s="11"/>
       <c r="F105" s="6" t="s">
@@ -4618,200 +4606,198 @@
     </row>
     <row r="106" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A106" s="34"/>
-      <c r="B106" s="41"/>
-      <c r="C106" s="6" t="s">
-        <v>150</v>
-      </c>
-      <c r="D106" s="6" t="s">
-        <v>147</v>
-      </c>
-      <c r="E106" s="11"/>
-      <c r="F106" s="6" t="s">
-        <v>149</v>
-      </c>
+      <c r="B106" s="45"/>
+      <c r="C106" s="15"/>
+      <c r="D106" s="15"/>
+      <c r="E106" s="16"/>
+      <c r="F106" s="15"/>
     </row>
     <row r="107" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A107" s="34"/>
-      <c r="B107" s="45"/>
-      <c r="C107" s="15"/>
-      <c r="D107" s="15"/>
-      <c r="E107" s="16"/>
-      <c r="F107" s="15"/>
+      <c r="B107" s="44" t="s">
+        <v>299</v>
+      </c>
+      <c r="C107" s="6" t="s">
+        <v>300</v>
+      </c>
+      <c r="D107" s="6" t="s">
+        <v>301</v>
+      </c>
+      <c r="E107" s="11"/>
+      <c r="F107" s="6" t="s">
+        <v>290</v>
+      </c>
     </row>
     <row r="108" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A108" s="34"/>
-      <c r="B108" s="44" t="s">
-        <v>301</v>
-      </c>
+      <c r="B108" s="41"/>
       <c r="C108" s="6" t="s">
+        <v>303</v>
+      </c>
+      <c r="D108" s="6" t="s">
         <v>302</v>
-      </c>
-      <c r="D108" s="6" t="s">
-        <v>303</v>
       </c>
       <c r="E108" s="11"/>
       <c r="F108" s="6" t="s">
-        <v>292</v>
+        <v>149</v>
       </c>
     </row>
     <row r="109" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A109" s="34"/>
-      <c r="B109" s="41"/>
-      <c r="C109" s="6" t="s">
-        <v>306</v>
-      </c>
-      <c r="D109" s="6" t="s">
-        <v>304</v>
-      </c>
+      <c r="B109" s="45"/>
       <c r="E109" s="11"/>
-      <c r="F109" s="6" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="110" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A110" s="34"/>
-      <c r="B110" s="41"/>
-      <c r="C110" s="6" t="s">
-        <v>307</v>
-      </c>
-      <c r="D110" s="6" t="s">
-        <v>305</v>
-      </c>
-      <c r="E110" s="11"/>
-      <c r="F110" s="6" t="s">
-        <v>149</v>
+      <c r="B110" s="44" t="s">
+        <v>79</v>
+      </c>
+      <c r="C110" s="13" t="s">
+        <v>131</v>
+      </c>
+      <c r="D110" s="13" t="s">
+        <v>130</v>
+      </c>
+      <c r="E110" s="18"/>
+      <c r="F110" s="13" t="s">
+        <v>132</v>
       </c>
     </row>
     <row r="111" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A111" s="34"/>
-      <c r="B111" s="45"/>
+      <c r="B111" s="41"/>
+      <c r="C111" s="6" t="s">
+        <v>151</v>
+      </c>
+      <c r="D111" s="6" t="s">
+        <v>148</v>
+      </c>
       <c r="E111" s="11"/>
+      <c r="F111" s="6" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="112" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A112" s="34"/>
-      <c r="B112" s="44" t="s">
-        <v>79</v>
-      </c>
-      <c r="C112" s="13" t="s">
-        <v>131</v>
-      </c>
-      <c r="D112" s="13" t="s">
-        <v>130</v>
-      </c>
-      <c r="E112" s="18"/>
-      <c r="F112" s="13" t="s">
-        <v>132</v>
-      </c>
+      <c r="B112" s="45"/>
+      <c r="C112" s="15"/>
+      <c r="D112" s="15"/>
+      <c r="E112" s="16"/>
+      <c r="F112" s="15"/>
     </row>
     <row r="113" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A113" s="34"/>
-      <c r="B113" s="41"/>
+      <c r="B113" s="44" t="s">
+        <v>258</v>
+      </c>
       <c r="C113" s="6" t="s">
-        <v>151</v>
+        <v>257</v>
       </c>
       <c r="D113" s="6" t="s">
-        <v>148</v>
+        <v>260</v>
       </c>
       <c r="E113" s="11"/>
       <c r="F113" s="6" t="s">
-        <v>149</v>
+        <v>254</v>
       </c>
     </row>
     <row r="114" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A114" s="34"/>
-      <c r="B114" s="45"/>
-      <c r="C114" s="15"/>
-      <c r="D114" s="15"/>
-      <c r="E114" s="16"/>
-      <c r="F114" s="15"/>
-    </row>
-    <row r="115" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A115" s="34"/>
-      <c r="B115" s="44" t="s">
-        <v>260</v>
-      </c>
-      <c r="C115" s="6" t="s">
+      <c r="B114" s="41"/>
+      <c r="C114" s="6" t="s">
         <v>259</v>
       </c>
-      <c r="D115" s="6" t="s">
-        <v>262</v>
-      </c>
-      <c r="E115" s="11"/>
-      <c r="F115" s="6" t="s">
-        <v>256</v>
-      </c>
+      <c r="D114" s="6" t="s">
+        <v>261</v>
+      </c>
+      <c r="E114" s="11"/>
+      <c r="F114" s="6" t="s">
+        <v>149</v>
+      </c>
+    </row>
+    <row r="115" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
+      <c r="A115" s="35"/>
+      <c r="B115" s="42"/>
+      <c r="C115" s="19"/>
+      <c r="D115" s="19"/>
+      <c r="E115" s="20"/>
+      <c r="F115" s="19"/>
     </row>
     <row r="116" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A116" s="34"/>
-      <c r="B116" s="41"/>
-      <c r="C116" s="6" t="s">
-        <v>261</v>
-      </c>
-      <c r="D116" s="6" t="s">
-        <v>263</v>
-      </c>
-      <c r="E116" s="11"/>
-      <c r="F116" s="6" t="s">
-        <v>149</v>
-      </c>
-    </row>
-    <row r="117" spans="1:6" ht="15" thickBot="1" x14ac:dyDescent="0.35">
-      <c r="A117" s="35"/>
-      <c r="B117" s="42"/>
-      <c r="C117" s="19"/>
-      <c r="D117" s="19"/>
-      <c r="E117" s="20"/>
-      <c r="F117" s="19"/>
+      <c r="A116" s="33" t="s">
+        <v>163</v>
+      </c>
+      <c r="B116" s="43" t="s">
+        <v>13</v>
+      </c>
+      <c r="C116" s="7" t="s">
+        <v>173</v>
+      </c>
+      <c r="D116" s="7" t="s">
+        <v>172</v>
+      </c>
+      <c r="E116" s="7"/>
+      <c r="F116" s="7" t="s">
+        <v>140</v>
+      </c>
+    </row>
+    <row r="117" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A117" s="34"/>
+      <c r="B117" s="41"/>
+      <c r="C117" s="6" t="s">
+        <v>174</v>
+      </c>
+      <c r="D117" s="6" t="s">
+        <v>175</v>
+      </c>
+      <c r="F117" s="6" t="s">
+        <v>140</v>
+      </c>
     </row>
     <row r="118" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A118" s="33" t="s">
-        <v>163</v>
-      </c>
-      <c r="B118" s="43" t="s">
-        <v>13</v>
-      </c>
-      <c r="C118" s="7" t="s">
-        <v>173</v>
-      </c>
-      <c r="D118" s="7" t="s">
-        <v>172</v>
-      </c>
-      <c r="E118" s="7"/>
-      <c r="F118" s="7" t="s">
-        <v>140</v>
-      </c>
+      <c r="A118" s="34"/>
+      <c r="B118" s="45"/>
+      <c r="C118" s="15"/>
+      <c r="D118" s="15"/>
+      <c r="E118" s="15"/>
+      <c r="F118" s="15"/>
     </row>
     <row r="119" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A119" s="34"/>
-      <c r="B119" s="41"/>
+      <c r="B119" s="44" t="s">
+        <v>183</v>
+      </c>
       <c r="C119" s="6" t="s">
-        <v>174</v>
+        <v>165</v>
       </c>
       <c r="D119" s="6" t="s">
-        <v>175</v>
+        <v>164</v>
       </c>
       <c r="F119" s="6" t="s">
-        <v>140</v>
+        <v>149</v>
       </c>
     </row>
     <row r="120" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A120" s="34"/>
-      <c r="B120" s="45"/>
-      <c r="C120" s="15"/>
-      <c r="D120" s="15"/>
-      <c r="E120" s="15"/>
-      <c r="F120" s="15"/>
+      <c r="B120" s="41"/>
+      <c r="C120" s="6" t="s">
+        <v>181</v>
+      </c>
+      <c r="D120" s="6" t="s">
+        <v>305</v>
+      </c>
+      <c r="F120" s="6" t="s">
+        <v>149</v>
+      </c>
     </row>
     <row r="121" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A121" s="34"/>
-      <c r="B121" s="44" t="s">
-        <v>183</v>
-      </c>
+      <c r="B121" s="41"/>
       <c r="C121" s="6" t="s">
-        <v>165</v>
+        <v>177</v>
       </c>
       <c r="D121" s="6" t="s">
-        <v>164</v>
+        <v>176</v>
       </c>
       <c r="F121" s="6" t="s">
         <v>149</v>
@@ -4821,10 +4807,10 @@
       <c r="A122" s="34"/>
       <c r="B122" s="41"/>
       <c r="C122" s="6" t="s">
-        <v>181</v>
+        <v>179</v>
       </c>
       <c r="D122" s="6" t="s">
-        <v>309</v>
+        <v>178</v>
       </c>
       <c r="F122" s="6" t="s">
         <v>149</v>
@@ -4834,10 +4820,10 @@
       <c r="A123" s="34"/>
       <c r="B123" s="41"/>
       <c r="C123" s="6" t="s">
-        <v>177</v>
+        <v>182</v>
       </c>
       <c r="D123" s="6" t="s">
-        <v>176</v>
+        <v>180</v>
       </c>
       <c r="F123" s="6" t="s">
         <v>149</v>
@@ -4847,10 +4833,10 @@
       <c r="A124" s="34"/>
       <c r="B124" s="41"/>
       <c r="C124" s="6" t="s">
-        <v>179</v>
+        <v>191</v>
       </c>
       <c r="D124" s="6" t="s">
-        <v>178</v>
+        <v>187</v>
       </c>
       <c r="F124" s="6" t="s">
         <v>149</v>
@@ -4859,57 +4845,57 @@
     <row r="125" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A125" s="34"/>
       <c r="B125" s="41"/>
-      <c r="C125" s="6" t="s">
-        <v>182</v>
-      </c>
-      <c r="D125" s="6" t="s">
-        <v>180</v>
-      </c>
-      <c r="F125" s="6" t="s">
-        <v>149</v>
-      </c>
     </row>
     <row r="126" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A126" s="34"/>
-      <c r="B126" s="41"/>
-      <c r="C126" s="6" t="s">
-        <v>191</v>
-      </c>
-      <c r="D126" s="6" t="s">
-        <v>187</v>
-      </c>
-      <c r="F126" s="6" t="s">
-        <v>149</v>
+      <c r="B126" s="44" t="s">
+        <v>206</v>
+      </c>
+      <c r="C126" s="13" t="s">
+        <v>203</v>
+      </c>
+      <c r="D126" s="13" t="s">
+        <v>207</v>
+      </c>
+      <c r="E126" s="13"/>
+      <c r="F126" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="127" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A127" s="34"/>
       <c r="B127" s="41"/>
+      <c r="C127" s="6" t="s">
+        <v>204</v>
+      </c>
+      <c r="D127" s="6" t="s">
+        <v>210</v>
+      </c>
+      <c r="F127" s="6" t="s">
+        <v>208</v>
+      </c>
     </row>
     <row r="128" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A128" s="34"/>
-      <c r="B128" s="44" t="s">
-        <v>206</v>
-      </c>
-      <c r="C128" s="13" t="s">
-        <v>203</v>
-      </c>
-      <c r="D128" s="13" t="s">
-        <v>207</v>
-      </c>
-      <c r="E128" s="13"/>
-      <c r="F128" s="13" t="s">
-        <v>208</v>
+      <c r="B128" s="41"/>
+      <c r="C128" s="6" t="s">
+        <v>215</v>
+      </c>
+      <c r="D128" s="6" t="s">
+        <v>214</v>
+      </c>
+      <c r="F128" s="6" t="s">
+        <v>219</v>
       </c>
     </row>
     <row r="129" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A129" s="34"/>
       <c r="B129" s="41"/>
       <c r="C129" s="6" t="s">
-        <v>204</v>
+        <v>205</v>
       </c>
       <c r="D129" s="6" t="s">
-        <v>210</v>
+        <v>209</v>
       </c>
       <c r="F129" s="6" t="s">
         <v>208</v>
@@ -4919,88 +4905,88 @@
       <c r="A130" s="34"/>
       <c r="B130" s="41"/>
       <c r="C130" s="6" t="s">
-        <v>215</v>
+        <v>306</v>
       </c>
       <c r="D130" s="6" t="s">
-        <v>214</v>
+        <v>307</v>
       </c>
       <c r="F130" s="6" t="s">
-        <v>219</v>
+        <v>310</v>
       </c>
     </row>
     <row r="131" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A131" s="34"/>
       <c r="B131" s="41"/>
       <c r="C131" s="6" t="s">
-        <v>205</v>
+        <v>330</v>
       </c>
       <c r="D131" s="6" t="s">
-        <v>209</v>
+        <v>331</v>
       </c>
       <c r="F131" s="6" t="s">
-        <v>208</v>
+        <v>310</v>
       </c>
     </row>
     <row r="132" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A132" s="34"/>
       <c r="B132" s="41"/>
       <c r="C132" s="6" t="s">
+        <v>332</v>
+      </c>
+      <c r="D132" s="6" t="s">
+        <v>333</v>
+      </c>
+      <c r="F132" s="6" t="s">
         <v>310</v>
-      </c>
-      <c r="D132" s="6" t="s">
-        <v>311</v>
-      </c>
-      <c r="F132" s="6" t="s">
-        <v>314</v>
       </c>
     </row>
     <row r="133" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A133" s="34"/>
       <c r="B133" s="41"/>
       <c r="C133" s="6" t="s">
-        <v>334</v>
+        <v>217</v>
       </c>
       <c r="D133" s="6" t="s">
-        <v>335</v>
+        <v>216</v>
       </c>
       <c r="F133" s="6" t="s">
-        <v>314</v>
+        <v>218</v>
       </c>
     </row>
     <row r="134" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A134" s="34"/>
       <c r="B134" s="41"/>
       <c r="C134" s="6" t="s">
-        <v>336</v>
+        <v>221</v>
       </c>
       <c r="D134" s="6" t="s">
-        <v>337</v>
+        <v>211</v>
       </c>
       <c r="F134" s="6" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
     </row>
     <row r="135" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A135" s="34"/>
       <c r="B135" s="41"/>
       <c r="C135" s="6" t="s">
-        <v>217</v>
+        <v>202</v>
       </c>
       <c r="D135" s="6" t="s">
-        <v>216</v>
+        <v>220</v>
       </c>
       <c r="F135" s="6" t="s">
-        <v>218</v>
+        <v>212</v>
       </c>
     </row>
     <row r="136" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A136" s="34"/>
       <c r="B136" s="41"/>
       <c r="C136" s="6" t="s">
-        <v>221</v>
+        <v>262</v>
       </c>
       <c r="D136" s="6" t="s">
-        <v>211</v>
+        <v>365</v>
       </c>
       <c r="F136" s="6" t="s">
         <v>212</v>
@@ -5010,154 +4996,137 @@
       <c r="A137" s="34"/>
       <c r="B137" s="41"/>
       <c r="C137" s="6" t="s">
-        <v>202</v>
+        <v>264</v>
       </c>
       <c r="D137" s="6" t="s">
-        <v>220</v>
+        <v>263</v>
       </c>
       <c r="F137" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="138" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A138" s="34"/>
       <c r="B138" s="41"/>
-      <c r="C138" s="6" t="s">
-        <v>264</v>
-      </c>
-      <c r="D138" s="6" t="s">
-        <v>369</v>
-      </c>
-      <c r="F138" s="6" t="s">
-        <v>212</v>
-      </c>
     </row>
     <row r="139" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A139" s="34"/>
-      <c r="B139" s="41"/>
-      <c r="C139" s="6" t="s">
-        <v>266</v>
-      </c>
-      <c r="D139" s="6" t="s">
-        <v>265</v>
-      </c>
-      <c r="F139" s="6" t="s">
-        <v>213</v>
+      <c r="B139" s="44" t="s">
+        <v>222</v>
+      </c>
+      <c r="C139" s="13" t="s">
+        <v>224</v>
+      </c>
+      <c r="D139" s="13" t="s">
+        <v>223</v>
+      </c>
+      <c r="E139" s="13"/>
+      <c r="F139" s="13" t="s">
+        <v>208</v>
       </c>
     </row>
     <row r="140" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A140" s="34"/>
       <c r="B140" s="41"/>
+      <c r="C140" s="6" t="s">
+        <v>308</v>
+      </c>
+      <c r="D140" s="6" t="s">
+        <v>309</v>
+      </c>
+      <c r="F140" s="6" t="s">
+        <v>310</v>
+      </c>
     </row>
     <row r="141" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A141" s="34"/>
-      <c r="B141" s="44" t="s">
-        <v>222</v>
-      </c>
-      <c r="C141" s="13" t="s">
-        <v>224</v>
-      </c>
-      <c r="D141" s="13" t="s">
-        <v>223</v>
-      </c>
-      <c r="E141" s="13"/>
-      <c r="F141" s="13" t="s">
-        <v>208</v>
+      <c r="B141" s="41"/>
+      <c r="C141" s="6" t="s">
+        <v>225</v>
+      </c>
+      <c r="D141" s="6" t="s">
+        <v>226</v>
+      </c>
+      <c r="F141" s="6" t="s">
+        <v>212</v>
       </c>
     </row>
     <row r="142" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A142" s="34"/>
       <c r="B142" s="41"/>
       <c r="C142" s="6" t="s">
-        <v>312</v>
+        <v>265</v>
       </c>
       <c r="D142" s="6" t="s">
-        <v>313</v>
+        <v>266</v>
       </c>
       <c r="F142" s="6" t="s">
-        <v>314</v>
+        <v>212</v>
       </c>
     </row>
     <row r="143" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A143" s="34"/>
       <c r="B143" s="41"/>
       <c r="C143" s="6" t="s">
-        <v>225</v>
+        <v>267</v>
       </c>
       <c r="D143" s="6" t="s">
-        <v>226</v>
+        <v>304</v>
       </c>
       <c r="F143" s="6" t="s">
-        <v>212</v>
+        <v>213</v>
       </c>
     </row>
     <row r="144" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A144" s="34"/>
-      <c r="B144" s="41"/>
-      <c r="C144" s="6" t="s">
-        <v>267</v>
-      </c>
-      <c r="D144" s="6" t="s">
-        <v>268</v>
-      </c>
-      <c r="F144" s="6" t="s">
-        <v>212</v>
-      </c>
+      <c r="B144" s="45"/>
     </row>
     <row r="145" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A145" s="34"/>
-      <c r="B145" s="41"/>
-      <c r="C145" s="6" t="s">
-        <v>269</v>
-      </c>
-      <c r="D145" s="6" t="s">
-        <v>308</v>
-      </c>
-      <c r="F145" s="6" t="s">
-        <v>213</v>
+      <c r="B145" s="44" t="s">
+        <v>376</v>
+      </c>
+      <c r="C145" s="13" t="s">
+        <v>377</v>
+      </c>
+      <c r="D145" s="13" t="s">
+        <v>378</v>
+      </c>
+      <c r="E145" s="13"/>
+      <c r="F145" s="13" t="s">
+        <v>271</v>
       </c>
     </row>
     <row r="146" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A146" s="34"/>
-      <c r="B146" s="45"/>
+      <c r="B146" s="41"/>
+      <c r="C146" s="6" t="s">
+        <v>379</v>
+      </c>
+      <c r="D146" s="6" t="s">
+        <v>380</v>
+      </c>
+      <c r="F146" s="6" t="s">
+        <v>271</v>
+      </c>
     </row>
     <row r="147" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A147" s="34"/>
-      <c r="B147" s="44" t="s">
-        <v>380</v>
-      </c>
-      <c r="C147" s="13" t="s">
-        <v>381</v>
-      </c>
-      <c r="D147" s="13" t="s">
-        <v>382</v>
-      </c>
-      <c r="E147" s="13"/>
-      <c r="F147" s="13" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="148" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A148" s="34"/>
-      <c r="B148" s="41"/>
-      <c r="C148" s="6" t="s">
-        <v>383</v>
-      </c>
-      <c r="D148" s="6" t="s">
-        <v>384</v>
-      </c>
-      <c r="F148" s="6" t="s">
-        <v>273</v>
-      </c>
-    </row>
-    <row r="149" spans="1:6" x14ac:dyDescent="0.3">
-      <c r="A149" s="34"/>
     </row>
   </sheetData>
   <mergeCells count="25">
-    <mergeCell ref="B147:B148"/>
-    <mergeCell ref="B141:B146"/>
-    <mergeCell ref="A118:A149"/>
+    <mergeCell ref="B116:B118"/>
+    <mergeCell ref="A78:A103"/>
+    <mergeCell ref="B84:B93"/>
+    <mergeCell ref="B94:B103"/>
+    <mergeCell ref="A104:A115"/>
+    <mergeCell ref="B110:B112"/>
+    <mergeCell ref="B104:B106"/>
+    <mergeCell ref="B107:B109"/>
+    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B145:B146"/>
+    <mergeCell ref="B139:B144"/>
+    <mergeCell ref="A116:A147"/>
     <mergeCell ref="A2:A45"/>
     <mergeCell ref="B2:B11"/>
     <mergeCell ref="B12:B22"/>
@@ -5168,18 +5137,9 @@
     <mergeCell ref="B46:B55"/>
     <mergeCell ref="B56:B65"/>
     <mergeCell ref="B81:B83"/>
-    <mergeCell ref="B115:B117"/>
-    <mergeCell ref="B121:B127"/>
-    <mergeCell ref="B128:B140"/>
-    <mergeCell ref="B118:B120"/>
-    <mergeCell ref="A78:A103"/>
-    <mergeCell ref="B84:B93"/>
-    <mergeCell ref="B94:B103"/>
-    <mergeCell ref="A104:A117"/>
-    <mergeCell ref="B112:B114"/>
-    <mergeCell ref="B104:B107"/>
-    <mergeCell ref="B108:B111"/>
-    <mergeCell ref="B78:B80"/>
+    <mergeCell ref="B113:B115"/>
+    <mergeCell ref="B119:B125"/>
+    <mergeCell ref="B126:B138"/>
   </mergeCells>
   <pageMargins left="0.7" right="0.7" top="0.78740157499999996" bottom="0.78740157499999996" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
